--- a/research/traditional_assets/database/data/ireland/ireland_diversified.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_diversified.xlsx
@@ -650,10 +650,10 @@
         <v>0.1218705194661961</v>
       </c>
       <c r="X2">
-        <v>0.09917076609944661</v>
+        <v>0.09914584142549879</v>
       </c>
       <c r="Y2">
-        <v>0.02269975336674948</v>
+        <v>0.0227246780406973</v>
       </c>
       <c r="Z2">
         <v>4.79559334430426</v>
@@ -662,10 +662,10 @@
         <v>0.1148842280262028</v>
       </c>
       <c r="AB2">
-        <v>0.08491682311435889</v>
+        <v>0.0849000842662474</v>
       </c>
       <c r="AC2">
-        <v>0.02996740491184387</v>
+        <v>0.02998414375995535</v>
       </c>
       <c r="AD2">
         <v>3114.3</v>
@@ -787,10 +787,10 @@
         <v>0.1218705194661961</v>
       </c>
       <c r="X3">
-        <v>0.09917076609944661</v>
+        <v>0.09914584142549879</v>
       </c>
       <c r="Y3">
-        <v>0.02269975336674948</v>
+        <v>0.0227246780406973</v>
       </c>
       <c r="Z3">
         <v>4.79559334430426</v>
@@ -799,10 +799,10 @@
         <v>0.1148842280262028</v>
       </c>
       <c r="AB3">
-        <v>0.08491682311435889</v>
+        <v>0.0849000842662474</v>
       </c>
       <c r="AC3">
-        <v>0.02996740491184387</v>
+        <v>0.02998414375995535</v>
       </c>
       <c r="AD3">
         <v>3114.3</v>
@@ -1139,7 +1139,7 @@
         <v>6.44186046511628</v>
       </c>
       <c r="F2">
-        <v>8.68834513575978</v>
+        <v>8.904639854609171</v>
       </c>
       <c r="G2">
         <v>2.71209614212314</v>
@@ -1157,13 +1157,13 @@
         <v>6368.3</v>
       </c>
       <c r="L2">
-        <v>7872.83983178274</v>
+        <v>7932.01353882488</v>
       </c>
       <c r="M2">
         <v>8370.700000000001</v>
       </c>
       <c r="N2">
-        <v>8752.285831782739</v>
+        <v>8811.45953882488</v>
       </c>
       <c r="O2">
         <v>3114.3</v>
@@ -1172,16 +1172,16 @@
         <v>1991.346</v>
       </c>
       <c r="Q2">
-        <v>0.0849168231143589</v>
+        <v>0.0849000842662474</v>
       </c>
       <c r="R2">
-        <v>0.0831686150906388</v>
+        <v>0.082894367852688</v>
       </c>
       <c r="S2">
         <v>0.0557695395797173</v>
       </c>
       <c r="T2">
-        <v>0.0504320395797173</v>
+        <v>0.0492070395797173</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0991707660994466</v>
+        <v>0.0991458414254988</v>
       </c>
       <c r="X2">
-        <v>0.09187074275809889</v>
+        <v>0.09184922726702199</v>
       </c>
       <c r="Y2">
         <v>1.0398097419454</v>
@@ -1236,7 +1236,7 @@
         <v>6368.3</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963755</v>
+        <v>0.05130346377183671</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08317703391927922</v>
+        <v>0.08315957847594085</v>
       </c>
       <c r="C2">
-        <v>9862.264885645411</v>
+        <v>9862.43448648732</v>
       </c>
       <c r="D2">
-        <v>8750.364885645411</v>
+        <v>8750.53448648732</v>
       </c>
       <c r="E2">
         <v>-3114.3</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08317703391927922</v>
+        <v>0.08315957847594085</v>
       </c>
       <c r="T2">
         <v>0.7282077218429368</v>
       </c>
       <c r="U2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V2">
         <v>0.125</v>
       </c>
       <c r="W2">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08317663302267732</v>
+        <v>0.0831469493986431</v>
       </c>
       <c r="C3">
-        <v>9767.530340150246</v>
+        <v>9770.490568676669</v>
       </c>
       <c r="D3">
-        <v>8750.456340150246</v>
+        <v>8753.416568676668</v>
       </c>
       <c r="E3">
         <v>-3019.474</v>
@@ -1539,37 +1539,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M3">
-        <v>5.465449811641458</v>
+        <v>5.332693411641459</v>
       </c>
       <c r="N3">
-        <v>991.7345501883585</v>
+        <v>991.8673065883585</v>
       </c>
       <c r="O3">
-        <v>123.9668187735448</v>
+        <v>123.9834133235448</v>
       </c>
       <c r="P3">
-        <v>867.7677314148137</v>
+        <v>867.8838932648137</v>
       </c>
       <c r="Q3">
-        <v>1018.867731414814</v>
+        <v>1018.983893264814</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08350738649179812</v>
+        <v>0.08348977677055144</v>
       </c>
       <c r="T3">
         <v>0.7346439012026598</v>
       </c>
       <c r="U3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V3">
         <v>0.125</v>
       </c>
       <c r="W3">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>182.4552478509554</v>
+        <v>186.9974369467926</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08317623212607538</v>
+        <v>0.08313432032134534</v>
       </c>
       <c r="C4">
-        <v>9672.795796566787</v>
+        <v>9678.548549980742</v>
       </c>
       <c r="D4">
-        <v>8750.547796566787</v>
+        <v>8756.300549980742</v>
       </c>
       <c r="E4">
         <v>-2924.648</v>
@@ -1621,37 +1621,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M4">
-        <v>10.93089962328292</v>
+        <v>10.66538682328292</v>
       </c>
       <c r="N4">
-        <v>986.269100376717</v>
+        <v>986.534613176717</v>
       </c>
       <c r="O4">
-        <v>123.2836375470896</v>
+        <v>123.3168266470896</v>
       </c>
       <c r="P4">
-        <v>862.9854628296274</v>
+        <v>863.2177865296273</v>
       </c>
       <c r="Q4">
-        <v>1014.085462829627</v>
+        <v>1014.317786529627</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08384448095355207</v>
+        <v>0.08382671380586837</v>
       </c>
       <c r="T4">
         <v>0.7412114311615606</v>
       </c>
       <c r="U4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V4">
         <v>0.125</v>
       </c>
       <c r="W4">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>91.22762392547772</v>
+        <v>93.49871847339629</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08317583122947345</v>
+        <v>0.0831216912440476</v>
       </c>
       <c r="C5">
-        <v>9578.061254895078</v>
+        <v>9586.608432277257</v>
       </c>
       <c r="D5">
-        <v>8750.639254895077</v>
+        <v>8759.186432277256</v>
       </c>
       <c r="E5">
         <v>-2829.822</v>
@@ -1703,37 +1703,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M5">
-        <v>16.39634943492437</v>
+        <v>15.99808023492438</v>
       </c>
       <c r="N5">
-        <v>980.8036505650756</v>
+        <v>981.2019197650756</v>
       </c>
       <c r="O5">
-        <v>122.6004563206344</v>
+        <v>122.6502399706344</v>
       </c>
       <c r="P5">
-        <v>858.2031942444412</v>
+        <v>858.5516797944412</v>
       </c>
       <c r="Q5">
-        <v>1009.303194244441</v>
+        <v>1009.651679794441</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.0841885258165793</v>
+        <v>0.08417059799655266</v>
       </c>
       <c r="T5">
         <v>0.7479143741093048</v>
       </c>
       <c r="U5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V5">
         <v>0.125</v>
       </c>
       <c r="W5">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>60.81841595031848</v>
+        <v>62.33247898226419</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08317543033287153</v>
+        <v>0.08310906216674985</v>
       </c>
       <c r="C6">
-        <v>9483.326715135183</v>
+        <v>9494.67021744641</v>
       </c>
       <c r="D6">
-        <v>8750.730715135183</v>
+        <v>8762.07421744641</v>
       </c>
       <c r="E6">
         <v>-2734.996</v>
@@ -1785,37 +1785,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M6">
-        <v>21.86179924656583</v>
+        <v>21.33077364656583</v>
       </c>
       <c r="N6">
-        <v>975.3382007534341</v>
+        <v>975.8692263534341</v>
       </c>
       <c r="O6">
-        <v>121.9172750941793</v>
+        <v>121.9836532941793</v>
       </c>
       <c r="P6">
-        <v>853.4209256592549</v>
+        <v>853.8855730592549</v>
       </c>
       <c r="Q6">
-        <v>1004.520925659255</v>
+        <v>1004.985573059255</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08453973828091962</v>
+        <v>0.08452164644120953</v>
       </c>
       <c r="T6">
         <v>0.7547569617017938</v>
       </c>
       <c r="U6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V6">
         <v>0.125</v>
       </c>
       <c r="W6">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>45.61381196273886</v>
+        <v>46.74935923669815</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08317502943626959</v>
+        <v>0.08309643308945208</v>
       </c>
       <c r="C7">
-        <v>9388.592177287166</v>
+        <v>9402.733907370879</v>
       </c>
       <c r="D7">
-        <v>8750.822177287166</v>
+        <v>8764.963907370879</v>
       </c>
       <c r="E7">
         <v>-2640.17</v>
@@ -1867,37 +1867,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M7">
-        <v>27.3272490582073</v>
+        <v>26.6634670582073</v>
       </c>
       <c r="N7">
-        <v>969.8727509417927</v>
+        <v>970.5365329417926</v>
       </c>
       <c r="O7">
-        <v>121.2340938677241</v>
+        <v>121.3170666177241</v>
       </c>
       <c r="P7">
-        <v>848.6386570740685</v>
+        <v>849.2194663240685</v>
       </c>
       <c r="Q7">
-        <v>999.7386570740686</v>
+        <v>1000.319466324069</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08489834469187761</v>
+        <v>0.08488008537943813</v>
       </c>
       <c r="T7">
         <v>0.7617436037699141</v>
       </c>
       <c r="U7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V7">
         <v>0.125</v>
       </c>
       <c r="W7">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>36.49104957019108</v>
+        <v>37.39948738935851</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08317462853966767</v>
+        <v>0.08308380401215433</v>
       </c>
       <c r="C8">
-        <v>9293.857641351078</v>
+        <v>9310.799503935816</v>
       </c>
       <c r="D8">
-        <v>8750.913641351079</v>
+        <v>8767.855503935816</v>
       </c>
       <c r="E8">
         <v>-2545.344</v>
@@ -1949,37 +1949,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M8">
-        <v>32.79269886984875</v>
+        <v>31.99616046984875</v>
       </c>
       <c r="N8">
-        <v>964.4073011301512</v>
+        <v>965.2038395301512</v>
       </c>
       <c r="O8">
-        <v>120.5509126412689</v>
+        <v>120.6504799412689</v>
       </c>
       <c r="P8">
-        <v>843.8563884888822</v>
+        <v>844.5533595888822</v>
       </c>
       <c r="Q8">
-        <v>994.9563884888822</v>
+        <v>995.6533595888823</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08526458102647302</v>
+        <v>0.08524615067805458</v>
       </c>
       <c r="T8">
         <v>0.7688788977969306</v>
       </c>
       <c r="U8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V8">
         <v>0.125</v>
       </c>
       <c r="W8">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>30.40920797515924</v>
+        <v>31.1662394911321</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08317422764306574</v>
+        <v>0.08307117493485659</v>
       </c>
       <c r="C9">
-        <v>9199.123107326992</v>
+        <v>9218.867009028871</v>
       </c>
       <c r="D9">
-        <v>8751.005107326991</v>
+        <v>8770.74900902887</v>
       </c>
       <c r="E9">
         <v>-2450.518</v>
@@ -2031,37 +2031,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M9">
-        <v>38.25814868149021</v>
+        <v>37.32885388149021</v>
       </c>
       <c r="N9">
-        <v>958.9418513185097</v>
+        <v>959.8711461185097</v>
       </c>
       <c r="O9">
-        <v>119.8677314148137</v>
+        <v>119.9838932648137</v>
       </c>
       <c r="P9">
-        <v>839.074119903696</v>
+        <v>839.8872528536961</v>
       </c>
       <c r="Q9">
-        <v>990.174119903696</v>
+        <v>990.9872528536961</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08563869341127477</v>
+        <v>0.08562008834868427</v>
       </c>
       <c r="T9">
         <v>0.7761676390073238</v>
       </c>
       <c r="U9">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V9">
         <v>0.125</v>
       </c>
       <c r="W9">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.06503540727935</v>
+        <v>26.71391956382751</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08317382674646384</v>
+        <v>0.08305854585755884</v>
       </c>
       <c r="C10">
-        <v>9104.388575214949</v>
+        <v>9126.936424540188</v>
       </c>
       <c r="D10">
-        <v>8751.09657521495</v>
+        <v>8773.644424540189</v>
       </c>
       <c r="E10">
         <v>-2355.692</v>
@@ -2113,37 +2113,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M10">
-        <v>43.72359849313167</v>
+        <v>42.66154729313167</v>
       </c>
       <c r="N10">
-        <v>953.4764015068682</v>
+        <v>954.5384527068683</v>
       </c>
       <c r="O10">
-        <v>119.1845501883585</v>
+        <v>119.3173065883585</v>
       </c>
       <c r="P10">
-        <v>834.2918513185097</v>
+        <v>835.2211461185098</v>
       </c>
       <c r="Q10">
-        <v>985.3918513185097</v>
+        <v>986.3211461185098</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08602093867400701</v>
+        <v>0.08600215509911027</v>
       </c>
       <c r="T10">
         <v>0.7836148311135951</v>
       </c>
       <c r="U10">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V10">
         <v>0.125</v>
       </c>
       <c r="W10">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.80690598136943</v>
+        <v>23.37467961834907</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.0831734258498619</v>
+        <v>0.08304591678026108</v>
       </c>
       <c r="C11">
-        <v>9009.654045015033</v>
+        <v>9035.007752362406</v>
       </c>
       <c r="D11">
-        <v>8751.188045015033</v>
+        <v>8776.541752362406</v>
       </c>
       <c r="E11">
         <v>-2260.866</v>
@@ -2195,37 +2195,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M11">
-        <v>49.18904830477312</v>
+        <v>47.99424070477313</v>
       </c>
       <c r="N11">
-        <v>948.0109516952268</v>
+        <v>949.2057592952268</v>
       </c>
       <c r="O11">
-        <v>118.5013689619034</v>
+        <v>118.6507199119034</v>
       </c>
       <c r="P11">
-        <v>829.5095827333234</v>
+        <v>830.5550393833234</v>
       </c>
       <c r="Q11">
-        <v>980.6095827333235</v>
+        <v>981.6550393833235</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08641158493152454</v>
+        <v>0.08639261892097419</v>
       </c>
       <c r="T11">
         <v>0.7912256977716524</v>
       </c>
       <c r="U11">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V11">
         <v>0.125</v>
       </c>
       <c r="W11">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.27280531677282</v>
+        <v>20.77749299408807</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08317302495325998</v>
+        <v>0.08303328770296332</v>
       </c>
       <c r="C12">
-        <v>8914.919516727283</v>
+        <v>8943.080994390652</v>
       </c>
       <c r="D12">
-        <v>8751.279516727283</v>
+        <v>8779.440994390652</v>
       </c>
       <c r="E12">
         <v>-2166.04</v>
@@ -2277,37 +2277,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M12">
-        <v>54.65449811641459</v>
+        <v>53.32693411641459</v>
       </c>
       <c r="N12">
-        <v>942.5455018835853</v>
+        <v>943.8730658835854</v>
       </c>
       <c r="O12">
-        <v>117.8181877354482</v>
+        <v>117.9841332354482</v>
       </c>
       <c r="P12">
-        <v>824.7273141481371</v>
+        <v>825.8889326481371</v>
       </c>
       <c r="Q12">
-        <v>975.8273141481371</v>
+        <v>976.9889326481372</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08681091221698693</v>
+        <v>0.08679175971665733</v>
       </c>
       <c r="T12">
         <v>0.799005694799889</v>
       </c>
       <c r="U12">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V12">
         <v>0.125</v>
       </c>
       <c r="W12">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.24552478509554</v>
+        <v>18.69974369467926</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08317262405665804</v>
+        <v>0.08302065862566557</v>
       </c>
       <c r="C13">
-        <v>8820.184990351776</v>
+        <v>8851.156152522579</v>
       </c>
       <c r="D13">
-        <v>8751.370990351776</v>
+        <v>8782.342152522579</v>
       </c>
       <c r="E13">
         <v>-2071.214</v>
@@ -2359,37 +2359,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M13">
-        <v>60.11994792805604</v>
+        <v>58.65962752805604</v>
       </c>
       <c r="N13">
-        <v>937.0800520719439</v>
+        <v>938.5403724719439</v>
       </c>
       <c r="O13">
-        <v>117.135006508993</v>
+        <v>117.317546558993</v>
       </c>
       <c r="P13">
-        <v>819.9450455629509</v>
+        <v>821.222825912951</v>
       </c>
       <c r="Q13">
-        <v>971.0450455629509</v>
+        <v>972.322825912951</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08721921314931363</v>
+        <v>0.08719986996842322</v>
       </c>
       <c r="T13">
         <v>0.8069605232220185</v>
       </c>
       <c r="U13">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V13">
         <v>0.125</v>
       </c>
       <c r="W13">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.58684071372322</v>
+        <v>16.99976699516296</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08317222316005612</v>
+        <v>0.08300802954836783</v>
       </c>
       <c r="C14">
-        <v>8725.450465888554</v>
+        <v>8759.233228658328</v>
       </c>
       <c r="D14">
-        <v>8751.462465888555</v>
+        <v>8785.245228658328</v>
       </c>
       <c r="E14">
         <v>-1976.388</v>
@@ -2441,37 +2441,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M14">
-        <v>65.5853977396975</v>
+        <v>63.99232093969751</v>
       </c>
       <c r="N14">
-        <v>931.6146022603025</v>
+        <v>933.2076790603024</v>
       </c>
       <c r="O14">
-        <v>116.4518252825378</v>
+        <v>116.6509598825378</v>
       </c>
       <c r="P14">
-        <v>815.1627769777647</v>
+        <v>816.5567191777646</v>
       </c>
       <c r="Q14">
-        <v>966.2627769777647</v>
+        <v>967.6567191777647</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08763679364828414</v>
+        <v>0.0876172554531838</v>
       </c>
       <c r="T14">
         <v>0.8150961431991963</v>
       </c>
       <c r="U14">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V14">
         <v>0.125</v>
       </c>
       <c r="W14">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.20460398757962</v>
+        <v>15.58311974556605</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.0831718222634542</v>
+        <v>0.08299540047107007</v>
       </c>
       <c r="C15">
-        <v>8630.715943337695</v>
+        <v>8667.312224700581</v>
       </c>
       <c r="D15">
-        <v>8751.553943337694</v>
+        <v>8788.150224700581</v>
       </c>
       <c r="E15">
         <v>-1881.562</v>
@@ -2523,37 +2523,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M15">
-        <v>71.05084755133896</v>
+        <v>69.32501435133896</v>
       </c>
       <c r="N15">
-        <v>926.149152448661</v>
+        <v>927.874985648661</v>
       </c>
       <c r="O15">
-        <v>115.7686440560826</v>
+        <v>115.9843732060826</v>
       </c>
       <c r="P15">
-        <v>810.3805083925783</v>
+        <v>811.8906124425783</v>
       </c>
       <c r="Q15">
-        <v>961.4805083925784</v>
+        <v>962.9906124425784</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08806397369895511</v>
+        <v>0.08804423600655956</v>
       </c>
       <c r="T15">
         <v>0.823418788922976</v>
       </c>
       <c r="U15">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V15">
         <v>0.125</v>
       </c>
       <c r="W15">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.03501906545811</v>
+        <v>14.38441822667635</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08317142136685227</v>
+        <v>0.08298277139377232</v>
       </c>
       <c r="C16">
-        <v>8535.981422699246</v>
+        <v>8575.393142554505</v>
       </c>
       <c r="D16">
-        <v>8751.645422699246</v>
+        <v>8791.057142554506</v>
       </c>
       <c r="E16">
         <v>-1786.736</v>
@@ -2605,37 +2605,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M16">
-        <v>76.51629736298042</v>
+        <v>74.65770776298042</v>
       </c>
       <c r="N16">
-        <v>920.6837026370195</v>
+        <v>922.5422922370195</v>
       </c>
       <c r="O16">
-        <v>115.0854628296274</v>
+        <v>115.3177865296274</v>
       </c>
       <c r="P16">
-        <v>805.598239807392</v>
+        <v>807.224505707392</v>
       </c>
       <c r="Q16">
-        <v>956.698239807392</v>
+        <v>958.3245057073921</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08850108816940912</v>
+        <v>0.08848114634024638</v>
       </c>
       <c r="T16">
         <v>0.8319349845473086</v>
       </c>
       <c r="U16">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V16">
         <v>0.125</v>
       </c>
       <c r="W16">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.03251770363967</v>
+        <v>13.35695978191376</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08317102047025035</v>
+        <v>0.08297014231647457</v>
       </c>
       <c r="C17">
-        <v>8441.24690397327</v>
+        <v>8483.475984127814</v>
       </c>
       <c r="D17">
-        <v>8751.736903973269</v>
+        <v>8793.965984127813</v>
       </c>
       <c r="E17">
         <v>-1691.91</v>
@@ -2687,37 +2687,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M17">
-        <v>81.98174717462189</v>
+        <v>79.99040117462188</v>
       </c>
       <c r="N17">
-        <v>915.218252825378</v>
+        <v>917.2095988253781</v>
       </c>
       <c r="O17">
-        <v>114.4022816031723</v>
+        <v>114.6511998531723</v>
       </c>
       <c r="P17">
-        <v>800.8159712222058</v>
+        <v>802.5583989722059</v>
       </c>
       <c r="Q17">
-        <v>951.9159712222058</v>
+        <v>953.6583989722059</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08894848768622676</v>
+        <v>0.08892833691707877</v>
       </c>
       <c r="T17">
         <v>0.8406515612451549</v>
       </c>
       <c r="U17">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V17">
         <v>0.125</v>
       </c>
       <c r="W17">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.16368319006369</v>
+        <v>12.46649579645284</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08317061957364842</v>
+        <v>0.08295751323917681</v>
       </c>
       <c r="C18">
-        <v>8346.512387159828</v>
+        <v>8391.560751330731</v>
       </c>
       <c r="D18">
-        <v>8751.828387159829</v>
+        <v>8796.876751330732</v>
       </c>
       <c r="E18">
         <v>-1597.084</v>
@@ -2769,37 +2769,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M18">
-        <v>87.44719698626334</v>
+        <v>85.32309458626334</v>
       </c>
       <c r="N18">
-        <v>909.7528030137366</v>
+        <v>911.8769054137366</v>
       </c>
       <c r="O18">
-        <v>113.7191003767171</v>
+        <v>113.9846131767171</v>
       </c>
       <c r="P18">
-        <v>796.0337026370196</v>
+        <v>797.8922922370195</v>
       </c>
       <c r="Q18">
-        <v>947.1337026370196</v>
+        <v>948.9922922370196</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08940653957249244</v>
+        <v>0.08938617488859767</v>
       </c>
       <c r="T18">
         <v>0.8495756754834263</v>
       </c>
       <c r="U18">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V18">
         <v>0.125</v>
       </c>
       <c r="W18">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.40345299068471</v>
+        <v>11.68733980917454</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08317021867704651</v>
+        <v>0.08294488416187905</v>
       </c>
       <c r="C19">
-        <v>8251.777872258981</v>
+        <v>8299.647446076026</v>
       </c>
       <c r="D19">
-        <v>8751.919872258981</v>
+        <v>8799.789446076025</v>
       </c>
       <c r="E19">
         <v>-1502.258</v>
@@ -2851,37 +2851,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M19">
-        <v>92.9126467979048</v>
+        <v>90.65578799790481</v>
       </c>
       <c r="N19">
-        <v>904.2873532020951</v>
+        <v>906.5442120020952</v>
       </c>
       <c r="O19">
-        <v>113.0359191502619</v>
+        <v>113.3180265002619</v>
       </c>
       <c r="P19">
-        <v>791.2514340518333</v>
+        <v>793.2261855018332</v>
       </c>
       <c r="Q19">
-        <v>942.3514340518333</v>
+        <v>944.3261855018333</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08987562885360789</v>
+        <v>0.0898550451003941</v>
       </c>
       <c r="T19">
         <v>0.8587148286190053</v>
       </c>
       <c r="U19">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V19">
         <v>0.125</v>
       </c>
       <c r="W19">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.73266163829149</v>
+        <v>10.99984923216427</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08316981778044458</v>
+        <v>0.08293225508458131</v>
       </c>
       <c r="C20">
-        <v>8157.04335927079</v>
+        <v>8207.736070278976</v>
       </c>
       <c r="D20">
-        <v>8752.011359270791</v>
+        <v>8802.704070278976</v>
       </c>
       <c r="E20">
         <v>-1407.432</v>
@@ -2933,37 +2933,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M20">
-        <v>98.37809660954625</v>
+        <v>95.98848140954625</v>
       </c>
       <c r="N20">
-        <v>898.8219033904537</v>
+        <v>901.2115185904537</v>
       </c>
       <c r="O20">
-        <v>112.3527379238067</v>
+        <v>112.6514398238067</v>
       </c>
       <c r="P20">
-        <v>786.469165466647</v>
+        <v>788.5600787666469</v>
       </c>
       <c r="Q20">
-        <v>937.5691654666471</v>
+        <v>939.660078766647</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09035615933670177</v>
+        <v>0.09033535117101486</v>
       </c>
       <c r="T20">
         <v>0.8680768879286229</v>
       </c>
       <c r="U20">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V20">
         <v>0.125</v>
       </c>
       <c r="W20">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.13640265838641</v>
+        <v>10.38874649704403</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08316941688384263</v>
+        <v>0.08291962600728356</v>
       </c>
       <c r="C21">
-        <v>8062.308848195315</v>
+        <v>8115.82662585743</v>
       </c>
       <c r="D21">
-        <v>8752.102848195316</v>
+        <v>8805.620625857431</v>
       </c>
       <c r="E21">
         <v>-1312.606</v>
@@ -3015,37 +3015,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M21">
-        <v>103.8435464211877</v>
+        <v>101.3211748211877</v>
       </c>
       <c r="N21">
-        <v>893.3564535788122</v>
+        <v>895.8788251788122</v>
       </c>
       <c r="O21">
-        <v>111.6695566973515</v>
+        <v>111.9848531473515</v>
       </c>
       <c r="P21">
-        <v>781.6868968814607</v>
+        <v>783.8939720314607</v>
       </c>
       <c r="Q21">
-        <v>932.7868968814607</v>
+        <v>934.9939720314608</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09084855476999548</v>
+        <v>0.09082751665078673</v>
       </c>
       <c r="T21">
         <v>0.8776701091965025</v>
       </c>
       <c r="U21">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V21">
         <v>0.125</v>
       </c>
       <c r="W21">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.602907781629231</v>
+        <v>9.841970365620663</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08316901598724072</v>
+        <v>0.08290699692998582</v>
       </c>
       <c r="C22">
-        <v>7967.574339032612</v>
+        <v>8023.919114731751</v>
       </c>
       <c r="D22">
-        <v>8752.194339032612</v>
+        <v>8808.539114731751</v>
       </c>
       <c r="E22">
         <v>-1217.78</v>
@@ -3097,37 +3097,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M22">
-        <v>109.3089962328292</v>
+        <v>106.6538682328292</v>
       </c>
       <c r="N22">
-        <v>887.8910037671708</v>
+        <v>890.5461317671708</v>
       </c>
       <c r="O22">
-        <v>110.9863754708963</v>
+        <v>111.3182664708963</v>
       </c>
       <c r="P22">
-        <v>776.9046282962745</v>
+        <v>779.2278652962744</v>
       </c>
       <c r="Q22">
-        <v>928.0046282962745</v>
+        <v>930.3278652962745</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09135326008912156</v>
+        <v>0.09133198626755293</v>
       </c>
       <c r="T22">
         <v>0.8875031609960793</v>
       </c>
       <c r="U22">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V22">
         <v>0.125</v>
       </c>
       <c r="W22">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.12276239254777</v>
+        <v>9.34987184733963</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08316861509063879</v>
+        <v>0.08289436785268804</v>
       </c>
       <c r="C23">
-        <v>7872.839831782743</v>
+        <v>7932.01353882488</v>
       </c>
       <c r="D23">
-        <v>8752.285831782743</v>
+        <v>8811.45953882488</v>
       </c>
       <c r="E23">
         <v>-1122.954</v>
@@ -3179,37 +3179,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M23">
-        <v>114.7744460444706</v>
+        <v>111.9865616444706</v>
       </c>
       <c r="N23">
-        <v>882.4255539555293</v>
+        <v>885.2134383555293</v>
       </c>
       <c r="O23">
-        <v>110.3031942444412</v>
+        <v>110.6516797944412</v>
       </c>
       <c r="P23">
-        <v>772.1223597110882</v>
+        <v>774.5617585610881</v>
       </c>
       <c r="Q23">
-        <v>923.2223597110882</v>
+        <v>925.6617585610882</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09187074275809892</v>
+        <v>0.09184922726702202</v>
       </c>
       <c r="T23">
         <v>0.8975851508158983</v>
       </c>
       <c r="U23">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V23">
         <v>0.125</v>
       </c>
       <c r="W23">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.688345135759782</v>
+        <v>8.904639854609172</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08337996419403687</v>
+        <v>0.08317048877539029</v>
       </c>
       <c r="C24">
-        <v>7730.043536662281</v>
+        <v>7773.774174219294</v>
       </c>
       <c r="D24">
-        <v>8704.315536662281</v>
+        <v>8748.046174219295</v>
       </c>
       <c r="E24">
         <v>-1028.128</v>
@@ -3261,37 +3261,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M24">
-        <v>122.5346850561121</v>
+        <v>120.4485130561121</v>
       </c>
       <c r="N24">
-        <v>874.6653149438879</v>
+        <v>876.7514869438878</v>
       </c>
       <c r="O24">
-        <v>109.333164367986</v>
+        <v>109.593935867986</v>
       </c>
       <c r="P24">
-        <v>765.3321505759019</v>
+        <v>767.1575510759019</v>
       </c>
       <c r="Q24">
-        <v>916.4321505759019</v>
+        <v>918.2575510759019</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09240149421346032</v>
+        <v>0.09237973085622113</v>
       </c>
       <c r="T24">
         <v>0.9079256531952</v>
       </c>
       <c r="U24">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V24">
         <v>0.125</v>
       </c>
       <c r="W24">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.138103913543777</v>
+        <v>8.27905612695646</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08338918829743493</v>
+        <v>0.08317098469809253</v>
       </c>
       <c r="C25">
-        <v>7633.135897725322</v>
+        <v>7678.83510274041</v>
       </c>
       <c r="D25">
-        <v>8702.233897725322</v>
+        <v>8747.93310274041</v>
       </c>
       <c r="E25">
         <v>-933.3020000000001</v>
@@ -3343,37 +3343,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M25">
-        <v>128.1044434677535</v>
+        <v>125.9234454677535</v>
       </c>
       <c r="N25">
-        <v>869.0955565322464</v>
+        <v>871.2765545322463</v>
       </c>
       <c r="O25">
-        <v>108.6369445665308</v>
+        <v>108.9095693165308</v>
       </c>
       <c r="P25">
-        <v>760.4586119657156</v>
+        <v>762.3669852157155</v>
       </c>
       <c r="Q25">
-        <v>911.5586119657156</v>
+        <v>913.4669852157156</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09294603142090901</v>
+        <v>0.09292401375942538</v>
       </c>
       <c r="T25">
         <v>0.9185347400518861</v>
       </c>
       <c r="U25">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V25">
         <v>0.125</v>
       </c>
       <c r="W25">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.784273308607093</v>
+        <v>7.919097164914874</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08339841240083301</v>
+        <v>0.08317148062079478</v>
       </c>
       <c r="C26">
-        <v>7536.229254199103</v>
+        <v>7583.896034184461</v>
       </c>
       <c r="D26">
-        <v>8700.153254199104</v>
+        <v>8747.820034184462</v>
       </c>
       <c r="E26">
         <v>-838.4760000000001</v>
@@ -3425,37 +3425,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M26">
-        <v>133.674201879395</v>
+        <v>131.398377879395</v>
       </c>
       <c r="N26">
-        <v>863.5257981206049</v>
+        <v>865.801622120605</v>
       </c>
       <c r="O26">
-        <v>107.9407247650756</v>
+        <v>108.2252027650756</v>
       </c>
       <c r="P26">
-        <v>755.5850733555293</v>
+        <v>757.5764193555293</v>
       </c>
       <c r="Q26">
-        <v>906.6850733555293</v>
+        <v>908.6764193555293</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09350489855486954</v>
+        <v>0.09348261989692451</v>
       </c>
       <c r="T26">
         <v>0.9294230134048008</v>
       </c>
       <c r="U26">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V26">
         <v>0.125</v>
       </c>
       <c r="W26">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.45992858741513</v>
+        <v>7.589134783043423</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08340763650423108</v>
+        <v>0.08317197654349703</v>
       </c>
       <c r="C27">
-        <v>7439.32360536982</v>
+        <v>7488.956968551336</v>
       </c>
       <c r="D27">
-        <v>8698.07360536982</v>
+        <v>8747.706968551336</v>
       </c>
       <c r="E27">
         <v>-743.6500000000001</v>
@@ -3507,37 +3507,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M27">
-        <v>139.2439602910365</v>
+        <v>136.8733102910365</v>
       </c>
       <c r="N27">
-        <v>857.9560397089634</v>
+        <v>860.3266897089635</v>
       </c>
       <c r="O27">
-        <v>107.2445049636204</v>
+        <v>107.5408362136204</v>
       </c>
       <c r="P27">
-        <v>750.711534745343</v>
+        <v>752.7858534953431</v>
       </c>
       <c r="Q27">
-        <v>901.811534745343</v>
+        <v>903.8858534953431</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09407866881240233</v>
+        <v>0.09405612219809026</v>
       </c>
       <c r="T27">
         <v>0.9406016407137933</v>
       </c>
       <c r="U27">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V27">
         <v>0.125</v>
       </c>
       <c r="W27">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.161531443918523</v>
+        <v>7.285569391721685</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08341686060762916</v>
+        <v>0.08317247246619928</v>
       </c>
       <c r="C28">
-        <v>7342.418950524332</v>
+        <v>7394.017905840918</v>
       </c>
       <c r="D28">
-        <v>8695.994950524333</v>
+        <v>8747.593905840919</v>
       </c>
       <c r="E28">
         <v>-648.8240000000001</v>
@@ -3589,37 +3589,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M28">
-        <v>144.8137187026779</v>
+        <v>142.3482427026779</v>
       </c>
       <c r="N28">
-        <v>852.3862812973221</v>
+        <v>854.851757297322</v>
       </c>
       <c r="O28">
-        <v>106.5482851621653</v>
+        <v>106.8564696621653</v>
       </c>
       <c r="P28">
-        <v>745.8379961351568</v>
+        <v>747.9952876351567</v>
       </c>
       <c r="Q28">
-        <v>896.9379961351568</v>
+        <v>899.0952876351568</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09466794637419278</v>
+        <v>0.0946451245614497</v>
       </c>
       <c r="T28">
         <v>0.952082393085191</v>
       </c>
       <c r="U28">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V28">
         <v>0.125</v>
       </c>
       <c r="W28">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.886087926844734</v>
+        <v>7.005355184347774</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08394583471102723</v>
+        <v>0.08317296838890154</v>
       </c>
       <c r="C29">
-        <v>7130.028133937421</v>
+        <v>7299.0788460531</v>
       </c>
       <c r="D29">
-        <v>8578.430133937421</v>
+        <v>8747.4808460531</v>
       </c>
       <c r="E29">
         <v>-553.998</v>
@@ -3671,45 +3671,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M29">
-        <v>156.0161415143194</v>
+        <v>147.8231751143194</v>
       </c>
       <c r="N29">
-        <v>841.1838584856805</v>
+        <v>849.3768248856805</v>
       </c>
       <c r="O29">
-        <v>105.1479823107101</v>
+        <v>106.1721031107101</v>
       </c>
       <c r="P29">
-        <v>736.0358761749704</v>
+        <v>743.2047217749705</v>
       </c>
       <c r="Q29">
-        <v>887.1358761749705</v>
+        <v>894.3047217749705</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09527336852671719</v>
+        <v>0.09525026397586007</v>
       </c>
       <c r="T29">
         <v>0.963877686617449</v>
       </c>
       <c r="U29">
-        <v>0.0609366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V29">
         <v>0.125</v>
       </c>
       <c r="W29">
-        <v>0.05331953957971734</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.391646340699149</v>
+        <v>6.745897584927485</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08397430881442532</v>
+        <v>0.08358996431160377</v>
       </c>
       <c r="C30">
-        <v>7028.963843071657</v>
+        <v>7110.209937016674</v>
       </c>
       <c r="D30">
-        <v>8572.191843071658</v>
+        <v>8653.437937016675</v>
       </c>
       <c r="E30">
         <v>-459.172</v>
@@ -3753,37 +3753,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M30">
-        <v>161.7945171259609</v>
+        <v>157.8118251259608</v>
       </c>
       <c r="N30">
-        <v>835.4054828740391</v>
+        <v>839.3881748740391</v>
       </c>
       <c r="O30">
-        <v>104.4256853592549</v>
+        <v>104.9235218592549</v>
       </c>
       <c r="P30">
-        <v>730.9797975147842</v>
+        <v>734.4646530147843</v>
       </c>
       <c r="Q30">
-        <v>882.0797975147842</v>
+        <v>885.5646530147843</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09589560796125619</v>
+        <v>0.09587221281844852</v>
       </c>
       <c r="T30">
         <v>0.9760006271922695</v>
       </c>
       <c r="U30">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V30">
         <v>0.125</v>
       </c>
       <c r="W30">
-        <v>0.05331953957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.16337325710275</v>
+        <v>6.318918111517079</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08400278291782338</v>
+        <v>0.08360533523430601</v>
       </c>
       <c r="C31">
-        <v>6927.908618665077</v>
+        <v>7011.95603976307</v>
       </c>
       <c r="D31">
-        <v>8565.962618665077</v>
+        <v>8650.01003976307</v>
       </c>
       <c r="E31">
         <v>-364.3460000000005</v>
@@ -3835,37 +3835,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M31">
-        <v>167.5728927376023</v>
+        <v>163.4479617376023</v>
       </c>
       <c r="N31">
-        <v>829.6271072623977</v>
+        <v>833.7520382623977</v>
       </c>
       <c r="O31">
-        <v>103.7033884077997</v>
+        <v>104.2190047827997</v>
       </c>
       <c r="P31">
-        <v>725.923718854598</v>
+        <v>729.533033479598</v>
       </c>
       <c r="Q31">
-        <v>877.023718854598</v>
+        <v>880.633033479598</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09653537526719064</v>
+        <v>0.09651168134674365</v>
       </c>
       <c r="T31">
         <v>0.9884650590508878</v>
       </c>
       <c r="U31">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V31">
         <v>0.125</v>
       </c>
       <c r="W31">
-        <v>0.05331953957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.950843144788863</v>
+        <v>6.101024383533733</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08403125702122145</v>
+        <v>0.08362070615700826</v>
       </c>
       <c r="C32">
-        <v>6826.862440966835</v>
+        <v>6913.704857228578</v>
       </c>
       <c r="D32">
-        <v>8559.742440966837</v>
+        <v>8646.584857228579</v>
       </c>
       <c r="E32">
         <v>-269.52</v>
@@ -3917,37 +3917,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M32">
-        <v>173.3512683492438</v>
+        <v>169.0840983492438</v>
       </c>
       <c r="N32">
-        <v>823.8487316507562</v>
+        <v>828.1159016507562</v>
       </c>
       <c r="O32">
-        <v>102.9810914563445</v>
+        <v>103.5144877063445</v>
       </c>
       <c r="P32">
-        <v>720.8676401944117</v>
+        <v>724.6014139444117</v>
       </c>
       <c r="Q32">
-        <v>871.9676401944117</v>
+        <v>875.7014139444117</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09719342163900893</v>
+        <v>0.09716942040441867</v>
       </c>
       <c r="T32">
         <v>1.001285617534038</v>
       </c>
       <c r="U32">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V32">
         <v>0.125</v>
       </c>
       <c r="W32">
-        <v>0.05331953957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.752481706629234</v>
+        <v>5.897656904082607</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08446660612461954</v>
+        <v>0.08363607707971052</v>
       </c>
       <c r="C33">
-        <v>6638.04684155114</v>
+        <v>6815.456386189597</v>
       </c>
       <c r="D33">
-        <v>8465.752841551141</v>
+        <v>8643.162386189597</v>
       </c>
       <c r="E33">
         <v>-174.694</v>
@@ -3999,45 +3999,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M33">
-        <v>183.5390529608852</v>
+        <v>174.7202349608852</v>
       </c>
       <c r="N33">
-        <v>813.6609470391147</v>
+        <v>822.4797650391147</v>
       </c>
       <c r="O33">
-        <v>101.7076183798893</v>
+        <v>102.8099706298893</v>
       </c>
       <c r="P33">
-        <v>711.9533286592253</v>
+        <v>719.6697944092253</v>
       </c>
       <c r="Q33">
-        <v>863.0533286592254</v>
+        <v>870.7697944092254</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09787054181870602</v>
+        <v>0.09784622436231616</v>
       </c>
       <c r="T33">
         <v>1.014477786408004</v>
       </c>
       <c r="U33">
-        <v>0.0624366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V33">
         <v>0.125</v>
       </c>
       <c r="W33">
-        <v>0.05463203957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>5.433176121991418</v>
+        <v>5.707409907176716</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08450820522801761</v>
+        <v>0.08387544800241276</v>
       </c>
       <c r="C34">
-        <v>6534.347737547285</v>
+        <v>6667.679832874033</v>
       </c>
       <c r="D34">
-        <v>8456.879737547286</v>
+        <v>8590.211832874034</v>
       </c>
       <c r="E34">
         <v>-79.86799999999994</v>
@@ -4081,37 +4081,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M34">
-        <v>189.4596675725267</v>
+        <v>182.7839171725267</v>
       </c>
       <c r="N34">
-        <v>807.7403324274733</v>
+        <v>814.4160828274732</v>
       </c>
       <c r="O34">
-        <v>100.9675415534342</v>
+        <v>101.8020103534342</v>
       </c>
       <c r="P34">
-        <v>706.7727908740392</v>
+        <v>712.6140724740391</v>
       </c>
       <c r="Q34">
-        <v>857.8727908740392</v>
+        <v>863.7140724740391</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.09856757729780596</v>
+        <v>0.09854293431897532</v>
       </c>
       <c r="T34">
         <v>1.028057960248852</v>
       </c>
       <c r="U34">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V34">
         <v>0.125</v>
       </c>
       <c r="W34">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.263389368179187</v>
+        <v>5.455622220081647</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08454980433141568</v>
+        <v>0.08389781892511501</v>
       </c>
       <c r="C35">
-        <v>6430.667214180539</v>
+        <v>6567.938356367871</v>
       </c>
       <c r="D35">
-        <v>8448.025214180539</v>
+        <v>8585.296356367871</v>
       </c>
       <c r="E35">
         <v>14.95800000000008</v>
@@ -4163,37 +4163,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M35">
-        <v>195.3802821841682</v>
+        <v>188.4959145841681</v>
       </c>
       <c r="N35">
-        <v>801.8197178158318</v>
+        <v>808.7040854158317</v>
       </c>
       <c r="O35">
-        <v>100.227464726979</v>
+        <v>101.088010676979</v>
       </c>
       <c r="P35">
-        <v>701.5922530888529</v>
+        <v>707.6160747388528</v>
       </c>
       <c r="Q35">
-        <v>852.6922530888529</v>
+        <v>858.7160747388529</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.09928541980613279</v>
+        <v>0.09926044158777357</v>
       </c>
       <c r="T35">
         <v>1.042043512413307</v>
       </c>
       <c r="U35">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V35">
         <v>0.125</v>
       </c>
       <c r="W35">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.103892720658605</v>
+        <v>5.290300334624628</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08459140343481375</v>
+        <v>0.08392018984781727</v>
       </c>
       <c r="C36">
-        <v>6327.005213149041</v>
+        <v>6468.202502095892</v>
       </c>
       <c r="D36">
-        <v>8439.189213149042</v>
+        <v>8580.386502095893</v>
       </c>
       <c r="E36">
         <v>109.7840000000001</v>
@@ -4245,37 +4245,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M36">
-        <v>201.3008967958096</v>
+        <v>194.2079119958096</v>
       </c>
       <c r="N36">
-        <v>795.8991032041904</v>
+        <v>802.9920880041904</v>
       </c>
       <c r="O36">
-        <v>99.4873879005238</v>
+        <v>100.3740110005238</v>
       </c>
       <c r="P36">
-        <v>696.4117153036666</v>
+        <v>702.6180770036666</v>
       </c>
       <c r="Q36">
-        <v>847.5117153036666</v>
+        <v>853.7180770036666</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1000250151177422</v>
+        <v>0.09999969150108087</v>
       </c>
       <c r="T36">
         <v>1.056452869188806</v>
       </c>
       <c r="U36">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V36">
         <v>0.125</v>
       </c>
       <c r="W36">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.953778228874529</v>
+        <v>5.134703265959197</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08463300253821182</v>
+        <v>0.08394256077051949</v>
       </c>
       <c r="C37">
-        <v>6223.361676394592</v>
+        <v>6368.4722604177</v>
       </c>
       <c r="D37">
-        <v>8430.371676394592</v>
+        <v>8575.482260417701</v>
       </c>
       <c r="E37">
         <v>204.6100000000001</v>
@@ -4327,37 +4327,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M37">
-        <v>207.2215114074511</v>
+        <v>199.9199094074511</v>
       </c>
       <c r="N37">
-        <v>789.9784885925488</v>
+        <v>797.2800905925488</v>
       </c>
       <c r="O37">
-        <v>98.74731107406861</v>
+        <v>99.66001132406861</v>
       </c>
       <c r="P37">
-        <v>691.2311775184802</v>
+        <v>697.6200792684803</v>
       </c>
       <c r="Q37">
-        <v>842.3311775184802</v>
+        <v>848.7200792684803</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1007873672081704</v>
+        <v>0.1007616875655668</v>
       </c>
       <c r="T37">
         <v>1.071305590788167</v>
       </c>
       <c r="U37">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V37">
         <v>0.125</v>
       </c>
       <c r="W37">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.812241708049542</v>
+        <v>4.987997458360363</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08467460164160991</v>
+        <v>0.08396493169322176</v>
       </c>
       <c r="C38">
-        <v>6119.736546101388</v>
+        <v>6268.747621714904</v>
       </c>
       <c r="D38">
-        <v>8421.572546101388</v>
+        <v>8570.583621714904</v>
       </c>
       <c r="E38">
         <v>299.4359999999997</v>
@@ -4409,37 +4409,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M38">
-        <v>213.1421260190925</v>
+        <v>205.6319068190925</v>
       </c>
       <c r="N38">
-        <v>784.0578739809074</v>
+        <v>791.5680931809075</v>
       </c>
       <c r="O38">
-        <v>98.00723424761343</v>
+        <v>98.94601164761343</v>
       </c>
       <c r="P38">
-        <v>686.050639733294</v>
+        <v>692.622081533294</v>
       </c>
       <c r="Q38">
-        <v>837.150639733294</v>
+        <v>843.722081533294</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1015735428014245</v>
+        <v>0.101547496007068</v>
       </c>
       <c r="T38">
         <v>1.086622459937507</v>
       </c>
       <c r="U38">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V38">
         <v>0.125</v>
       </c>
       <c r="W38">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.678568327270389</v>
+        <v>4.849441973405909</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08471620074500798</v>
+        <v>0.08398730261592399</v>
       </c>
       <c r="C39">
-        <v>6016.129764694748</v>
+        <v>6169.028576391109</v>
       </c>
       <c r="D39">
-        <v>8412.791764694748</v>
+        <v>8565.690576391109</v>
       </c>
       <c r="E39">
         <v>394.2619999999997</v>
@@ -4491,37 +4491,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M39">
-        <v>219.0627406307339</v>
+        <v>211.343904230734</v>
       </c>
       <c r="N39">
-        <v>778.137259369266</v>
+        <v>785.8560957692659</v>
       </c>
       <c r="O39">
-        <v>97.26715742115825</v>
+        <v>98.23201197115824</v>
       </c>
       <c r="P39">
-        <v>680.8701019481077</v>
+        <v>687.6240837981077</v>
       </c>
       <c r="Q39">
-        <v>831.9701019481078</v>
+        <v>838.7240837981077</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1023846763500199</v>
+        <v>0.1023582507482994</v>
       </c>
       <c r="T39">
         <v>1.102425578901113</v>
       </c>
       <c r="U39">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V39">
         <v>0.125</v>
       </c>
       <c r="W39">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.552120534641459</v>
+        <v>4.718375974124668</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08475779984840606</v>
+        <v>0.08400967353862625</v>
       </c>
       <c r="C40">
-        <v>5912.541274839863</v>
+        <v>6069.315114871792</v>
       </c>
       <c r="D40">
-        <v>8404.029274839864</v>
+        <v>8560.803114871793</v>
       </c>
       <c r="E40">
         <v>489.0880000000002</v>
@@ -4573,37 +4573,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M40">
-        <v>224.9833552423754</v>
+        <v>217.0559016423754</v>
       </c>
       <c r="N40">
-        <v>772.2166447576245</v>
+        <v>780.1440983576244</v>
       </c>
       <c r="O40">
-        <v>96.52708059470307</v>
+        <v>97.51801229470306</v>
       </c>
       <c r="P40">
-        <v>675.6895641629214</v>
+        <v>682.6260860629213</v>
       </c>
       <c r="Q40">
-        <v>826.7895641629215</v>
+        <v>833.7260860629214</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1032219754969572</v>
+        <v>0.1031951588682801</v>
       </c>
       <c r="T40">
         <v>1.118738475895802</v>
       </c>
       <c r="U40">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V40">
         <v>0.125</v>
       </c>
       <c r="W40">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.432327888992999</v>
+        <v>4.594208185331913</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08479939895180413</v>
+        <v>0.08403204446132849</v>
       </c>
       <c r="C41">
-        <v>5808.971019440556</v>
+        <v>5969.607227604298</v>
       </c>
       <c r="D41">
-        <v>8395.285019440556</v>
+        <v>8555.921227604298</v>
       </c>
       <c r="E41">
         <v>583.9140000000002</v>
@@ -4655,37 +4655,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M41">
-        <v>230.9039698540169</v>
+        <v>222.7678990540169</v>
       </c>
       <c r="N41">
-        <v>766.296030145983</v>
+        <v>774.4321009459831</v>
       </c>
       <c r="O41">
-        <v>95.78700376824787</v>
+        <v>96.80401261824788</v>
       </c>
       <c r="P41">
-        <v>670.5090263777352</v>
+        <v>677.6280883277352</v>
       </c>
       <c r="Q41">
-        <v>821.6090263777352</v>
+        <v>828.7280883277352</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1040867270749416</v>
+        <v>0.104059506598752</v>
       </c>
       <c r="T41">
         <v>1.135586221972285</v>
       </c>
       <c r="U41">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V41">
         <v>0.125</v>
       </c>
       <c r="W41">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.318678455941896</v>
+        <v>4.476407975451608</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.0853309980552022</v>
+        <v>0.08405441538403075</v>
       </c>
       <c r="C42">
-        <v>5603.982344501612</v>
+        <v>5869.904905057729</v>
       </c>
       <c r="D42">
-        <v>8285.122344501613</v>
+        <v>8551.04490505773</v>
       </c>
       <c r="E42">
         <v>678.7400000000002</v>
@@ -4737,45 +4737,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M42">
-        <v>242.1348404656584</v>
+        <v>228.4798964656584</v>
       </c>
       <c r="N42">
-        <v>755.0651595343415</v>
+        <v>768.7201035343415</v>
       </c>
       <c r="O42">
-        <v>94.38314494179269</v>
+        <v>96.09001294179269</v>
       </c>
       <c r="P42">
-        <v>660.6820145925489</v>
+        <v>672.6300905925489</v>
       </c>
       <c r="Q42">
-        <v>811.7820145925489</v>
+        <v>823.7300905925489</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1049803037055254</v>
+        <v>0.1049526659202397</v>
       </c>
       <c r="T42">
         <v>1.15299555958465</v>
       </c>
       <c r="U42">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V42">
         <v>0.125</v>
       </c>
       <c r="W42">
-        <v>0.05585703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.118366436165271</v>
+        <v>4.364497776065317</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08538484715860027</v>
+        <v>0.08407678630673299</v>
       </c>
       <c r="C43">
-        <v>5498.158304227449</v>
+        <v>5770.208137722913</v>
       </c>
       <c r="D43">
-        <v>8274.124304227449</v>
+        <v>8546.174137722914</v>
       </c>
       <c r="E43">
         <v>773.5660000000003</v>
@@ -4819,45 +4819,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M43">
-        <v>248.1882114772998</v>
+        <v>234.1918938772998</v>
       </c>
       <c r="N43">
-        <v>749.0117885227002</v>
+        <v>763.0081061227002</v>
       </c>
       <c r="O43">
-        <v>93.62647356533752</v>
+        <v>95.37601326533752</v>
       </c>
       <c r="P43">
-        <v>655.3853149573627</v>
+        <v>667.6320928573626</v>
       </c>
       <c r="Q43">
-        <v>806.4853149573627</v>
+        <v>818.7320928573627</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1059041710693494</v>
+        <v>0.1058761018288964</v>
       </c>
       <c r="T43">
         <v>1.170995044234723</v>
       </c>
       <c r="U43">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V43">
         <v>0.125</v>
       </c>
       <c r="W43">
-        <v>0.05585703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.017918474307582</v>
+        <v>4.258046610795432</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08543869626199836</v>
+        <v>0.08446665722943525</v>
       </c>
       <c r="C44">
-        <v>5392.363423821812</v>
+        <v>5591.378725119149</v>
       </c>
       <c r="D44">
-        <v>8263.155423821812</v>
+        <v>8462.170725119149</v>
       </c>
       <c r="E44">
         <v>868.3919999999998</v>
@@ -4901,37 +4901,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M44">
-        <v>254.2415824889412</v>
+        <v>243.8865832889412</v>
       </c>
       <c r="N44">
-        <v>742.9584175110587</v>
+        <v>753.3134167110587</v>
       </c>
       <c r="O44">
-        <v>92.86980218888233</v>
+        <v>94.16417708888234</v>
       </c>
       <c r="P44">
-        <v>650.0886153221763</v>
+        <v>659.1492396221764</v>
       </c>
       <c r="Q44">
-        <v>801.1886153221764</v>
+        <v>810.2492396221764</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1068598959284777</v>
+        <v>0.106831380355093</v>
       </c>
       <c r="T44">
         <v>1.18961520076928</v>
       </c>
       <c r="U44">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V44">
         <v>0.125</v>
       </c>
       <c r="W44">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.92225374872883</v>
+        <v>4.088785805894788</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08549254536539644</v>
+        <v>0.08449777815213749</v>
       </c>
       <c r="C45">
-        <v>5286.59758746787</v>
+        <v>5489.918381324087</v>
       </c>
       <c r="D45">
-        <v>8252.21558746787</v>
+        <v>8455.536381324087</v>
       </c>
       <c r="E45">
         <v>963.2179999999998</v>
@@ -4983,37 +4983,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M45">
-        <v>260.2949535005827</v>
+        <v>249.6934067005827</v>
       </c>
       <c r="N45">
-        <v>736.9050464994173</v>
+        <v>747.5065932994172</v>
       </c>
       <c r="O45">
-        <v>92.11313081242716</v>
+        <v>93.43832416242715</v>
       </c>
       <c r="P45">
-        <v>644.7919156869901</v>
+        <v>654.06826913699</v>
       </c>
       <c r="Q45">
-        <v>795.8919156869902</v>
+        <v>805.16826913699</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1078491549931894</v>
+        <v>0.1078201774260685</v>
       </c>
       <c r="T45">
         <v>1.208888696129612</v>
       </c>
       <c r="U45">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V45">
         <v>0.125</v>
       </c>
       <c r="W45">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.83103854527002</v>
+        <v>3.993697763897234</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.0855463944687945</v>
+        <v>0.08452889907483974</v>
       </c>
       <c r="C46">
-        <v>5180.860679961298</v>
+        <v>5388.468432033854</v>
       </c>
       <c r="D46">
-        <v>8241.304679961298</v>
+        <v>8448.912432033854</v>
       </c>
       <c r="E46">
         <v>1058.044</v>
@@ -5065,37 +5065,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M46">
-        <v>266.3483245122242</v>
+        <v>255.5002301122242</v>
       </c>
       <c r="N46">
-        <v>730.8516754877758</v>
+        <v>741.6997698877758</v>
       </c>
       <c r="O46">
-        <v>91.35645943597197</v>
+        <v>92.71247123597198</v>
       </c>
       <c r="P46">
-        <v>639.4952160518038</v>
+        <v>648.9872986518038</v>
       </c>
       <c r="Q46">
-        <v>790.5952160518038</v>
+        <v>800.0872986518038</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1088737447387837</v>
+        <v>0.1088442886781502</v>
       </c>
       <c r="T46">
         <v>1.228850530609956</v>
       </c>
       <c r="U46">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V46">
         <v>0.125</v>
       </c>
       <c r="W46">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.743969487422974</v>
+        <v>3.902931905626843</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08560024357219258</v>
+        <v>0.08456001999754198</v>
       </c>
       <c r="C47">
-        <v>5075.152586706252</v>
+        <v>5287.028852838843</v>
       </c>
       <c r="D47">
-        <v>8230.422586706252</v>
+        <v>8442.298852838843</v>
       </c>
       <c r="E47">
         <v>1152.87</v>
@@ -5147,37 +5147,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M47">
-        <v>272.4016955238656</v>
+        <v>261.3070535238656</v>
       </c>
       <c r="N47">
-        <v>724.7983044761343</v>
+        <v>735.8929464761343</v>
       </c>
       <c r="O47">
-        <v>90.59978805951678</v>
+        <v>91.98661830951679</v>
       </c>
       <c r="P47">
-        <v>634.1985164166175</v>
+        <v>643.9063281666175</v>
       </c>
       <c r="Q47">
-        <v>785.2985164166175</v>
+        <v>795.0063281666175</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1099355922933087</v>
+        <v>0.1099056403393985</v>
       </c>
       <c r="T47">
         <v>1.249538249980494</v>
       </c>
       <c r="U47">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V47">
         <v>0.125</v>
       </c>
       <c r="W47">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.660770165480241</v>
+        <v>3.816200085501801</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08565409267559065</v>
+        <v>0.08459114092024422</v>
       </c>
       <c r="C48">
-        <v>4969.47319371136</v>
+        <v>5185.599619405811</v>
       </c>
       <c r="D48">
-        <v>8219.569193711361</v>
+        <v>8435.695619405811</v>
       </c>
       <c r="E48">
         <v>1247.696</v>
@@ -5229,37 +5229,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M48">
-        <v>278.4550665355071</v>
+        <v>267.1138769355071</v>
       </c>
       <c r="N48">
-        <v>718.7449334644929</v>
+        <v>730.0861230644928</v>
       </c>
       <c r="O48">
-        <v>89.84311668306161</v>
+        <v>91.2607653830616</v>
       </c>
       <c r="P48">
-        <v>628.9018167814313</v>
+        <v>638.8253576814311</v>
       </c>
       <c r="Q48">
-        <v>780.0018167814313</v>
+        <v>789.9253576814311</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1110367675350383</v>
+        <v>0.1110063013214338</v>
       </c>
       <c r="T48">
         <v>1.27099218117957</v>
       </c>
       <c r="U48">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V48">
         <v>0.125</v>
       </c>
       <c r="W48">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.581188205361106</v>
+        <v>3.733239214077849</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08570794177898873</v>
+        <v>0.08462226184294647</v>
       </c>
       <c r="C49">
-        <v>4863.822387585731</v>
+        <v>5084.180707477592</v>
       </c>
       <c r="D49">
-        <v>8208.744387585732</v>
+        <v>8429.102707477592</v>
       </c>
       <c r="E49">
         <v>1342.522</v>
@@ -5311,37 +5311,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M49">
-        <v>284.5084375471486</v>
+        <v>272.9207003471486</v>
       </c>
       <c r="N49">
-        <v>712.6915624528514</v>
+        <v>724.2792996528514</v>
       </c>
       <c r="O49">
-        <v>89.08644530660642</v>
+        <v>90.53491245660642</v>
       </c>
       <c r="P49">
-        <v>623.605117146245</v>
+        <v>633.7443871962449</v>
       </c>
       <c r="Q49">
-        <v>774.705117146245</v>
+        <v>784.844387196245</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1121794965594747</v>
+        <v>0.1121484966801497</v>
       </c>
       <c r="T49">
         <v>1.293255694688046</v>
       </c>
       <c r="U49">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V49">
         <v>0.125</v>
       </c>
       <c r="W49">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.504992711630018</v>
+        <v>3.653808592501725</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08576179088238679</v>
+        <v>0.08465338276564871</v>
       </c>
       <c r="C50">
-        <v>4758.200055535018</v>
+        <v>4982.772092872791</v>
       </c>
       <c r="D50">
-        <v>8197.948055535018</v>
+        <v>8422.520092872792</v>
       </c>
       <c r="E50">
         <v>1437.348</v>
@@ -5393,37 +5393,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M50">
-        <v>290.56180855879</v>
+        <v>278.72752375879</v>
       </c>
       <c r="N50">
-        <v>706.63819144121</v>
+        <v>718.47247624121</v>
       </c>
       <c r="O50">
-        <v>88.32977393015125</v>
+        <v>89.80905953015125</v>
       </c>
       <c r="P50">
-        <v>618.3084175110587</v>
+        <v>628.6634167110587</v>
       </c>
       <c r="Q50">
-        <v>769.4084175110587</v>
+        <v>779.7634167110588</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1133661767002355</v>
+        <v>0.1133346226295854</v>
       </c>
       <c r="T50">
         <v>1.316375497177616</v>
       </c>
       <c r="U50">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V50">
         <v>0.125</v>
       </c>
       <c r="W50">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.431972030137727</v>
+        <v>3.577687580157939</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08581563998578487</v>
+        <v>0.08468450368835098</v>
       </c>
       <c r="C51">
-        <v>4652.606085357484</v>
+        <v>4881.373751485484</v>
       </c>
       <c r="D51">
-        <v>8187.180085357484</v>
+        <v>8415.947751485484</v>
       </c>
       <c r="E51">
         <v>1532.174</v>
@@ -5475,37 +5475,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M51">
-        <v>296.6151795704315</v>
+        <v>284.5343471704315</v>
       </c>
       <c r="N51">
-        <v>700.5848204295685</v>
+        <v>712.6656528295684</v>
       </c>
       <c r="O51">
-        <v>87.57310255369606</v>
+        <v>89.08320660369606</v>
       </c>
       <c r="P51">
-        <v>613.0117178758724</v>
+        <v>623.5824462258724</v>
       </c>
       <c r="Q51">
-        <v>764.1117178758724</v>
+        <v>774.6824462258725</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1145993933171047</v>
+        <v>0.1145672633221362</v>
       </c>
       <c r="T51">
         <v>1.340401958588347</v>
       </c>
       <c r="U51">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V51">
         <v>0.125</v>
       </c>
       <c r="W51">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.361931784624712</v>
+        <v>3.504673547909818</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08586948908918295</v>
+        <v>0.08471562461105321</v>
       </c>
       <c r="C52">
-        <v>4547.040365440132</v>
+        <v>4779.985659284949</v>
       </c>
       <c r="D52">
-        <v>8176.440365440132</v>
+        <v>8409.38565928495</v>
       </c>
       <c r="E52">
         <v>1627</v>
@@ -5557,37 +5557,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M52">
-        <v>302.6685505820729</v>
+        <v>290.3411705820729</v>
       </c>
       <c r="N52">
-        <v>694.531449417927</v>
+        <v>706.8588294179269</v>
       </c>
       <c r="O52">
-        <v>86.81643117724087</v>
+        <v>88.35735367724087</v>
       </c>
       <c r="P52">
-        <v>607.715018240686</v>
+        <v>618.501475740686</v>
       </c>
       <c r="Q52">
-        <v>758.8150182406861</v>
+        <v>769.6014757406861</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1158819385986486</v>
+        <v>0.1158492096423891</v>
       </c>
       <c r="T52">
         <v>1.365389478455507</v>
       </c>
       <c r="U52">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V52">
         <v>0.125</v>
       </c>
       <c r="W52">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.294693148932217</v>
+        <v>3.434580076951621</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08592333819258102</v>
+        <v>0.08474674553375547</v>
       </c>
       <c r="C53">
-        <v>4441.502784754839</v>
+        <v>4678.607792315332</v>
       </c>
       <c r="D53">
-        <v>8165.72878475484</v>
+        <v>8402.833792315332</v>
       </c>
       <c r="E53">
         <v>1721.826</v>
@@ -5639,37 +5639,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M53">
-        <v>308.7219215937144</v>
+        <v>296.1479939937144</v>
       </c>
       <c r="N53">
-        <v>688.4780784062855</v>
+        <v>701.0520060062855</v>
       </c>
       <c r="O53">
-        <v>86.05975980078568</v>
+        <v>87.63150075078569</v>
       </c>
       <c r="P53">
-        <v>602.4183186054997</v>
+        <v>613.4205052554998</v>
       </c>
       <c r="Q53">
-        <v>753.5183186054998</v>
+        <v>764.5205052554999</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1172168326671942</v>
+        <v>0.1171834803022442</v>
       </c>
       <c r="T53">
         <v>1.391396897092754</v>
       </c>
       <c r="U53">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V53">
         <v>0.125</v>
       </c>
       <c r="W53">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.230091322482566</v>
+        <v>3.367235369560413</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08597718729597909</v>
+        <v>0.08477786645645771</v>
       </c>
       <c r="C54">
-        <v>4335.993232854536</v>
+        <v>4577.240126695396</v>
       </c>
       <c r="D54">
-        <v>8155.045232854536</v>
+        <v>8396.292126695396</v>
       </c>
       <c r="E54">
         <v>1816.652</v>
@@ -5721,37 +5721,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M54">
-        <v>314.7752926053558</v>
+        <v>301.9548174053559</v>
       </c>
       <c r="N54">
-        <v>682.4247073946441</v>
+        <v>695.2451825946441</v>
       </c>
       <c r="O54">
-        <v>85.30308842433051</v>
+        <v>86.90564782433052</v>
       </c>
       <c r="P54">
-        <v>597.1216189703135</v>
+        <v>608.3395347703135</v>
       </c>
       <c r="Q54">
-        <v>748.2216189703136</v>
+        <v>759.4395347703136</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1186073473219293</v>
+        <v>0.1185733455729265</v>
       </c>
       <c r="T54">
         <v>1.418487958173221</v>
       </c>
       <c r="U54">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V54">
         <v>0.125</v>
       </c>
       <c r="W54">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.167974181665593</v>
+        <v>3.302480843222713</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08603103639937716</v>
+        <v>0.08480898737915996</v>
       </c>
       <c r="C55">
-        <v>4230.5115998694</v>
+        <v>4475.882638618201</v>
       </c>
       <c r="D55">
-        <v>8144.389599869401</v>
+        <v>8389.760638618201</v>
       </c>
       <c r="E55">
         <v>1911.478</v>
@@ -5803,37 +5803,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M55">
-        <v>320.8286636169973</v>
+        <v>307.7616408169973</v>
       </c>
       <c r="N55">
-        <v>676.3713363830027</v>
+        <v>689.4383591830026</v>
       </c>
       <c r="O55">
-        <v>84.54641704787534</v>
+        <v>86.17979489787533</v>
       </c>
       <c r="P55">
-        <v>591.8249193351273</v>
+        <v>603.2585642851272</v>
       </c>
       <c r="Q55">
-        <v>742.9249193351274</v>
+        <v>754.3585642851273</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1200570328130361</v>
+        <v>0.1200223540466165</v>
       </c>
       <c r="T55">
         <v>1.446731830363494</v>
       </c>
       <c r="U55">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V55">
         <v>0.125</v>
       </c>
       <c r="W55">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.108201083898318</v>
+        <v>3.240169883916624</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08608488550277524</v>
+        <v>0.08484010830186221</v>
       </c>
       <c r="C56">
-        <v>4125.057776503102</v>
+        <v>4374.535304350832</v>
       </c>
       <c r="D56">
-        <v>8133.761776503103</v>
+        <v>8383.239304350833</v>
       </c>
       <c r="E56">
         <v>2006.304</v>
@@ -5885,37 +5885,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M56">
-        <v>326.8820346286387</v>
+        <v>313.5684642286388</v>
       </c>
       <c r="N56">
-        <v>670.3179653713612</v>
+        <v>683.6315357713611</v>
       </c>
       <c r="O56">
-        <v>83.78974567142015</v>
+        <v>85.45394197142014</v>
       </c>
       <c r="P56">
-        <v>586.528219699941</v>
+        <v>598.177593799941</v>
       </c>
       <c r="Q56">
-        <v>737.628219699941</v>
+        <v>749.277593799941</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1215697481081041</v>
+        <v>0.1215343628887279</v>
       </c>
       <c r="T56">
         <v>1.476203696996823</v>
       </c>
       <c r="U56">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V56">
         <v>0.125</v>
       </c>
       <c r="W56">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.050641804566868</v>
+        <v>3.180166737918168</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08738998460617331</v>
+        <v>0.08487122922456444</v>
       </c>
       <c r="C57">
-        <v>3780.875806158492</v>
+        <v>4273.198100234118</v>
       </c>
       <c r="D57">
-        <v>7884.405806158492</v>
+        <v>8376.728100234119</v>
       </c>
       <c r="E57">
         <v>2101.13</v>
@@ -5967,45 +5967,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M57">
-        <v>346.4955236402802</v>
+        <v>319.3752876402802</v>
       </c>
       <c r="N57">
-        <v>650.7044763597198</v>
+        <v>677.8247123597197</v>
       </c>
       <c r="O57">
-        <v>81.33805954496498</v>
+        <v>84.72808904496496</v>
       </c>
       <c r="P57">
-        <v>569.3664168147549</v>
+        <v>593.0966233147548</v>
       </c>
       <c r="Q57">
-        <v>720.4664168147549</v>
+        <v>744.1966233147548</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.123149695194064</v>
+        <v>0.123113572123822</v>
       </c>
       <c r="T57">
         <v>1.506985424369411</v>
       </c>
       <c r="U57">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V57">
         <v>0.125</v>
       </c>
       <c r="W57">
-        <v>0.05813203957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.877959257664925</v>
+        <v>3.122345524501474</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08746658370957139</v>
+        <v>0.0849023501472667</v>
       </c>
       <c r="C58">
-        <v>3671.888713851205</v>
+        <v>4171.871002682306</v>
       </c>
       <c r="D58">
-        <v>7870.244713851205</v>
+        <v>8370.227002682306</v>
       </c>
       <c r="E58">
         <v>2195.956</v>
@@ -6049,45 +6049,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M58">
-        <v>352.7954422519217</v>
+        <v>325.1821110519217</v>
       </c>
       <c r="N58">
-        <v>644.4045577480783</v>
+        <v>672.0178889480783</v>
       </c>
       <c r="O58">
-        <v>80.55056971850979</v>
+        <v>84.00223611850979</v>
       </c>
       <c r="P58">
-        <v>563.8539880295685</v>
+        <v>588.0156528295685</v>
       </c>
       <c r="Q58">
-        <v>714.9539880295686</v>
+        <v>739.1156528295685</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1248014580566584</v>
+        <v>0.124764563596875</v>
       </c>
       <c r="T58">
         <v>1.539166321168026</v>
       </c>
       <c r="U58">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V58">
         <v>0.125</v>
       </c>
       <c r="W58">
-        <v>0.05813203957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.826567128063765</v>
+        <v>3.066589354421091</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08754318281296947</v>
+        <v>0.08493347106996894</v>
       </c>
       <c r="C59">
-        <v>3562.952399498427</v>
+        <v>4070.553988182834</v>
       </c>
       <c r="D59">
-        <v>7856.134399498428</v>
+        <v>8363.735988182836</v>
       </c>
       <c r="E59">
         <v>2290.782000000001</v>
@@ -6131,45 +6131,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M59">
-        <v>359.0953608635631</v>
+        <v>330.9889344635632</v>
       </c>
       <c r="N59">
-        <v>638.1046391364368</v>
+        <v>666.2110655364368</v>
       </c>
       <c r="O59">
-        <v>79.76307989205461</v>
+        <v>83.2763831920546</v>
       </c>
       <c r="P59">
-        <v>558.3415592443822</v>
+        <v>582.9346823443822</v>
       </c>
       <c r="Q59">
-        <v>709.4415592443822</v>
+        <v>734.0346823443822</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1265300470989083</v>
+        <v>0.1264923453710002</v>
       </c>
       <c r="T59">
         <v>1.57284400386425</v>
       </c>
       <c r="U59">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V59">
         <v>0.125</v>
       </c>
       <c r="W59">
-        <v>0.05813203957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.77697823108019</v>
+        <v>3.012789541185632</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.08761978191636752</v>
+        <v>0.08623334199267119</v>
       </c>
       <c r="C60">
-        <v>3454.066590474355</v>
+        <v>3713.318670713872</v>
       </c>
       <c r="D60">
-        <v>7842.074590474354</v>
+        <v>8101.326670713871</v>
       </c>
       <c r="E60">
         <v>2385.607999999999</v>
@@ -6213,37 +6213,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M60">
-        <v>365.3952794752045</v>
+        <v>350.5455278752045</v>
       </c>
       <c r="N60">
-        <v>631.8047205247955</v>
+        <v>646.6544721247953</v>
       </c>
       <c r="O60">
-        <v>78.97559006559943</v>
+        <v>80.83180901559942</v>
       </c>
       <c r="P60">
-        <v>552.829130459196</v>
+        <v>565.8226631091959</v>
       </c>
       <c r="Q60">
-        <v>703.929130459196</v>
+        <v>716.9226631091959</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1283409499050749</v>
+        <v>0.1283024024677027</v>
       </c>
       <c r="T60">
         <v>1.608125385736485</v>
       </c>
       <c r="U60">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V60">
         <v>0.125</v>
       </c>
       <c r="W60">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.729099296061567</v>
+        <v>2.844708948490727</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.0876963810197656</v>
+        <v>0.08628633791537343</v>
       </c>
       <c r="C61">
-        <v>3345.231016101306</v>
+        <v>3608.143104733864</v>
       </c>
       <c r="D61">
-        <v>7828.065016101305</v>
+        <v>8090.977104733864</v>
       </c>
       <c r="E61">
         <v>2480.433999999999</v>
@@ -6295,37 +6295,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M61">
-        <v>371.6951980868459</v>
+        <v>356.589416286846</v>
       </c>
       <c r="N61">
-        <v>625.504801913154</v>
+        <v>640.610583713154</v>
       </c>
       <c r="O61">
-        <v>78.18810023914425</v>
+        <v>80.07632296414425</v>
       </c>
       <c r="P61">
-        <v>547.3167016740098</v>
+        <v>560.5342607490097</v>
       </c>
       <c r="Q61">
-        <v>698.4167016740098</v>
+        <v>711.6342607490097</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1302401894334936</v>
+        <v>0.1302007550325371</v>
       </c>
       <c r="T61">
         <v>1.645127810626878</v>
       </c>
       <c r="U61">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V61">
         <v>0.125</v>
       </c>
       <c r="W61">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.682843375789337</v>
+        <v>2.796493542584105</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.08777298012316369</v>
+        <v>0.08633933383807568</v>
       </c>
       <c r="C62">
-        <v>3236.445407632383</v>
+        <v>3502.993948465696</v>
       </c>
       <c r="D62">
-        <v>7814.105407632383</v>
+        <v>8080.653948465697</v>
       </c>
       <c r="E62">
         <v>2575.26</v>
@@ -6377,37 +6377,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M62">
-        <v>377.9951166984875</v>
+        <v>362.6333046984875</v>
       </c>
       <c r="N62">
-        <v>619.2048833015124</v>
+        <v>634.5666953015125</v>
       </c>
       <c r="O62">
-        <v>77.40061041268905</v>
+        <v>79.32083691268906</v>
       </c>
       <c r="P62">
-        <v>541.8042728888233</v>
+        <v>555.2458583888234</v>
       </c>
       <c r="Q62">
-        <v>692.9042728888234</v>
+        <v>706.3458583888234</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1322343909383332</v>
+        <v>0.1321940252256132</v>
       </c>
       <c r="T62">
         <v>1.683980356761791</v>
       </c>
       <c r="U62">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V62">
         <v>0.125</v>
       </c>
       <c r="W62">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.63812931952618</v>
+        <v>2.749885316874369</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.08784957922656175</v>
+        <v>0.08639232976077793</v>
       </c>
       <c r="C63">
-        <v>3127.709498234288</v>
+        <v>3397.871100950915</v>
       </c>
       <c r="D63">
-        <v>7800.195498234289</v>
+        <v>8070.357100950915</v>
       </c>
       <c r="E63">
         <v>2670.086</v>
@@ -6459,37 +6459,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M63">
-        <v>384.2950353101289</v>
+        <v>368.6771931101289</v>
       </c>
       <c r="N63">
-        <v>612.904964689871</v>
+        <v>628.5228068898709</v>
       </c>
       <c r="O63">
-        <v>76.61312058623388</v>
+        <v>78.56535086123387</v>
       </c>
       <c r="P63">
-        <v>536.2918441036371</v>
+        <v>549.9574560286371</v>
       </c>
       <c r="Q63">
-        <v>687.3918441036371</v>
+        <v>701.0574560286371</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1343308591870107</v>
+        <v>0.1342895144029496</v>
       </c>
       <c r="T63">
         <v>1.724825341160033</v>
       </c>
       <c r="U63">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V63">
         <v>0.125</v>
       </c>
       <c r="W63">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.594881297894604</v>
+        <v>2.704805229712494</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.08792617832995983</v>
+        <v>0.08644532568348018</v>
       </c>
       <c r="C64">
-        <v>3019.023022970293</v>
+        <v>3292.774461745</v>
       </c>
       <c r="D64">
-        <v>7786.335022970293</v>
+        <v>8060.086461745001</v>
       </c>
       <c r="E64">
         <v>2764.912</v>
@@ -6541,37 +6541,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M64">
-        <v>390.5949539217704</v>
+        <v>374.7210815217704</v>
       </c>
       <c r="N64">
-        <v>606.6050460782295</v>
+        <v>622.4789184782295</v>
       </c>
       <c r="O64">
-        <v>75.82563075977869</v>
+        <v>77.80986480977869</v>
       </c>
       <c r="P64">
-        <v>530.7794153184508</v>
+        <v>544.6690536684508</v>
       </c>
       <c r="Q64">
-        <v>681.8794153184508</v>
+        <v>695.7690536684509</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1365376678698292</v>
+        <v>0.1364952924843564</v>
       </c>
       <c r="T64">
         <v>1.767820061579235</v>
       </c>
       <c r="U64">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V64">
         <v>0.125</v>
       </c>
       <c r="W64">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.553028373735013</v>
+        <v>2.66117933891068</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.08800277743335791</v>
+        <v>0.08649832160618243</v>
       </c>
       <c r="C65">
-        <v>2910.385718783442</v>
+        <v>3187.7039309141</v>
       </c>
       <c r="D65">
-        <v>7772.523718783443</v>
+        <v>8049.8419309141</v>
       </c>
       <c r="E65">
         <v>2859.738</v>
@@ -6623,37 +6623,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M65">
-        <v>396.8948725334118</v>
+        <v>380.7649699334119</v>
       </c>
       <c r="N65">
-        <v>600.3051274665881</v>
+        <v>616.4350300665881</v>
       </c>
       <c r="O65">
-        <v>75.03814093332352</v>
+        <v>77.05437875832351</v>
       </c>
       <c r="P65">
-        <v>525.2669865332646</v>
+        <v>539.3806513082645</v>
       </c>
       <c r="Q65">
-        <v>676.3669865332646</v>
+        <v>690.4806513082646</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1388637635084757</v>
+        <v>0.1388203018134068</v>
       </c>
       <c r="T65">
         <v>1.813138820940015</v>
       </c>
       <c r="U65">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V65">
         <v>0.125</v>
       </c>
       <c r="W65">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.512504113834458</v>
+        <v>2.618938397023209</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.08959137653675597</v>
+        <v>0.08655131752888467</v>
       </c>
       <c r="C66">
-        <v>2539.778415193713</v>
+        <v>3082.659409031791</v>
       </c>
       <c r="D66">
-        <v>7496.742415193714</v>
+        <v>8039.623409031791</v>
       </c>
       <c r="E66">
         <v>2954.564</v>
@@ -6705,45 +6705,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M66">
-        <v>419.5807239450534</v>
+        <v>386.8088583450534</v>
       </c>
       <c r="N66">
-        <v>577.6192760549466</v>
+        <v>610.3911416549465</v>
       </c>
       <c r="O66">
-        <v>72.20240950686832</v>
+        <v>76.29889270686832</v>
       </c>
       <c r="P66">
-        <v>505.4168665480782</v>
+        <v>534.0922489480782</v>
       </c>
       <c r="Q66">
-        <v>656.5168665480783</v>
+        <v>685.1922489480783</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1413190866826025</v>
+        <v>0.1412744783274044</v>
       </c>
       <c r="T66">
         <v>1.860975289154172</v>
       </c>
       <c r="U66">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V66">
         <v>0.125</v>
       </c>
       <c r="W66">
-        <v>0.06049453957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.376658275966437</v>
+        <v>2.578017484569721</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.08969160064015405</v>
+        <v>0.08660431345158692</v>
       </c>
       <c r="C67">
-        <v>2428.208302816158</v>
+        <v>2977.640797175856</v>
       </c>
       <c r="D67">
-        <v>7479.998302816159</v>
+        <v>8029.430797175856</v>
       </c>
       <c r="E67">
         <v>3049.39</v>
@@ -6787,45 +6787,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M67">
-        <v>426.1366727566948</v>
+        <v>392.8527467566948</v>
       </c>
       <c r="N67">
-        <v>571.0633272433051</v>
+        <v>604.3472532433052</v>
       </c>
       <c r="O67">
-        <v>71.38291590541314</v>
+        <v>75.54340665541315</v>
       </c>
       <c r="P67">
-        <v>499.680411337892</v>
+        <v>528.8038465878921</v>
       </c>
       <c r="Q67">
-        <v>650.780411337892</v>
+        <v>679.9038465878921</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.143914714038108</v>
+        <v>0.1438688934993448</v>
       </c>
       <c r="T67">
         <v>1.911545269837709</v>
       </c>
       <c r="U67">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V67">
         <v>0.125</v>
       </c>
       <c r="W67">
-        <v>0.06049453957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.34009430249003</v>
+        <v>2.538355677114803</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.08979182474355213</v>
+        <v>0.08867855937428917</v>
       </c>
       <c r="C68">
-        <v>2316.712820318696</v>
+        <v>2503.220465761279</v>
       </c>
       <c r="D68">
-        <v>7463.328820318696</v>
+        <v>7649.836465761279</v>
       </c>
       <c r="E68">
         <v>3144.216</v>
@@ -6869,37 +6869,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M68">
-        <v>432.6926215683363</v>
+        <v>420.8014411683363</v>
       </c>
       <c r="N68">
-        <v>564.5073784316637</v>
+        <v>576.3985588316636</v>
       </c>
       <c r="O68">
-        <v>70.56342230395796</v>
+        <v>72.04981985395796</v>
       </c>
       <c r="P68">
-        <v>493.9439561277057</v>
+        <v>504.3487389777057</v>
       </c>
       <c r="Q68">
-        <v>645.0439561277058</v>
+        <v>655.4487389777057</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.146663025355702</v>
+        <v>0.146615921328458</v>
       </c>
       <c r="T68">
         <v>1.965089955267337</v>
       </c>
       <c r="U68">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V68">
         <v>0.125</v>
       </c>
       <c r="W68">
-        <v>0.06049453957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.304638328209878</v>
+        <v>2.369763747080616</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.08989204884695021</v>
+        <v>0.08876218029699143</v>
       </c>
       <c r="C69">
-        <v>2205.291469863545</v>
+        <v>2393.842726441202</v>
       </c>
       <c r="D69">
-        <v>7446.733469863545</v>
+        <v>7635.284726441203</v>
       </c>
       <c r="E69">
         <v>3239.042</v>
@@ -6951,37 +6951,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M69">
-        <v>439.2485703799777</v>
+        <v>427.1772205799778</v>
       </c>
       <c r="N69">
-        <v>557.9514296200223</v>
+        <v>570.0227794200222</v>
       </c>
       <c r="O69">
-        <v>69.74392870250279</v>
+        <v>71.25284742750277</v>
       </c>
       <c r="P69">
-        <v>488.2075009175195</v>
+        <v>498.7699319925194</v>
       </c>
       <c r="Q69">
-        <v>639.3075009175195</v>
+        <v>649.8699319925194</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1495779009955745</v>
+        <v>0.1495294356926691</v>
       </c>
       <c r="T69">
         <v>2.021879773147245</v>
       </c>
       <c r="U69">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V69">
         <v>0.125</v>
       </c>
       <c r="W69">
-        <v>0.06049453957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.270240741221671</v>
+        <v>2.334394138915234</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.09278877295034829</v>
+        <v>0.08884580121969368</v>
       </c>
       <c r="C70">
-        <v>1660.785055771067</v>
+        <v>2284.520243486429</v>
       </c>
       <c r="D70">
-        <v>6997.053055771068</v>
+        <v>7620.788243486429</v>
       </c>
       <c r="E70">
         <v>3333.868</v>
@@ -7033,45 +7033,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M70">
-        <v>476.1109087916192</v>
+        <v>433.5529999916192</v>
       </c>
       <c r="N70">
-        <v>521.0890912083808</v>
+        <v>563.6470000083807</v>
       </c>
       <c r="O70">
-        <v>65.13613640104759</v>
+        <v>70.45587500104759</v>
       </c>
       <c r="P70">
-        <v>455.9529548073332</v>
+        <v>493.1911250073331</v>
       </c>
       <c r="Q70">
-        <v>607.0529548073332</v>
+        <v>644.2911250073331</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1526749563629391</v>
+        <v>0.1526250447046434</v>
       </c>
       <c r="T70">
         <v>2.082218954644648</v>
       </c>
       <c r="U70">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V70">
         <v>0.125</v>
       </c>
       <c r="W70">
-        <v>0.06460703957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.094469968207444</v>
+        <v>2.300064813342951</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09293012205374634</v>
+        <v>0.08892942214239591</v>
       </c>
       <c r="C71">
-        <v>1545.40197533788</v>
+        <v>2175.252702761327</v>
       </c>
       <c r="D71">
-        <v>6976.495975337881</v>
+        <v>7606.346702761327</v>
       </c>
       <c r="E71">
         <v>3428.694</v>
@@ -7115,45 +7115,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M71">
-        <v>483.1125398032607</v>
+        <v>439.9287794032606</v>
       </c>
       <c r="N71">
-        <v>514.0874601967392</v>
+        <v>557.2712205967393</v>
       </c>
       <c r="O71">
-        <v>64.26093252459241</v>
+        <v>69.65890257459242</v>
       </c>
       <c r="P71">
-        <v>449.8265276721468</v>
+        <v>487.612318022147</v>
       </c>
       <c r="Q71">
-        <v>600.9265276721468</v>
+        <v>638.712318022147</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1559718217540045</v>
+        <v>0.1559203704270676</v>
       </c>
       <c r="T71">
         <v>2.146450986561237</v>
       </c>
       <c r="U71">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V71">
         <v>0.125</v>
       </c>
       <c r="W71">
-        <v>0.06460703957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.064115330987046</v>
+        <v>2.266730540685807</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09307147115714443</v>
+        <v>0.09072804306509816</v>
       </c>
       <c r="C72">
-        <v>1430.139332930664</v>
+        <v>1782.531380984255</v>
       </c>
       <c r="D72">
-        <v>6956.059332930665</v>
+        <v>7308.451380984255</v>
       </c>
       <c r="E72">
         <v>3523.52</v>
@@ -7197,37 +7197,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M72">
-        <v>490.1141708149022</v>
+        <v>464.8904548149021</v>
       </c>
       <c r="N72">
-        <v>507.0858291850977</v>
+        <v>532.3095451850978</v>
       </c>
       <c r="O72">
-        <v>63.38572864813722</v>
+        <v>66.53869314813723</v>
       </c>
       <c r="P72">
-        <v>443.7001005369605</v>
+        <v>465.7708520369606</v>
       </c>
       <c r="Q72">
-        <v>594.8001005369605</v>
+        <v>616.8708520369606</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.159488478171141</v>
+        <v>0.1594353845309868</v>
       </c>
       <c r="T72">
         <v>2.214965153938933</v>
       </c>
       <c r="U72">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V72">
         <v>0.125</v>
       </c>
       <c r="W72">
-        <v>0.06460703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.034627969115802</v>
+        <v>2.145021455424459</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.09321282026054251</v>
+        <v>0.09083616398780041</v>
       </c>
       <c r="C73">
-        <v>1314.996073223184</v>
+        <v>1670.539670544956</v>
       </c>
       <c r="D73">
-        <v>6935.742073223183</v>
+        <v>7291.285670544956</v>
       </c>
       <c r="E73">
         <v>3618.346</v>
@@ -7279,37 +7279,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M73">
-        <v>497.1158018265436</v>
+        <v>471.5317470265435</v>
       </c>
       <c r="N73">
-        <v>500.0841981734563</v>
+        <v>525.6682529734564</v>
       </c>
       <c r="O73">
-        <v>62.51052477168204</v>
+        <v>65.70853162168206</v>
       </c>
       <c r="P73">
-        <v>437.5736734017743</v>
+        <v>459.9597213517744</v>
       </c>
       <c r="Q73">
-        <v>588.6736734017743</v>
+        <v>611.0597213517744</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1632476626170455</v>
+        <v>0.1631928134006934</v>
       </c>
       <c r="T73">
         <v>2.288204436308193</v>
       </c>
       <c r="U73">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V73">
         <v>0.125</v>
       </c>
       <c r="W73">
-        <v>0.06460703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.005971237156425</v>
+        <v>2.114809885629748</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.09921316936394058</v>
+        <v>0.09094428491050266</v>
       </c>
       <c r="C74">
-        <v>455.0740403837954</v>
+        <v>1558.628407011687</v>
       </c>
       <c r="D74">
-        <v>6170.646040383795</v>
+        <v>7274.200407011687</v>
       </c>
       <c r="E74">
         <v>3713.172</v>
@@ -7361,45 +7361,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M74">
-        <v>567.6129224381849</v>
+        <v>478.173039238185</v>
       </c>
       <c r="N74">
-        <v>429.587077561815</v>
+        <v>519.026960761815</v>
       </c>
       <c r="O74">
-        <v>53.69838469522688</v>
+        <v>64.87837009522687</v>
       </c>
       <c r="P74">
-        <v>375.8886928665881</v>
+        <v>454.1485906665881</v>
       </c>
       <c r="Q74">
-        <v>526.9886928665882</v>
+        <v>605.2485906665881</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1672753602376575</v>
+        <v>0.1672186300468078</v>
       </c>
       <c r="T74">
         <v>2.366675095989545</v>
       </c>
       <c r="U74">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V74">
         <v>0.125</v>
       </c>
       <c r="W74">
-        <v>0.07274453957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y74">
-        <v>1.756831038512162</v>
+        <v>2.085437526107113</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1024380184673387</v>
+        <v>0.09105240583320491</v>
       </c>
       <c r="C75">
-        <v>14.88720324084625</v>
+        <v>1446.797026186244</v>
       </c>
       <c r="D75">
-        <v>5825.285203240845</v>
+        <v>7257.195026186244</v>
       </c>
       <c r="E75">
         <v>3807.998</v>
@@ -7443,45 +7443,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M75">
-        <v>608.0312358498264</v>
+        <v>484.8143314498264</v>
       </c>
       <c r="N75">
-        <v>389.1687641501735</v>
+        <v>512.3856685501735</v>
       </c>
       <c r="O75">
-        <v>48.64609551877169</v>
+        <v>64.04820856877168</v>
       </c>
       <c r="P75">
-        <v>340.5226686314018</v>
+        <v>448.3374599814018</v>
       </c>
       <c r="Q75">
-        <v>491.6226686314018</v>
+        <v>599.4374599814018</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1716014058301667</v>
+        <v>0.171542655333375</v>
       </c>
       <c r="T75">
         <v>2.450958397128773</v>
       </c>
       <c r="U75">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V75">
         <v>0.125</v>
       </c>
       <c r="W75">
-        <v>0.07685703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.64004732192129</v>
+        <v>2.05686988876318</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1027018675707367</v>
+        <v>0.09116052675590716</v>
       </c>
       <c r="C76">
-        <v>-106.4922918776374</v>
+        <v>1335.044969133971</v>
       </c>
       <c r="D76">
-        <v>5798.731708122362</v>
+        <v>7240.26896913397</v>
       </c>
       <c r="E76">
         <v>3902.824</v>
@@ -7525,45 +7525,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M76">
-        <v>616.3604308614679</v>
+        <v>491.4556236614679</v>
       </c>
       <c r="N76">
-        <v>380.8395691385321</v>
+        <v>505.744376338532</v>
       </c>
       <c r="O76">
-        <v>47.60494614231651</v>
+        <v>63.21804704231651</v>
       </c>
       <c r="P76">
-        <v>333.2346229962155</v>
+        <v>442.5263292962155</v>
       </c>
       <c r="Q76">
-        <v>484.3346229962156</v>
+        <v>593.6263292962155</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1762602241605611</v>
+        <v>0.1761992979496782</v>
       </c>
       <c r="T76">
         <v>2.541725029124866</v>
       </c>
       <c r="U76">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V76">
         <v>0.125</v>
       </c>
       <c r="W76">
-        <v>0.07685703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.617884520273705</v>
+        <v>2.02907434972584</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1029657166741348</v>
+        <v>0.0912686476786094</v>
       </c>
       <c r="C77">
-        <v>-227.6308069762163</v>
+        <v>1223.371682122519</v>
       </c>
       <c r="D77">
-        <v>5772.419193023784</v>
+        <v>7223.421682122519</v>
       </c>
       <c r="E77">
         <v>3997.650000000001</v>
@@ -7607,45 +7607,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M77">
-        <v>624.6896258731094</v>
+        <v>498.0969158731094</v>
       </c>
       <c r="N77">
-        <v>372.5103741268905</v>
+        <v>499.1030841268906</v>
       </c>
       <c r="O77">
-        <v>46.56379676586131</v>
+        <v>62.38788551586132</v>
       </c>
       <c r="P77">
-        <v>325.9465773610292</v>
+        <v>436.7151986110292</v>
       </c>
       <c r="Q77">
-        <v>477.0465773610292</v>
+        <v>587.8151986110292</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1812917479573872</v>
+        <v>0.1812284719752856</v>
       </c>
       <c r="T77">
         <v>2.639752991680646</v>
       </c>
       <c r="U77">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V77">
         <v>0.125</v>
       </c>
       <c r="W77">
-        <v>0.07685703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.596312726670055</v>
+        <v>2.002020025062828</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1032295657775329</v>
+        <v>0.09656376860131165</v>
       </c>
       <c r="C78">
-        <v>-348.5316076732297</v>
+        <v>389.5942187046176</v>
       </c>
       <c r="D78">
-        <v>5746.344392326771</v>
+        <v>6484.470218704619</v>
       </c>
       <c r="E78">
         <v>4092.476000000001</v>
@@ -7689,45 +7689,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M78">
-        <v>633.0188208847509</v>
+        <v>560.951060884751</v>
       </c>
       <c r="N78">
-        <v>364.1811791152491</v>
+        <v>436.248939115249</v>
       </c>
       <c r="O78">
-        <v>45.52264738940613</v>
+        <v>54.53111738940612</v>
       </c>
       <c r="P78">
-        <v>318.6585317258429</v>
+        <v>381.7178217258428</v>
       </c>
       <c r="Q78">
-        <v>469.7585317258429</v>
+        <v>532.8178217258428</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1867425654039488</v>
+        <v>0.1866767438363603</v>
       </c>
       <c r="T78">
         <v>2.745949951116074</v>
       </c>
       <c r="U78">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V78">
         <v>0.125</v>
       </c>
       <c r="W78">
-        <v>0.07685703957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.575308611845449</v>
+        <v>1.777695185079394</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1034934148809309</v>
+        <v>0.09674013952401389</v>
       </c>
       <c r="C79">
-        <v>-469.1979008473827</v>
+        <v>272.7480193223728</v>
       </c>
       <c r="D79">
-        <v>5720.504099152618</v>
+        <v>6462.450019322374</v>
       </c>
       <c r="E79">
         <v>4187.302000000001</v>
@@ -7771,45 +7771,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M79">
-        <v>641.3480158963923</v>
+        <v>568.3319958963924</v>
       </c>
       <c r="N79">
-        <v>355.8519841036076</v>
+        <v>428.8680041036075</v>
       </c>
       <c r="O79">
-        <v>44.48149801295095</v>
+        <v>53.60850051295094</v>
       </c>
       <c r="P79">
-        <v>311.3704860906566</v>
+        <v>375.2595035906565</v>
       </c>
       <c r="Q79">
-        <v>462.4704860906567</v>
+        <v>526.3595035906566</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1926673669762983</v>
+        <v>0.1925987784679632</v>
       </c>
       <c r="T79">
         <v>2.861381428763279</v>
       </c>
       <c r="U79">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V79">
         <v>0.125</v>
       </c>
       <c r="W79">
-        <v>0.07685703957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.554850058444859</v>
+        <v>1.754608234623818</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.103757263984329</v>
+        <v>0.09957826044671614</v>
       </c>
       <c r="C80">
-        <v>-589.6328359525533</v>
+        <v>-156.921226329524</v>
       </c>
       <c r="D80">
-        <v>5694.895164047448</v>
+        <v>6127.606773670477</v>
       </c>
       <c r="E80">
         <v>4282.128000000001</v>
@@ -7853,37 +7853,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M80">
-        <v>649.6772109080338</v>
+        <v>604.5590001080338</v>
       </c>
       <c r="N80">
-        <v>347.5227890919662</v>
+        <v>392.6409998919661</v>
       </c>
       <c r="O80">
-        <v>43.44034863649577</v>
+        <v>49.08012498649576</v>
       </c>
       <c r="P80">
-        <v>304.0824404554704</v>
+        <v>343.5608749054703</v>
       </c>
       <c r="Q80">
-        <v>455.1824404554704</v>
+        <v>494.6608749054703</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1991307868734069</v>
+        <v>0.1990591798842574</v>
       </c>
       <c r="T80">
         <v>2.987306677105684</v>
       </c>
       <c r="U80">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V80">
         <v>0.125</v>
       </c>
       <c r="W80">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.534916083336592</v>
+        <v>1.649466801125782</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1040211130877271</v>
+        <v>0.09978875636941839</v>
       </c>
       <c r="C81">
-        <v>-709.8395062974196</v>
+        <v>-275.2047563970045</v>
       </c>
       <c r="D81">
-        <v>5669.514493702582</v>
+        <v>6104.149243602997</v>
       </c>
       <c r="E81">
         <v>4376.954000000001</v>
@@ -7935,37 +7935,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M81">
-        <v>658.0064059196752</v>
+        <v>612.3097565196753</v>
       </c>
       <c r="N81">
-        <v>339.1935940803247</v>
+        <v>384.8902434803247</v>
       </c>
       <c r="O81">
-        <v>42.39919926004059</v>
+        <v>48.11128043504058</v>
       </c>
       <c r="P81">
-        <v>296.7943948202841</v>
+        <v>336.7789630452841</v>
       </c>
       <c r="Q81">
-        <v>447.8943948202841</v>
+        <v>487.8789630452841</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2062097705702401</v>
+        <v>0.2061348576259129</v>
       </c>
       <c r="T81">
         <v>3.125224806242604</v>
       </c>
       <c r="U81">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V81">
         <v>0.125</v>
       </c>
       <c r="W81">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.515486765826002</v>
+        <v>1.628587474529253</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1156949621911252</v>
+        <v>0.09999925229212064</v>
       </c>
       <c r="C82">
-        <v>-1738.478885703215</v>
+        <v>-393.3093724783184</v>
       </c>
       <c r="D82">
-        <v>4735.701114296786</v>
+        <v>6080.870627521682</v>
       </c>
       <c r="E82">
         <v>4471.780000000001</v>
@@ -8017,45 +8017,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M82">
-        <v>789.9887049313168</v>
+        <v>620.0605129313167</v>
       </c>
       <c r="N82">
-        <v>207.2112950686832</v>
+        <v>377.1394870686833</v>
       </c>
       <c r="O82">
-        <v>25.9014118835854</v>
+        <v>47.14243588358541</v>
       </c>
       <c r="P82">
-        <v>181.3098831850978</v>
+        <v>329.9970511850979</v>
       </c>
       <c r="Q82">
-        <v>332.4098831850978</v>
+        <v>481.0970511850978</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2139966526367565</v>
+        <v>0.2139181031417339</v>
       </c>
       <c r="T82">
         <v>3.276934748293216</v>
       </c>
       <c r="U82">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V82">
         <v>0.125</v>
       </c>
       <c r="W82">
-        <v>0.09111953957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y82">
-        <v>1.262296528767077</v>
+        <v>1.608230131097638</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1401809616971741</v>
+        <v>0.1002097482148229</v>
       </c>
       <c r="C83">
-        <v>-3049.284479640744</v>
+        <v>-511.2371137015125</v>
       </c>
       <c r="D83">
-        <v>3519.721520359256</v>
+        <v>6057.768886298488</v>
       </c>
       <c r="E83">
         <v>4566.606000000001</v>
@@ -8099,45 +8099,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M83">
-        <v>1051.029189942958</v>
+        <v>627.8112693429582</v>
       </c>
       <c r="N83">
-        <v>-53.82918994295835</v>
+        <v>369.3887306570417</v>
       </c>
       <c r="O83">
-        <v>-6.728648742869794</v>
+        <v>46.17359133213021</v>
       </c>
       <c r="P83">
-        <v>-47.10054120008856</v>
+        <v>323.2151393249115</v>
       </c>
       <c r="Q83">
-        <v>103.9994587999114</v>
+        <v>474.3151393249115</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2236233219662523</v>
+        <v>0.2225206376592203</v>
       </c>
       <c r="T83">
-        <v>3.464488821109878</v>
+        <v>3.444614157928103</v>
       </c>
       <c r="U83">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V83">
-        <v>0.1185980381827122</v>
+        <v>0.125</v>
       </c>
       <c r="W83">
-        <v>0.1206080623747977</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.9487843054616972</v>
+        <v>1.588375438121123</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1410913278637994</v>
+        <v>0.1004202441375251</v>
       </c>
       <c r="C84">
-        <v>-3177.393466044788</v>
+        <v>-628.989988324628</v>
       </c>
       <c r="D84">
-        <v>3486.438533955213</v>
+        <v>6034.842011675372</v>
       </c>
       <c r="E84">
         <v>4661.432000000001</v>
@@ -8181,45 +8181,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M84">
-        <v>1064.0048589546</v>
+        <v>635.5620257545996</v>
       </c>
       <c r="N84">
-        <v>-66.80485895459981</v>
+        <v>361.6379742454003</v>
       </c>
       <c r="O84">
-        <v>-8.350607369324976</v>
+        <v>45.20474678067504</v>
       </c>
       <c r="P84">
-        <v>-58.45425158527483</v>
+        <v>316.4332274647253</v>
       </c>
       <c r="Q84">
-        <v>92.64574841472516</v>
+        <v>467.5332274647253</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2335023954088218</v>
+        <v>0.2320790093453163</v>
       </c>
       <c r="T84">
-        <v>3.656960422282649</v>
+        <v>3.630924613077978</v>
       </c>
       <c r="U84">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V84">
-        <v>0.1171517206438986</v>
+        <v>0.125</v>
       </c>
       <c r="W84">
-        <v>0.1208059715734287</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.9372137651511887</v>
+        <v>1.569005005948915</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1420016940304248</v>
+        <v>0.1006307400602274</v>
       </c>
       <c r="C85">
-        <v>-3304.878891638895</v>
+        <v>-746.5699743176774</v>
       </c>
       <c r="D85">
-        <v>3453.779108361106</v>
+        <v>6012.088025682323</v>
       </c>
       <c r="E85">
         <v>4756.258000000001</v>
@@ -8263,45 +8263,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M85">
-        <v>1076.980527966241</v>
+        <v>643.312782166241</v>
       </c>
       <c r="N85">
-        <v>-79.78052796624127</v>
+        <v>353.8872178337589</v>
       </c>
       <c r="O85">
-        <v>-9.972565995780158</v>
+        <v>44.23590222921986</v>
       </c>
       <c r="P85">
-        <v>-69.80796197046111</v>
+        <v>309.651315604539</v>
       </c>
       <c r="Q85">
-        <v>81.29203802953889</v>
+        <v>460.7513156045391</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2445437127858114</v>
+        <v>0.2427618953474236</v>
       </c>
       <c r="T85">
-        <v>3.872075741240452</v>
+        <v>3.839153945304308</v>
       </c>
       <c r="U85">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V85">
-        <v>0.1157402541301167</v>
+        <v>0.125</v>
       </c>
       <c r="W85">
-        <v>0.1209991118757071</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.9259220330409335</v>
+        <v>1.550101331178446</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1429120601970501</v>
+        <v>0.1008412359829296</v>
       </c>
       <c r="C86">
-        <v>-3431.758117523645</v>
+        <v>-863.9790199314848</v>
       </c>
       <c r="D86">
-        <v>3421.725882476355</v>
+        <v>5989.504980068516</v>
       </c>
       <c r="E86">
         <v>4851.084</v>
@@ -8345,45 +8345,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M86">
-        <v>1089.956196977883</v>
+        <v>651.0635385778825</v>
       </c>
       <c r="N86">
-        <v>-92.75619697788272</v>
+        <v>346.1364614221175</v>
       </c>
       <c r="O86">
-        <v>-11.59452462223534</v>
+        <v>43.26705767776468</v>
       </c>
       <c r="P86">
-        <v>-81.16167235564738</v>
+        <v>302.8694037443528</v>
       </c>
       <c r="Q86">
-        <v>69.93832764435261</v>
+        <v>453.9694037443528</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2569651948349244</v>
+        <v>0.2547801420997941</v>
       </c>
       <c r="T86">
-        <v>4.114080475067977</v>
+        <v>4.073411944058927</v>
       </c>
       <c r="U86">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V86">
-        <v>0.114362393961901</v>
+        <v>0.125</v>
       </c>
       <c r="W86">
-        <v>0.1211876535993598</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.9148991516952081</v>
+        <v>1.531647743902512</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1438224263636755</v>
+        <v>0.1010517319056319</v>
       </c>
       <c r="C87">
-        <v>-3558.047866238468</v>
+        <v>-981.2190442537676</v>
       </c>
       <c r="D87">
-        <v>3390.262133761532</v>
+        <v>5967.090955746233</v>
       </c>
       <c r="E87">
         <v>4945.91</v>
@@ -8427,45 +8427,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M87">
-        <v>1102.931865989524</v>
+        <v>658.8142949895239</v>
       </c>
       <c r="N87">
-        <v>-105.7318659895242</v>
+        <v>338.385705010476</v>
       </c>
       <c r="O87">
-        <v>-13.21648324869052</v>
+        <v>42.29821312630951</v>
       </c>
       <c r="P87">
-        <v>-92.51538274083366</v>
+        <v>296.0874918841665</v>
       </c>
       <c r="Q87">
-        <v>58.58461725916634</v>
+        <v>447.1874918841665</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2710428744905861</v>
+        <v>0.2684008217524809</v>
       </c>
       <c r="T87">
-        <v>4.388352506739176</v>
+        <v>4.338904342647498</v>
       </c>
       <c r="U87">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V87">
-        <v>0.1130169540329375</v>
+        <v>0.125</v>
       </c>
       <c r="W87">
-        <v>0.1213717590471618</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.9041356322634997</v>
+        <v>1.51362835868013</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1447327925303008</v>
+        <v>0.1119477278283341</v>
       </c>
       <c r="C88">
-        <v>-3683.764250852896</v>
+        <v>-2044.358485164299</v>
       </c>
       <c r="D88">
-        <v>3359.371749147104</v>
+        <v>4998.7775148357</v>
       </c>
       <c r="E88">
         <v>5040.736</v>
@@ -8509,45 +8509,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M88">
-        <v>1115.907535001166</v>
+        <v>782.3665626011655</v>
       </c>
       <c r="N88">
-        <v>-118.7075350011656</v>
+        <v>214.8334373988345</v>
       </c>
       <c r="O88">
-        <v>-14.8384418751457</v>
+        <v>26.85417967485431</v>
       </c>
       <c r="P88">
-        <v>-103.8690931260199</v>
+        <v>187.9792577239801</v>
       </c>
       <c r="Q88">
-        <v>47.23090687398006</v>
+        <v>339.0792577239802</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2871316512399136</v>
+        <v>0.283967312784123</v>
       </c>
       <c r="T88">
-        <v>4.701806257220547</v>
+        <v>4.642324226748722</v>
       </c>
       <c r="U88">
-        <v>0.1368366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V88">
-        <v>0.1117028034046475</v>
+        <v>0.125</v>
       </c>
       <c r="W88">
-        <v>0.121551582972922</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.89362242723718</v>
+        <v>1.274594349590516</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1456431586969261</v>
+        <v>0.1122824737510364</v>
       </c>
       <c r="C89">
-        <v>-3808.9228024818</v>
+        <v>-2163.981860358492</v>
       </c>
       <c r="D89">
-        <v>3329.0391975182</v>
+        <v>4973.98013964151</v>
       </c>
       <c r="E89">
         <v>5135.562000000001</v>
@@ -8591,45 +8591,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M89">
-        <v>1128.883204012807</v>
+        <v>791.463848212807</v>
       </c>
       <c r="N89">
-        <v>-131.6832040128071</v>
+        <v>205.736151787193</v>
       </c>
       <c r="O89">
-        <v>-16.46040050160089</v>
+        <v>25.71701897339912</v>
       </c>
       <c r="P89">
-        <v>-115.2228035112062</v>
+        <v>180.0191328137938</v>
       </c>
       <c r="Q89">
-        <v>35.87719648879379</v>
+        <v>331.1191328137938</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3056956244122147</v>
+        <v>0.3019286485898637</v>
       </c>
       <c r="T89">
-        <v>5.063483661622127</v>
+        <v>4.992424093019364</v>
       </c>
       <c r="U89">
-        <v>0.1368366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V89">
-        <v>0.1104188631356286</v>
+        <v>0.125</v>
       </c>
       <c r="W89">
-        <v>0.1217272730153313</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.8833509050850284</v>
+        <v>1.259943839825107</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1465535248635515</v>
+        <v>0.135359281935733</v>
       </c>
       <c r="C90">
-        <v>-3933.538496323312</v>
+        <v>-3526.342786343037</v>
       </c>
       <c r="D90">
-        <v>3299.249503676689</v>
+        <v>3706.445213656963</v>
       </c>
       <c r="E90">
         <v>5230.388</v>
@@ -8673,37 +8673,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M90">
-        <v>1141.858873024448</v>
+        <v>1039.219210624448</v>
       </c>
       <c r="N90">
-        <v>-144.6588730244486</v>
+        <v>-42.01921062444842</v>
       </c>
       <c r="O90">
-        <v>-18.08235912805607</v>
+        <v>-5.252401328056052</v>
       </c>
       <c r="P90">
-        <v>-126.5765138963925</v>
+        <v>-36.76680929639237</v>
       </c>
       <c r="Q90">
-        <v>24.52348610360751</v>
+        <v>114.3331907036076</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3273535931132326</v>
+        <v>0.324268235381412</v>
       </c>
       <c r="T90">
-        <v>5.485440633423972</v>
+        <v>5.427864220237669</v>
       </c>
       <c r="U90">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V90">
-        <v>0.1091641033272691</v>
+        <v>0.1199458196361671</v>
       </c>
       <c r="W90">
-        <v>0.1218989701022313</v>
+        <v>0.1095989701022313</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8733128266181531</v>
+        <v>0.9595665570893365</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1474638910301768</v>
+        <v>0.1361466481023583</v>
       </c>
       <c r="C91">
-        <v>-4057.625776311141</v>
+        <v>-3653.117599035299</v>
       </c>
       <c r="D91">
-        <v>3269.98822368886</v>
+        <v>3674.496400964703</v>
       </c>
       <c r="E91">
         <v>5325.214000000001</v>
@@ -8755,37 +8755,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M91">
-        <v>1154.83454203609</v>
+        <v>1051.02851983609</v>
       </c>
       <c r="N91">
-        <v>-157.63454203609</v>
+        <v>-53.82851983609009</v>
       </c>
       <c r="O91">
-        <v>-19.70431775451125</v>
+        <v>-6.728564979511262</v>
       </c>
       <c r="P91">
-        <v>-137.9302242815788</v>
+        <v>-47.09995485657883</v>
       </c>
       <c r="Q91">
-        <v>13.16977571842122</v>
+        <v>104.0000451434212</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3529493743053447</v>
+        <v>0.3495835295069949</v>
       </c>
       <c r="T91">
-        <v>5.984117054644333</v>
+        <v>5.921306422077457</v>
       </c>
       <c r="U91">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V91">
-        <v>0.1079375403685358</v>
+        <v>0.1185981137975584</v>
       </c>
       <c r="W91">
-        <v>0.122066808827628</v>
+        <v>0.109766808827628</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8635003229482863</v>
+        <v>0.9487849103804673</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1483742571968021</v>
+        <v>0.1369340142689837</v>
       </c>
       <c r="C92">
-        <v>-4181.198578466582</v>
+        <v>-3779.346334120303</v>
       </c>
       <c r="D92">
-        <v>3241.241421533418</v>
+        <v>3643.093665879697</v>
       </c>
       <c r="E92">
         <v>5420.04</v>
@@ -8837,37 +8837,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M92">
-        <v>1167.810211047731</v>
+        <v>1062.837829047731</v>
       </c>
       <c r="N92">
-        <v>-170.6102110477315</v>
+        <v>-65.63782904773132</v>
       </c>
       <c r="O92">
-        <v>-21.32627638096643</v>
+        <v>-8.204728630966414</v>
       </c>
       <c r="P92">
-        <v>-149.283934666765</v>
+        <v>-57.4331004167649</v>
       </c>
       <c r="Q92">
-        <v>1.816065333234945</v>
+        <v>93.66689958323509</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3836643117358792</v>
+        <v>0.3799618824576945</v>
       </c>
       <c r="T92">
-        <v>6.582528760108766</v>
+        <v>6.513437064285204</v>
       </c>
       <c r="U92">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V92">
-        <v>0.1067382343644409</v>
+        <v>0.1172803569775856</v>
       </c>
       <c r="W92">
-        <v>0.1222309178035714</v>
+        <v>0.1099309178035714</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8539058749155275</v>
+        <v>0.9382428558206846</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1492846233634275</v>
+        <v>0.137721380435609</v>
       </c>
       <c r="C93">
-        <v>-4304.270353029515</v>
+        <v>-3905.042873516965</v>
       </c>
       <c r="D93">
-        <v>3212.995646970486</v>
+        <v>3612.223126483036</v>
       </c>
       <c r="E93">
         <v>5514.866000000001</v>
@@ -8919,37 +8919,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M93">
-        <v>1180.785880059373</v>
+        <v>1074.647138259373</v>
       </c>
       <c r="N93">
-        <v>-183.5858800593729</v>
+        <v>-77.44713825937299</v>
       </c>
       <c r="O93">
-        <v>-22.94823500742162</v>
+        <v>-9.680892282421624</v>
       </c>
       <c r="P93">
-        <v>-160.6376450519513</v>
+        <v>-67.76624597695137</v>
       </c>
       <c r="Q93">
-        <v>-9.53764505195133</v>
+        <v>83.33375402304863</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4212047908176435</v>
+        <v>0.4170909805085494</v>
       </c>
       <c r="T93">
-        <v>7.313920844565295</v>
+        <v>7.237152293650228</v>
       </c>
       <c r="U93">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V93">
-        <v>0.1055652867340625</v>
+        <v>0.1159915618459637</v>
       </c>
       <c r="W93">
-        <v>0.1223914199888347</v>
+        <v>0.1100914199888347</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8445222938724998</v>
+        <v>0.9279324947677099</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1501949895300528</v>
+        <v>0.1385087466022343</v>
       </c>
       <c r="C94">
-        <v>-4426.854085442223</v>
+        <v>-4030.220632572069</v>
       </c>
       <c r="D94">
-        <v>3185.237914557777</v>
+        <v>3581.871367427931</v>
       </c>
       <c r="E94">
         <v>5609.692</v>
@@ -9001,37 +9001,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M94">
-        <v>1193.761549071014</v>
+        <v>1086.456447471014</v>
       </c>
       <c r="N94">
-        <v>-196.5615490710144</v>
+        <v>-89.25644747101421</v>
       </c>
       <c r="O94">
-        <v>-24.5701936338768</v>
+        <v>-11.15705593387678</v>
       </c>
       <c r="P94">
-        <v>-171.9913554371376</v>
+        <v>-78.09939153713744</v>
       </c>
       <c r="Q94">
-        <v>-20.89135543713761</v>
+        <v>73.00060846286256</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4681303896698491</v>
+        <v>0.4635023530721182</v>
       </c>
       <c r="T94">
-        <v>8.22816095013596</v>
+        <v>8.141796330356508</v>
       </c>
       <c r="U94">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V94">
-        <v>0.104417837965214</v>
+        <v>0.114730783999812</v>
       </c>
       <c r="W94">
-        <v>0.1225484329961575</v>
+        <v>0.1102484329961575</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8353427037217117</v>
+        <v>0.9178462719984958</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1511053556966782</v>
+        <v>0.1392961127688597</v>
       </c>
       <c r="C95">
-        <v>-4548.962316254841</v>
+        <v>-4154.89257949884</v>
       </c>
       <c r="D95">
-        <v>3157.95568374516</v>
+        <v>3552.025420501161</v>
       </c>
       <c r="E95">
         <v>5704.518000000001</v>
@@ -9083,37 +9083,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M95">
-        <v>1206.737218082656</v>
+        <v>1098.265756682656</v>
       </c>
       <c r="N95">
-        <v>-209.5372180826558</v>
+        <v>-101.0657566826559</v>
       </c>
       <c r="O95">
-        <v>-26.19215226033198</v>
+        <v>-12.63321958533199</v>
       </c>
       <c r="P95">
-        <v>-183.3450658223239</v>
+        <v>-88.4325370973239</v>
       </c>
       <c r="Q95">
-        <v>-32.24506582232388</v>
+        <v>62.66746290267609</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5284633024798276</v>
+        <v>0.5231741177967065</v>
       </c>
       <c r="T95">
-        <v>9.4036125144411</v>
+        <v>9.30491009183601</v>
       </c>
       <c r="U95">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V95">
-        <v>0.1032950655139751</v>
+        <v>0.113497119655728</v>
       </c>
       <c r="W95">
-        <v>0.122702069379667</v>
+        <v>0.1104020693796669</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8263605241118008</v>
+        <v>0.9079769572458236</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1520157218633035</v>
+        <v>0.140083478935485</v>
       </c>
       <c r="C96">
-        <v>-4670.607160016524</v>
+        <v>-4279.071253851691</v>
       </c>
       <c r="D96">
-        <v>3131.136839983476</v>
+        <v>3522.672746148309</v>
       </c>
       <c r="E96">
         <v>5799.344</v>
@@ -9165,37 +9165,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M96">
-        <v>1219.712887094297</v>
+        <v>1110.075065894297</v>
       </c>
       <c r="N96">
-        <v>-222.5128870942973</v>
+        <v>-112.8750658942971</v>
       </c>
       <c r="O96">
-        <v>-27.81411088678716</v>
+        <v>-14.10938323678714</v>
       </c>
       <c r="P96">
-        <v>-194.6987762075102</v>
+        <v>-98.76568265750997</v>
       </c>
       <c r="Q96">
-        <v>-43.59877620751016</v>
+        <v>52.33431734249002</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6089071862264657</v>
+        <v>0.6027364707628244</v>
       </c>
       <c r="T96">
-        <v>10.97088126684795</v>
+        <v>10.85572844047535</v>
       </c>
       <c r="U96">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V96">
-        <v>0.1021961818382945</v>
+        <v>0.1122897034891777</v>
       </c>
       <c r="W96">
-        <v>0.1228524369039528</v>
+        <v>0.1105524369039528</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8175694547063561</v>
+        <v>0.8983176279134215</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1529260880299289</v>
+        <v>0.1408708451021104</v>
       </c>
       <c r="C97">
-        <v>-4791.800323212128</v>
+        <v>-4402.768784092505</v>
       </c>
       <c r="D97">
-        <v>3104.769676787873</v>
+        <v>3493.801215907497</v>
       </c>
       <c r="E97">
         <v>5894.170000000001</v>
@@ -9247,37 +9247,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M97">
-        <v>1232.688556105939</v>
+        <v>1121.884375105939</v>
       </c>
       <c r="N97">
-        <v>-235.4885561059388</v>
+        <v>-124.6843751059388</v>
       </c>
       <c r="O97">
-        <v>-29.43606951324234</v>
+        <v>-15.58554688824235</v>
       </c>
       <c r="P97">
-        <v>-206.0524865926964</v>
+        <v>-109.0988282176964</v>
       </c>
       <c r="Q97">
-        <v>-54.95248659269643</v>
+        <v>42.00117178230356</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.7215286234717592</v>
+        <v>0.7141237649153896</v>
       </c>
       <c r="T97">
-        <v>13.16505752021755</v>
+        <v>13.02687412857042</v>
       </c>
       <c r="U97">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V97">
-        <v>0.1011204325557861</v>
+        <v>0.1111077066103442</v>
       </c>
       <c r="W97">
-        <v>0.1229996387961484</v>
+        <v>0.1106996387961484</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8089634604462892</v>
+        <v>0.8888616528827537</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.1538364541965542</v>
+        <v>0.1416582112687357</v>
       </c>
       <c r="C98">
-        <v>-4912.553121300174</v>
+        <v>-4525.996904300058</v>
       </c>
       <c r="D98">
-        <v>3078.842878699827</v>
+        <v>3465.399095699942</v>
       </c>
       <c r="E98">
         <v>5988.996</v>
@@ -9329,37 +9329,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M98">
-        <v>1245.66422511758</v>
+        <v>1133.69368431758</v>
       </c>
       <c r="N98">
-        <v>-248.4642251175802</v>
+        <v>-136.4936843175802</v>
       </c>
       <c r="O98">
-        <v>-31.05802813969753</v>
+        <v>-17.06171053969753</v>
       </c>
       <c r="P98">
-        <v>-217.4061969778827</v>
+        <v>-119.4319737778827</v>
       </c>
       <c r="Q98">
-        <v>-66.30619697788271</v>
+        <v>31.66802622211729</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.8904607793396969</v>
+        <v>0.8812047061442351</v>
       </c>
       <c r="T98">
-        <v>16.4563219002719</v>
+        <v>16.28359266071299</v>
       </c>
       <c r="U98">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V98">
-        <v>0.1000670947166634</v>
+        <v>0.1099503346664865</v>
       </c>
       <c r="W98">
-        <v>0.1231437739822565</v>
+        <v>0.1108437739822565</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8005367577333071</v>
+        <v>0.8796026773318917</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2384746143764441</v>
+        <v>0.1424455774353611</v>
       </c>
       <c r="C99">
-        <v>-6353.001881376504</v>
+        <v>-4648.766970071054</v>
       </c>
       <c r="D99">
-        <v>1733.220118623496</v>
+        <v>3437.455029928945</v>
       </c>
       <c r="E99">
         <v>6083.821999999999</v>
@@ -9411,45 +9411,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M99">
-        <v>2039.560451929221</v>
+        <v>1145.502993529221</v>
       </c>
       <c r="N99">
-        <v>-1042.360451929222</v>
+        <v>-148.3029935292215</v>
       </c>
       <c r="O99">
-        <v>-130.2950564911527</v>
+        <v>-18.53787419115268</v>
       </c>
       <c r="P99">
-        <v>-912.0653954380689</v>
+        <v>-129.7651193380688</v>
       </c>
       <c r="Q99">
-        <v>-760.9653954380689</v>
+        <v>21.33488066193124</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.217840839561749</v>
+        <v>1.159672941525647</v>
       </c>
       <c r="T99">
-        <v>22.83458852105198</v>
+        <v>21.71145688095066</v>
       </c>
       <c r="U99">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V99">
-        <v>0.06111610954315842</v>
+        <v>0.1088168260616773</v>
       </c>
       <c r="W99">
-        <v>0.2081849373088573</v>
+        <v>0.1109849373088573</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.4889288763452673</v>
+        <v>0.8705346084934187</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2402339805430694</v>
+        <v>0.1432329436019864</v>
       </c>
       <c r="C100">
-        <v>-6463.432450550317</v>
+        <v>-4771.089973657937</v>
       </c>
       <c r="D100">
-        <v>1717.615549449683</v>
+        <v>3409.958026342063</v>
       </c>
       <c r="E100">
         <v>6178.648</v>
@@ -9493,45 +9493,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M100">
-        <v>2060.586848340863</v>
+        <v>1157.312302740863</v>
       </c>
       <c r="N100">
-        <v>-1063.386848340863</v>
+        <v>-160.1123027408631</v>
       </c>
       <c r="O100">
-        <v>-132.9233560426079</v>
+        <v>-20.01403784260789</v>
       </c>
       <c r="P100">
-        <v>-930.4634922982553</v>
+        <v>-140.0982648982553</v>
       </c>
       <c r="Q100">
-        <v>-779.3634922982553</v>
+        <v>11.00173510174474</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.803861259342623</v>
+        <v>1.71660941228847</v>
       </c>
       <c r="T100">
-        <v>34.25188278157796</v>
+        <v>32.56718532142598</v>
       </c>
       <c r="U100">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V100">
-        <v>0.06049247577230986</v>
+        <v>0.1077064502855378</v>
       </c>
       <c r="W100">
-        <v>0.2083232197512418</v>
+        <v>0.1111232197512418</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.4839398061784789</v>
+        <v>0.861651602284302</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2419933467096948</v>
+        <v>0.1440203097686117</v>
       </c>
       <c r="C101">
-        <v>-6573.584544036086</v>
+        <v>-4892.976558385946</v>
       </c>
       <c r="D101">
-        <v>1702.289455963913</v>
+        <v>3382.897441614053</v>
       </c>
       <c r="E101">
         <v>6273.473999999999</v>
@@ -9575,45 +9575,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M101">
-        <v>2081.613244752504</v>
+        <v>1169.121611952504</v>
       </c>
       <c r="N101">
-        <v>-1084.413244752504</v>
+        <v>-171.9216119525043</v>
       </c>
       <c r="O101">
-        <v>-135.551655594063</v>
+        <v>-21.49020149406304</v>
       </c>
       <c r="P101">
-        <v>-948.8615891584413</v>
+        <v>-150.4314104584413</v>
       </c>
       <c r="Q101">
-        <v>-797.7615891584413</v>
+        <v>0.6685895415587026</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.561922518685245</v>
+        <v>3.38741882457694</v>
       </c>
       <c r="T101">
-        <v>68.50376556315592</v>
+        <v>65.13437064285196</v>
       </c>
       <c r="U101">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V101">
-        <v>0.05988144066349866</v>
+        <v>0.1066185063432596</v>
       </c>
       <c r="W101">
-        <v>0.2084587086089316</v>
+        <v>0.1112587086089316</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.4790515253079892</v>
+        <v>0.8529480507460769</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/ireland/ireland_diversified.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_diversified.xlsx
@@ -1175,7 +1175,7 @@
         <v>0.0849000842662474</v>
       </c>
       <c r="R2">
-        <v>0.082894367852688</v>
+        <v>0.0828943678526881</v>
       </c>
       <c r="S2">
         <v>0.0557695395797173</v>
@@ -1203,7 +1203,7 @@
         <v>1.0398097419454</v>
       </c>
       <c r="Z2">
-        <v>0.897585150815898</v>
+        <v>0.897585150815899</v>
       </c>
       <c r="AA2">
         <v>3114.3</v>
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08315957847594085</v>
+        <v>0.0831469493986431</v>
       </c>
       <c r="C2">
-        <v>9862.43448648732</v>
+        <v>9770.490568676669</v>
       </c>
       <c r="D2">
-        <v>8750.53448648732</v>
+        <v>8753.416568676668</v>
       </c>
       <c r="E2">
-        <v>-3114.3</v>
+        <v>-3019.474</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>94.82600000000001</v>
       </c>
       <c r="G2">
         <v>1111.9</v>
@@ -1457,28 +1457,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>5.332693411641459</v>
       </c>
       <c r="N2">
-        <v>997.1999999999999</v>
+        <v>991.8673065883585</v>
       </c>
       <c r="O2">
-        <v>124.65</v>
+        <v>123.9834133235448</v>
       </c>
       <c r="P2">
-        <v>872.55</v>
+        <v>867.8838932648137</v>
       </c>
       <c r="Q2">
-        <v>1023.65</v>
+        <v>1018.983893264814</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08315957847594085</v>
+        <v>0.08348977677055144</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7346439012026598</v>
       </c>
       <c r="U2">
         <v>0.0562366166625341</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>186.9974369467926</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0831469493986431</v>
+        <v>0.08313432032134534</v>
       </c>
       <c r="C3">
-        <v>9770.490568676669</v>
+        <v>9678.548549980742</v>
       </c>
       <c r="D3">
-        <v>8753.416568676668</v>
+        <v>8756.300549980742</v>
       </c>
       <c r="E3">
-        <v>-3019.474</v>
+        <v>-2924.648</v>
       </c>
       <c r="F3">
-        <v>94.82600000000001</v>
+        <v>189.652</v>
       </c>
       <c r="G3">
         <v>1111.9</v>
@@ -1539,28 +1539,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M3">
-        <v>5.332693411641459</v>
+        <v>10.66538682328292</v>
       </c>
       <c r="N3">
-        <v>991.8673065883585</v>
+        <v>986.534613176717</v>
       </c>
       <c r="O3">
-        <v>123.9834133235448</v>
+        <v>123.3168266470896</v>
       </c>
       <c r="P3">
-        <v>867.8838932648137</v>
+        <v>863.2177865296273</v>
       </c>
       <c r="Q3">
-        <v>1018.983893264814</v>
+        <v>1014.317786529627</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08348977677055144</v>
+        <v>0.08382671380586837</v>
       </c>
       <c r="T3">
-        <v>0.7346439012026598</v>
+        <v>0.7412114311615606</v>
       </c>
       <c r="U3">
         <v>0.0562366166625341</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>186.9974369467926</v>
+        <v>93.49871847339629</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08313432032134534</v>
+        <v>0.0831216912440476</v>
       </c>
       <c r="C4">
-        <v>9678.548549980742</v>
+        <v>9586.608432277257</v>
       </c>
       <c r="D4">
-        <v>8756.300549980742</v>
+        <v>8759.186432277256</v>
       </c>
       <c r="E4">
-        <v>-2924.648</v>
+        <v>-2829.822</v>
       </c>
       <c r="F4">
-        <v>189.652</v>
+        <v>284.478</v>
       </c>
       <c r="G4">
         <v>1111.9</v>
@@ -1621,28 +1621,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M4">
-        <v>10.66538682328292</v>
+        <v>15.99808023492438</v>
       </c>
       <c r="N4">
-        <v>986.534613176717</v>
+        <v>981.2019197650756</v>
       </c>
       <c r="O4">
-        <v>123.3168266470896</v>
+        <v>122.6502399706344</v>
       </c>
       <c r="P4">
-        <v>863.2177865296273</v>
+        <v>858.5516797944412</v>
       </c>
       <c r="Q4">
-        <v>1014.317786529627</v>
+        <v>1009.651679794441</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08382671380586837</v>
+        <v>0.08417059799655266</v>
       </c>
       <c r="T4">
-        <v>0.7412114311615606</v>
+        <v>0.7479143741093048</v>
       </c>
       <c r="U4">
         <v>0.0562366166625341</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>93.49871847339629</v>
+        <v>62.33247898226419</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0831216912440476</v>
+        <v>0.08310906216674985</v>
       </c>
       <c r="C5">
-        <v>9586.608432277257</v>
+        <v>9494.67021744641</v>
       </c>
       <c r="D5">
-        <v>8759.186432277256</v>
+        <v>8762.07421744641</v>
       </c>
       <c r="E5">
-        <v>-2829.822</v>
+        <v>-2734.996</v>
       </c>
       <c r="F5">
-        <v>284.478</v>
+        <v>379.304</v>
       </c>
       <c r="G5">
         <v>1111.9</v>
@@ -1703,28 +1703,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M5">
-        <v>15.99808023492438</v>
+        <v>21.33077364656583</v>
       </c>
       <c r="N5">
-        <v>981.2019197650756</v>
+        <v>975.8692263534341</v>
       </c>
       <c r="O5">
-        <v>122.6502399706344</v>
+        <v>121.9836532941793</v>
       </c>
       <c r="P5">
-        <v>858.5516797944412</v>
+        <v>853.8855730592549</v>
       </c>
       <c r="Q5">
-        <v>1009.651679794441</v>
+        <v>1004.985573059255</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08417059799655266</v>
+        <v>0.08452164644120953</v>
       </c>
       <c r="T5">
-        <v>0.7479143741093048</v>
+        <v>0.7547569617017938</v>
       </c>
       <c r="U5">
         <v>0.0562366166625341</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>62.33247898226419</v>
+        <v>46.74935923669815</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08310906216674985</v>
+        <v>0.08309643308945208</v>
       </c>
       <c r="C6">
-        <v>9494.67021744641</v>
+        <v>9402.733907370879</v>
       </c>
       <c r="D6">
-        <v>8762.07421744641</v>
+        <v>8764.963907370879</v>
       </c>
       <c r="E6">
-        <v>-2734.996</v>
+        <v>-2640.17</v>
       </c>
       <c r="F6">
-        <v>379.304</v>
+        <v>474.1300000000001</v>
       </c>
       <c r="G6">
         <v>1111.9</v>
@@ -1785,28 +1785,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M6">
-        <v>21.33077364656583</v>
+        <v>26.6634670582073</v>
       </c>
       <c r="N6">
-        <v>975.8692263534341</v>
+        <v>970.5365329417926</v>
       </c>
       <c r="O6">
-        <v>121.9836532941793</v>
+        <v>121.3170666177241</v>
       </c>
       <c r="P6">
-        <v>853.8855730592549</v>
+        <v>849.2194663240685</v>
       </c>
       <c r="Q6">
-        <v>1004.985573059255</v>
+        <v>1000.319466324069</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08452164644120953</v>
+        <v>0.08488008537943813</v>
       </c>
       <c r="T6">
-        <v>0.7547569617017938</v>
+        <v>0.7617436037699141</v>
       </c>
       <c r="U6">
         <v>0.0562366166625341</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>46.74935923669815</v>
+        <v>37.39948738935851</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08309643308945208</v>
+        <v>0.08308380401215433</v>
       </c>
       <c r="C7">
-        <v>9402.733907370879</v>
+        <v>9310.799503935816</v>
       </c>
       <c r="D7">
-        <v>8764.963907370879</v>
+        <v>8767.855503935816</v>
       </c>
       <c r="E7">
-        <v>-2640.17</v>
+        <v>-2545.344</v>
       </c>
       <c r="F7">
-        <v>474.1300000000001</v>
+        <v>568.956</v>
       </c>
       <c r="G7">
         <v>1111.9</v>
@@ -1867,28 +1867,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M7">
-        <v>26.6634670582073</v>
+        <v>31.99616046984875</v>
       </c>
       <c r="N7">
-        <v>970.5365329417926</v>
+        <v>965.2038395301512</v>
       </c>
       <c r="O7">
-        <v>121.3170666177241</v>
+        <v>120.6504799412689</v>
       </c>
       <c r="P7">
-        <v>849.2194663240685</v>
+        <v>844.5533595888822</v>
       </c>
       <c r="Q7">
-        <v>1000.319466324069</v>
+        <v>995.6533595888823</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08488008537943813</v>
+        <v>0.08524615067805458</v>
       </c>
       <c r="T7">
-        <v>0.7617436037699141</v>
+        <v>0.7688788977969306</v>
       </c>
       <c r="U7">
         <v>0.0562366166625341</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.39948738935851</v>
+        <v>31.1662394911321</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08308380401215433</v>
+        <v>0.08307117493485659</v>
       </c>
       <c r="C8">
-        <v>9310.799503935816</v>
+        <v>9218.867009028871</v>
       </c>
       <c r="D8">
-        <v>8767.855503935816</v>
+        <v>8770.74900902887</v>
       </c>
       <c r="E8">
-        <v>-2545.344</v>
+        <v>-2450.518</v>
       </c>
       <c r="F8">
-        <v>568.956</v>
+        <v>663.7819999999999</v>
       </c>
       <c r="G8">
         <v>1111.9</v>
@@ -1949,28 +1949,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M8">
-        <v>31.99616046984875</v>
+        <v>37.3288538814902</v>
       </c>
       <c r="N8">
-        <v>965.2038395301512</v>
+        <v>959.8711461185097</v>
       </c>
       <c r="O8">
-        <v>120.6504799412689</v>
+        <v>119.9838932648137</v>
       </c>
       <c r="P8">
-        <v>844.5533595888822</v>
+        <v>839.8872528536961</v>
       </c>
       <c r="Q8">
-        <v>995.6533595888823</v>
+        <v>990.9872528536961</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08524615067805458</v>
+        <v>0.08562008834868427</v>
       </c>
       <c r="T8">
-        <v>0.7688788977969306</v>
+        <v>0.7761676390073238</v>
       </c>
       <c r="U8">
         <v>0.0562366166625341</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.1662394911321</v>
+        <v>26.71391956382752</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08307117493485659</v>
+        <v>0.08305854585755884</v>
       </c>
       <c r="C9">
-        <v>9218.867009028871</v>
+        <v>9126.936424540188</v>
       </c>
       <c r="D9">
-        <v>8770.74900902887</v>
+        <v>8773.644424540189</v>
       </c>
       <c r="E9">
-        <v>-2450.518</v>
+        <v>-2355.692</v>
       </c>
       <c r="F9">
-        <v>663.782</v>
+        <v>758.6080000000001</v>
       </c>
       <c r="G9">
         <v>1111.9</v>
@@ -2031,28 +2031,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M9">
-        <v>37.32885388149021</v>
+        <v>42.66154729313167</v>
       </c>
       <c r="N9">
-        <v>959.8711461185097</v>
+        <v>954.5384527068683</v>
       </c>
       <c r="O9">
-        <v>119.9838932648137</v>
+        <v>119.3173065883585</v>
       </c>
       <c r="P9">
-        <v>839.8872528536961</v>
+        <v>835.2211461185098</v>
       </c>
       <c r="Q9">
-        <v>990.9872528536961</v>
+        <v>986.3211461185098</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08562008834868427</v>
+        <v>0.08600215509911027</v>
       </c>
       <c r="T9">
-        <v>0.7761676390073238</v>
+        <v>0.7836148311135951</v>
       </c>
       <c r="U9">
         <v>0.0562366166625341</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.71391956382751</v>
+        <v>23.37467961834907</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08305854585755884</v>
+        <v>0.08304591678026108</v>
       </c>
       <c r="C10">
-        <v>9126.936424540188</v>
+        <v>9035.007752362406</v>
       </c>
       <c r="D10">
-        <v>8773.644424540189</v>
+        <v>8776.541752362406</v>
       </c>
       <c r="E10">
-        <v>-2355.692</v>
+        <v>-2260.866</v>
       </c>
       <c r="F10">
-        <v>758.6080000000001</v>
+        <v>853.434</v>
       </c>
       <c r="G10">
         <v>1111.9</v>
@@ -2113,28 +2113,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M10">
-        <v>42.66154729313167</v>
+        <v>47.99424070477313</v>
       </c>
       <c r="N10">
-        <v>954.5384527068683</v>
+        <v>949.2057592952268</v>
       </c>
       <c r="O10">
-        <v>119.3173065883585</v>
+        <v>118.6507199119034</v>
       </c>
       <c r="P10">
-        <v>835.2211461185098</v>
+        <v>830.5550393833234</v>
       </c>
       <c r="Q10">
-        <v>986.3211461185098</v>
+        <v>981.6550393833235</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08600215509911027</v>
+        <v>0.08639261892097419</v>
       </c>
       <c r="T10">
-        <v>0.7836148311135951</v>
+        <v>0.7912256977716524</v>
       </c>
       <c r="U10">
         <v>0.0562366166625341</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.37467961834907</v>
+        <v>20.77749299408807</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08304591678026108</v>
+        <v>0.08303328770296332</v>
       </c>
       <c r="C11">
-        <v>9035.007752362406</v>
+        <v>8943.080994390652</v>
       </c>
       <c r="D11">
-        <v>8776.541752362406</v>
+        <v>8779.440994390652</v>
       </c>
       <c r="E11">
-        <v>-2260.866</v>
+        <v>-2166.04</v>
       </c>
       <c r="F11">
-        <v>853.434</v>
+        <v>948.26</v>
       </c>
       <c r="G11">
         <v>1111.9</v>
@@ -2195,28 +2195,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M11">
-        <v>47.99424070477313</v>
+        <v>53.32693411641458</v>
       </c>
       <c r="N11">
-        <v>949.2057592952268</v>
+        <v>943.8730658835854</v>
       </c>
       <c r="O11">
-        <v>118.6507199119034</v>
+        <v>117.9841332354482</v>
       </c>
       <c r="P11">
-        <v>830.5550393833234</v>
+        <v>825.8889326481371</v>
       </c>
       <c r="Q11">
-        <v>981.6550393833235</v>
+        <v>976.9889326481372</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08639261892097419</v>
+        <v>0.08679175971665733</v>
       </c>
       <c r="T11">
-        <v>0.7912256977716524</v>
+        <v>0.799005694799889</v>
       </c>
       <c r="U11">
         <v>0.0562366166625341</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.77749299408807</v>
+        <v>18.69974369467926</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08303328770296332</v>
+        <v>0.08302065862566557</v>
       </c>
       <c r="C12">
-        <v>8943.080994390652</v>
+        <v>8851.156152522579</v>
       </c>
       <c r="D12">
-        <v>8779.440994390652</v>
+        <v>8782.342152522579</v>
       </c>
       <c r="E12">
-        <v>-2166.04</v>
+        <v>-2071.214</v>
       </c>
       <c r="F12">
-        <v>948.2600000000001</v>
+        <v>1043.086</v>
       </c>
       <c r="G12">
         <v>1111.9</v>
@@ -2277,28 +2277,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M12">
-        <v>53.32693411641459</v>
+        <v>58.65962752805604</v>
       </c>
       <c r="N12">
-        <v>943.8730658835854</v>
+        <v>938.5403724719439</v>
       </c>
       <c r="O12">
-        <v>117.9841332354482</v>
+        <v>117.317546558993</v>
       </c>
       <c r="P12">
-        <v>825.8889326481371</v>
+        <v>821.222825912951</v>
       </c>
       <c r="Q12">
-        <v>976.9889326481372</v>
+        <v>972.322825912951</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08679175971665733</v>
+        <v>0.08719986996842322</v>
       </c>
       <c r="T12">
-        <v>0.799005694799889</v>
+        <v>0.8069605232220185</v>
       </c>
       <c r="U12">
         <v>0.0562366166625341</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.69974369467926</v>
+        <v>16.99976699516296</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08302065862566557</v>
+        <v>0.08300802954836783</v>
       </c>
       <c r="C13">
-        <v>8851.156152522579</v>
+        <v>8759.233228658328</v>
       </c>
       <c r="D13">
-        <v>8782.342152522579</v>
+        <v>8785.245228658328</v>
       </c>
       <c r="E13">
-        <v>-2071.214</v>
+        <v>-1976.388</v>
       </c>
       <c r="F13">
-        <v>1043.086</v>
+        <v>1137.912</v>
       </c>
       <c r="G13">
         <v>1111.9</v>
@@ -2359,28 +2359,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M13">
-        <v>58.65962752805604</v>
+        <v>63.99232093969751</v>
       </c>
       <c r="N13">
-        <v>938.5403724719439</v>
+        <v>933.2076790603024</v>
       </c>
       <c r="O13">
-        <v>117.317546558993</v>
+        <v>116.6509598825378</v>
       </c>
       <c r="P13">
-        <v>821.222825912951</v>
+        <v>816.5567191777646</v>
       </c>
       <c r="Q13">
-        <v>972.322825912951</v>
+        <v>967.6567191777647</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08719986996842322</v>
+        <v>0.0876172554531838</v>
       </c>
       <c r="T13">
-        <v>0.8069605232220185</v>
+        <v>0.8150961431991963</v>
       </c>
       <c r="U13">
         <v>0.0562366166625341</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.99976699516296</v>
+        <v>15.58311974556605</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08300802954836783</v>
+        <v>0.08299540047107007</v>
       </c>
       <c r="C14">
-        <v>8759.233228658328</v>
+        <v>8667.312224700581</v>
       </c>
       <c r="D14">
-        <v>8785.245228658328</v>
+        <v>8788.150224700581</v>
       </c>
       <c r="E14">
-        <v>-1976.388</v>
+        <v>-1881.562</v>
       </c>
       <c r="F14">
-        <v>1137.912</v>
+        <v>1232.738</v>
       </c>
       <c r="G14">
         <v>1111.9</v>
@@ -2441,28 +2441,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M14">
-        <v>63.99232093969751</v>
+        <v>69.32501435133896</v>
       </c>
       <c r="N14">
-        <v>933.2076790603024</v>
+        <v>927.874985648661</v>
       </c>
       <c r="O14">
-        <v>116.6509598825378</v>
+        <v>115.9843732060826</v>
       </c>
       <c r="P14">
-        <v>816.5567191777646</v>
+        <v>811.8906124425783</v>
       </c>
       <c r="Q14">
-        <v>967.6567191777647</v>
+        <v>962.9906124425784</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0876172554531838</v>
+        <v>0.08804423600655956</v>
       </c>
       <c r="T14">
-        <v>0.8150961431991963</v>
+        <v>0.823418788922976</v>
       </c>
       <c r="U14">
         <v>0.0562366166625341</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.58311974556605</v>
+        <v>14.38441822667635</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08299540047107007</v>
+        <v>0.08298277139377232</v>
       </c>
       <c r="C15">
-        <v>8667.312224700581</v>
+        <v>8575.393142554505</v>
       </c>
       <c r="D15">
-        <v>8788.150224700581</v>
+        <v>8791.057142554506</v>
       </c>
       <c r="E15">
-        <v>-1881.562</v>
+        <v>-1786.736</v>
       </c>
       <c r="F15">
-        <v>1232.738</v>
+        <v>1327.564</v>
       </c>
       <c r="G15">
         <v>1111.9</v>
@@ -2523,28 +2523,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M15">
-        <v>69.32501435133896</v>
+        <v>74.65770776298042</v>
       </c>
       <c r="N15">
-        <v>927.874985648661</v>
+        <v>922.5422922370195</v>
       </c>
       <c r="O15">
-        <v>115.9843732060826</v>
+        <v>115.3177865296274</v>
       </c>
       <c r="P15">
-        <v>811.8906124425783</v>
+        <v>807.224505707392</v>
       </c>
       <c r="Q15">
-        <v>962.9906124425784</v>
+        <v>958.3245057073921</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08804423600655956</v>
+        <v>0.08848114634024638</v>
       </c>
       <c r="T15">
-        <v>0.823418788922976</v>
+        <v>0.8319349845473086</v>
       </c>
       <c r="U15">
         <v>0.0562366166625341</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.38441822667635</v>
+        <v>13.35695978191376</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08298277139377232</v>
+        <v>0.08297014231647457</v>
       </c>
       <c r="C16">
-        <v>8575.393142554505</v>
+        <v>8483.475984127814</v>
       </c>
       <c r="D16">
-        <v>8791.057142554506</v>
+        <v>8793.965984127813</v>
       </c>
       <c r="E16">
-        <v>-1786.736</v>
+        <v>-1691.91</v>
       </c>
       <c r="F16">
-        <v>1327.564</v>
+        <v>1422.39</v>
       </c>
       <c r="G16">
         <v>1111.9</v>
@@ -2605,28 +2605,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M16">
-        <v>74.65770776298042</v>
+        <v>79.99040117462189</v>
       </c>
       <c r="N16">
-        <v>922.5422922370195</v>
+        <v>917.2095988253781</v>
       </c>
       <c r="O16">
-        <v>115.3177865296274</v>
+        <v>114.6511998531723</v>
       </c>
       <c r="P16">
-        <v>807.224505707392</v>
+        <v>802.5583989722059</v>
       </c>
       <c r="Q16">
-        <v>958.3245057073921</v>
+        <v>953.6583989722059</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08848114634024638</v>
+        <v>0.08892833691707878</v>
       </c>
       <c r="T16">
-        <v>0.8319349845473086</v>
+        <v>0.8406515612451551</v>
       </c>
       <c r="U16">
         <v>0.0562366166625341</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.35695978191376</v>
+        <v>12.46649579645284</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08297014231647457</v>
+        <v>0.08295751323917681</v>
       </c>
       <c r="C17">
-        <v>8483.475984127814</v>
+        <v>8391.560751330731</v>
       </c>
       <c r="D17">
-        <v>8793.965984127813</v>
+        <v>8796.876751330732</v>
       </c>
       <c r="E17">
-        <v>-1691.91</v>
+        <v>-1597.084</v>
       </c>
       <c r="F17">
-        <v>1422.39</v>
+        <v>1517.216</v>
       </c>
       <c r="G17">
         <v>1111.9</v>
@@ -2687,28 +2687,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M17">
-        <v>79.99040117462188</v>
+        <v>85.32309458626334</v>
       </c>
       <c r="N17">
-        <v>917.2095988253781</v>
+        <v>911.8769054137366</v>
       </c>
       <c r="O17">
-        <v>114.6511998531723</v>
+        <v>113.9846131767171</v>
       </c>
       <c r="P17">
-        <v>802.5583989722059</v>
+        <v>797.8922922370195</v>
       </c>
       <c r="Q17">
-        <v>953.6583989722059</v>
+        <v>948.9922922370196</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08892833691707877</v>
+        <v>0.08938617488859767</v>
       </c>
       <c r="T17">
-        <v>0.8406515612451549</v>
+        <v>0.8495756754834263</v>
       </c>
       <c r="U17">
         <v>0.0562366166625341</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.46649579645284</v>
+        <v>11.68733980917454</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08295751323917681</v>
+        <v>0.08294488416187905</v>
       </c>
       <c r="C18">
-        <v>8391.560751330731</v>
+        <v>8299.647446076026</v>
       </c>
       <c r="D18">
-        <v>8796.876751330732</v>
+        <v>8799.789446076025</v>
       </c>
       <c r="E18">
-        <v>-1597.084</v>
+        <v>-1502.258</v>
       </c>
       <c r="F18">
-        <v>1517.216</v>
+        <v>1612.042</v>
       </c>
       <c r="G18">
         <v>1111.9</v>
@@ -2769,28 +2769,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M18">
-        <v>85.32309458626334</v>
+        <v>90.65578799790481</v>
       </c>
       <c r="N18">
-        <v>911.8769054137366</v>
+        <v>906.5442120020952</v>
       </c>
       <c r="O18">
-        <v>113.9846131767171</v>
+        <v>113.3180265002619</v>
       </c>
       <c r="P18">
-        <v>797.8922922370195</v>
+        <v>793.2261855018332</v>
       </c>
       <c r="Q18">
-        <v>948.9922922370196</v>
+        <v>944.3261855018333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08938617488859767</v>
+        <v>0.0898550451003941</v>
       </c>
       <c r="T18">
-        <v>0.8495756754834263</v>
+        <v>0.8587148286190053</v>
       </c>
       <c r="U18">
         <v>0.0562366166625341</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.68733980917454</v>
+        <v>10.99984923216427</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08294488416187905</v>
+        <v>0.0829322550845813</v>
       </c>
       <c r="C19">
-        <v>8299.647446076026</v>
+        <v>8207.736070278979</v>
       </c>
       <c r="D19">
-        <v>8799.789446076025</v>
+        <v>8802.70407027898</v>
       </c>
       <c r="E19">
-        <v>-1502.258</v>
+        <v>-1407.432</v>
       </c>
       <c r="F19">
-        <v>1612.042</v>
+        <v>1706.868</v>
       </c>
       <c r="G19">
         <v>1111.9</v>
@@ -2851,28 +2851,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M19">
-        <v>90.65578799790481</v>
+        <v>95.98848140954627</v>
       </c>
       <c r="N19">
-        <v>906.5442120020952</v>
+        <v>901.2115185904537</v>
       </c>
       <c r="O19">
-        <v>113.3180265002619</v>
+        <v>112.6514398238067</v>
       </c>
       <c r="P19">
-        <v>793.2261855018332</v>
+        <v>788.5600787666469</v>
       </c>
       <c r="Q19">
-        <v>944.3261855018333</v>
+        <v>939.660078766647</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0898550451003941</v>
+        <v>0.09033535117101486</v>
       </c>
       <c r="T19">
-        <v>0.8587148286190053</v>
+        <v>0.8680768879286229</v>
       </c>
       <c r="U19">
         <v>0.0562366166625341</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.99984923216427</v>
+        <v>10.38874649704403</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08293225508458131</v>
+        <v>0.08291962600728356</v>
       </c>
       <c r="C20">
-        <v>8207.736070278976</v>
+        <v>8115.82662585743</v>
       </c>
       <c r="D20">
-        <v>8802.704070278976</v>
+        <v>8805.620625857431</v>
       </c>
       <c r="E20">
-        <v>-1407.432</v>
+        <v>-1312.606</v>
       </c>
       <c r="F20">
-        <v>1706.868</v>
+        <v>1801.694</v>
       </c>
       <c r="G20">
         <v>1111.9</v>
@@ -2933,28 +2933,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M20">
-        <v>95.98848140954625</v>
+        <v>101.3211748211877</v>
       </c>
       <c r="N20">
-        <v>901.2115185904537</v>
+        <v>895.8788251788122</v>
       </c>
       <c r="O20">
-        <v>112.6514398238067</v>
+        <v>111.9848531473515</v>
       </c>
       <c r="P20">
-        <v>788.5600787666469</v>
+        <v>783.8939720314607</v>
       </c>
       <c r="Q20">
-        <v>939.660078766647</v>
+        <v>934.9939720314608</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09033535117101486</v>
+        <v>0.09082751665078673</v>
       </c>
       <c r="T20">
-        <v>0.8680768879286229</v>
+        <v>0.8776701091965025</v>
       </c>
       <c r="U20">
         <v>0.0562366166625341</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.38874649704403</v>
+        <v>9.841970365620663</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08291962600728356</v>
+        <v>0.08290699692998582</v>
       </c>
       <c r="C21">
-        <v>8115.82662585743</v>
+        <v>8023.919114731751</v>
       </c>
       <c r="D21">
-        <v>8805.620625857431</v>
+        <v>8808.539114731751</v>
       </c>
       <c r="E21">
-        <v>-1312.606</v>
+        <v>-1217.78</v>
       </c>
       <c r="F21">
-        <v>1801.694</v>
+        <v>1896.52</v>
       </c>
       <c r="G21">
         <v>1111.9</v>
@@ -3015,28 +3015,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M21">
-        <v>101.3211748211877</v>
+        <v>106.6538682328292</v>
       </c>
       <c r="N21">
-        <v>895.8788251788122</v>
+        <v>890.5461317671708</v>
       </c>
       <c r="O21">
-        <v>111.9848531473515</v>
+        <v>111.3182664708963</v>
       </c>
       <c r="P21">
-        <v>783.8939720314607</v>
+        <v>779.2278652962744</v>
       </c>
       <c r="Q21">
-        <v>934.9939720314608</v>
+        <v>930.3278652962745</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09082751665078673</v>
+        <v>0.09133198626755293</v>
       </c>
       <c r="T21">
-        <v>0.8776701091965025</v>
+        <v>0.8875031609960793</v>
       </c>
       <c r="U21">
         <v>0.0562366166625341</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.841970365620663</v>
+        <v>9.34987184733963</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08290699692998582</v>
+        <v>0.08289436785268806</v>
       </c>
       <c r="C22">
-        <v>8023.919114731751</v>
+        <v>7932.013538824875</v>
       </c>
       <c r="D22">
-        <v>8808.539114731751</v>
+        <v>8811.459538824876</v>
       </c>
       <c r="E22">
-        <v>-1217.78</v>
+        <v>-1122.954</v>
       </c>
       <c r="F22">
-        <v>1896.52</v>
+        <v>1991.346</v>
       </c>
       <c r="G22">
         <v>1111.9</v>
@@ -3097,28 +3097,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M22">
-        <v>106.6538682328292</v>
+        <v>111.9865616444706</v>
       </c>
       <c r="N22">
-        <v>890.5461317671708</v>
+        <v>885.2134383555293</v>
       </c>
       <c r="O22">
-        <v>111.3182664708963</v>
+        <v>110.6516797944412</v>
       </c>
       <c r="P22">
-        <v>779.2278652962744</v>
+        <v>774.5617585610881</v>
       </c>
       <c r="Q22">
-        <v>930.3278652962745</v>
+        <v>925.6617585610882</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09133198626755293</v>
+        <v>0.09184922726702205</v>
       </c>
       <c r="T22">
-        <v>0.8875031609960793</v>
+        <v>0.8975851508158985</v>
       </c>
       <c r="U22">
         <v>0.0562366166625341</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.34987184733963</v>
+        <v>8.904639854609171</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08289436785268804</v>
+        <v>0.08317048877539029</v>
       </c>
       <c r="C23">
-        <v>7932.01353882488</v>
+        <v>7773.774174219294</v>
       </c>
       <c r="D23">
-        <v>8811.45953882488</v>
+        <v>8748.046174219295</v>
       </c>
       <c r="E23">
-        <v>-1122.954</v>
+        <v>-1028.128</v>
       </c>
       <c r="F23">
-        <v>1991.346</v>
+        <v>2086.172</v>
       </c>
       <c r="G23">
         <v>1111.9</v>
@@ -3179,45 +3179,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M23">
-        <v>111.9865616444706</v>
+        <v>120.4485130561121</v>
       </c>
       <c r="N23">
-        <v>885.2134383555293</v>
+        <v>876.7514869438878</v>
       </c>
       <c r="O23">
-        <v>110.6516797944412</v>
+        <v>109.593935867986</v>
       </c>
       <c r="P23">
-        <v>774.5617585610881</v>
+        <v>767.1575510759019</v>
       </c>
       <c r="Q23">
-        <v>925.6617585610882</v>
+        <v>918.2575510759019</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09184922726702202</v>
+        <v>0.09237973085622113</v>
       </c>
       <c r="T23">
-        <v>0.8975851508158983</v>
+        <v>0.9079256531952</v>
       </c>
       <c r="U23">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V23">
         <v>0.125</v>
       </c>
       <c r="W23">
-        <v>0.04920703957971734</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>8.904639854609172</v>
+        <v>8.27905612695646</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08317048877539029</v>
+        <v>0.08317098469809253</v>
       </c>
       <c r="C24">
-        <v>7773.774174219294</v>
+        <v>7678.83510274041</v>
       </c>
       <c r="D24">
-        <v>8748.046174219295</v>
+        <v>8747.93310274041</v>
       </c>
       <c r="E24">
-        <v>-1028.128</v>
+        <v>-933.3020000000001</v>
       </c>
       <c r="F24">
-        <v>2086.172</v>
+        <v>2180.998</v>
       </c>
       <c r="G24">
         <v>1111.9</v>
@@ -3261,28 +3261,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M24">
-        <v>120.4485130561121</v>
+        <v>125.9234454677535</v>
       </c>
       <c r="N24">
-        <v>876.7514869438878</v>
+        <v>871.2765545322463</v>
       </c>
       <c r="O24">
-        <v>109.593935867986</v>
+        <v>108.9095693165308</v>
       </c>
       <c r="P24">
-        <v>767.1575510759019</v>
+        <v>762.3669852157155</v>
       </c>
       <c r="Q24">
-        <v>918.2575510759019</v>
+        <v>913.4669852157156</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09237973085622113</v>
+        <v>0.09292401375942538</v>
       </c>
       <c r="T24">
-        <v>0.9079256531952</v>
+        <v>0.9185347400518861</v>
       </c>
       <c r="U24">
         <v>0.05773661666253409</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.27905612695646</v>
+        <v>7.919097164914874</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08317098469809253</v>
+        <v>0.08317148062079478</v>
       </c>
       <c r="C25">
-        <v>7678.83510274041</v>
+        <v>7583.896034184461</v>
       </c>
       <c r="D25">
-        <v>8747.93310274041</v>
+        <v>8747.820034184462</v>
       </c>
       <c r="E25">
-        <v>-933.3020000000001</v>
+        <v>-838.4760000000001</v>
       </c>
       <c r="F25">
-        <v>2180.998</v>
+        <v>2275.824</v>
       </c>
       <c r="G25">
         <v>1111.9</v>
@@ -3343,28 +3343,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M25">
-        <v>125.9234454677535</v>
+        <v>131.398377879395</v>
       </c>
       <c r="N25">
-        <v>871.2765545322463</v>
+        <v>865.801622120605</v>
       </c>
       <c r="O25">
-        <v>108.9095693165308</v>
+        <v>108.2252027650756</v>
       </c>
       <c r="P25">
-        <v>762.3669852157155</v>
+        <v>757.5764193555293</v>
       </c>
       <c r="Q25">
-        <v>913.4669852157156</v>
+        <v>908.6764193555293</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09292401375942538</v>
+        <v>0.09348261989692451</v>
       </c>
       <c r="T25">
-        <v>0.9185347400518861</v>
+        <v>0.9294230134048009</v>
       </c>
       <c r="U25">
         <v>0.05773661666253409</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.919097164914874</v>
+        <v>7.589134783043423</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08317148062079478</v>
+        <v>0.08317197654349703</v>
       </c>
       <c r="C26">
-        <v>7583.896034184461</v>
+        <v>7488.956968551336</v>
       </c>
       <c r="D26">
-        <v>8747.820034184462</v>
+        <v>8747.706968551336</v>
       </c>
       <c r="E26">
-        <v>-838.4760000000001</v>
+        <v>-743.6500000000001</v>
       </c>
       <c r="F26">
-        <v>2275.824</v>
+        <v>2370.65</v>
       </c>
       <c r="G26">
         <v>1111.9</v>
@@ -3425,28 +3425,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M26">
-        <v>131.398377879395</v>
+        <v>136.8733102910365</v>
       </c>
       <c r="N26">
-        <v>865.801622120605</v>
+        <v>860.3266897089635</v>
       </c>
       <c r="O26">
-        <v>108.2252027650756</v>
+        <v>107.5408362136204</v>
       </c>
       <c r="P26">
-        <v>757.5764193555293</v>
+        <v>752.7858534953431</v>
       </c>
       <c r="Q26">
-        <v>908.6764193555293</v>
+        <v>903.8858534953431</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09348261989692451</v>
+        <v>0.09405612219809026</v>
       </c>
       <c r="T26">
-        <v>0.9294230134048008</v>
+        <v>0.9406016407137933</v>
       </c>
       <c r="U26">
         <v>0.05773661666253409</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.589134783043423</v>
+        <v>7.285569391721685</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08317197654349703</v>
+        <v>0.08317247246619928</v>
       </c>
       <c r="C27">
-        <v>7488.956968551336</v>
+        <v>7394.017905840918</v>
       </c>
       <c r="D27">
-        <v>8747.706968551336</v>
+        <v>8747.593905840919</v>
       </c>
       <c r="E27">
-        <v>-743.6500000000001</v>
+        <v>-648.8240000000001</v>
       </c>
       <c r="F27">
-        <v>2370.65</v>
+        <v>2465.476</v>
       </c>
       <c r="G27">
         <v>1111.9</v>
@@ -3507,28 +3507,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M27">
-        <v>136.8733102910365</v>
+        <v>142.3482427026779</v>
       </c>
       <c r="N27">
-        <v>860.3266897089635</v>
+        <v>854.851757297322</v>
       </c>
       <c r="O27">
-        <v>107.5408362136204</v>
+        <v>106.8564696621653</v>
       </c>
       <c r="P27">
-        <v>752.7858534953431</v>
+        <v>747.9952876351567</v>
       </c>
       <c r="Q27">
-        <v>903.8858534953431</v>
+        <v>899.0952876351568</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09405612219809026</v>
+        <v>0.0946451245614497</v>
       </c>
       <c r="T27">
-        <v>0.9406016407137933</v>
+        <v>0.952082393085191</v>
       </c>
       <c r="U27">
         <v>0.05773661666253409</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.285569391721685</v>
+        <v>7.005355184347774</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08317247246619928</v>
+        <v>0.08317296838890154</v>
       </c>
       <c r="C28">
-        <v>7394.017905840918</v>
+        <v>7299.0788460531</v>
       </c>
       <c r="D28">
-        <v>8747.593905840919</v>
+        <v>8747.4808460531</v>
       </c>
       <c r="E28">
-        <v>-648.8240000000001</v>
+        <v>-553.998</v>
       </c>
       <c r="F28">
-        <v>2465.476</v>
+        <v>2560.302</v>
       </c>
       <c r="G28">
         <v>1111.9</v>
@@ -3589,28 +3589,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M28">
-        <v>142.3482427026779</v>
+        <v>147.8231751143194</v>
       </c>
       <c r="N28">
-        <v>854.851757297322</v>
+        <v>849.3768248856805</v>
       </c>
       <c r="O28">
-        <v>106.8564696621653</v>
+        <v>106.1721031107101</v>
       </c>
       <c r="P28">
-        <v>747.9952876351567</v>
+        <v>743.2047217749705</v>
       </c>
       <c r="Q28">
-        <v>899.0952876351568</v>
+        <v>894.3047217749705</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0946451245614497</v>
+        <v>0.09525026397586007</v>
       </c>
       <c r="T28">
-        <v>0.952082393085191</v>
+        <v>0.963877686617449</v>
       </c>
       <c r="U28">
         <v>0.05773661666253409</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.005355184347774</v>
+        <v>6.745897584927485</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08317296838890154</v>
+        <v>0.08358996431160377</v>
       </c>
       <c r="C29">
-        <v>7299.0788460531</v>
+        <v>7110.209937016674</v>
       </c>
       <c r="D29">
-        <v>8747.4808460531</v>
+        <v>8653.437937016675</v>
       </c>
       <c r="E29">
-        <v>-553.998</v>
+        <v>-459.172</v>
       </c>
       <c r="F29">
-        <v>2560.302</v>
+        <v>2655.128</v>
       </c>
       <c r="G29">
         <v>1111.9</v>
@@ -3671,45 +3671,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M29">
-        <v>147.8231751143194</v>
+        <v>157.8118251259608</v>
       </c>
       <c r="N29">
-        <v>849.3768248856805</v>
+        <v>839.3881748740391</v>
       </c>
       <c r="O29">
-        <v>106.1721031107101</v>
+        <v>104.9235218592549</v>
       </c>
       <c r="P29">
-        <v>743.2047217749705</v>
+        <v>734.4646530147843</v>
       </c>
       <c r="Q29">
-        <v>894.3047217749705</v>
+        <v>885.5646530147843</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09525026397586007</v>
+        <v>0.09587221281844852</v>
       </c>
       <c r="T29">
-        <v>0.963877686617449</v>
+        <v>0.9760006271922695</v>
       </c>
       <c r="U29">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V29">
         <v>0.125</v>
       </c>
       <c r="W29">
-        <v>0.05051953957971733</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.745897584927485</v>
+        <v>6.318918111517079</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08358996431160377</v>
+        <v>0.08360533523430602</v>
       </c>
       <c r="C30">
-        <v>7110.209937016674</v>
+        <v>7011.956039763068</v>
       </c>
       <c r="D30">
-        <v>8653.437937016675</v>
+        <v>8650.010039763069</v>
       </c>
       <c r="E30">
-        <v>-459.172</v>
+        <v>-364.3459999999995</v>
       </c>
       <c r="F30">
-        <v>2655.128</v>
+        <v>2749.954000000001</v>
       </c>
       <c r="G30">
         <v>1111.9</v>
@@ -3753,28 +3753,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M30">
-        <v>157.8118251259608</v>
+        <v>163.4479617376023</v>
       </c>
       <c r="N30">
-        <v>839.3881748740391</v>
+        <v>833.7520382623976</v>
       </c>
       <c r="O30">
-        <v>104.9235218592549</v>
+        <v>104.2190047827997</v>
       </c>
       <c r="P30">
-        <v>734.4646530147843</v>
+        <v>729.5330334795979</v>
       </c>
       <c r="Q30">
-        <v>885.5646530147843</v>
+        <v>880.6330334795979</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09587221281844852</v>
+        <v>0.09651168134674366</v>
       </c>
       <c r="T30">
-        <v>0.9760006271922695</v>
+        <v>0.9884650590508879</v>
       </c>
       <c r="U30">
         <v>0.05943661666253409</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.318918111517079</v>
+        <v>6.10102438353373</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08360533523430601</v>
+        <v>0.08362070615700826</v>
       </c>
       <c r="C31">
-        <v>7011.95603976307</v>
+        <v>6913.704857228578</v>
       </c>
       <c r="D31">
-        <v>8650.01003976307</v>
+        <v>8646.584857228579</v>
       </c>
       <c r="E31">
-        <v>-364.3460000000005</v>
+        <v>-269.52</v>
       </c>
       <c r="F31">
-        <v>2749.954</v>
+        <v>2844.78</v>
       </c>
       <c r="G31">
         <v>1111.9</v>
@@ -3835,28 +3835,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M31">
-        <v>163.4479617376023</v>
+        <v>169.0840983492438</v>
       </c>
       <c r="N31">
-        <v>833.7520382623977</v>
+        <v>828.1159016507562</v>
       </c>
       <c r="O31">
-        <v>104.2190047827997</v>
+        <v>103.5144877063445</v>
       </c>
       <c r="P31">
-        <v>729.533033479598</v>
+        <v>724.6014139444117</v>
       </c>
       <c r="Q31">
-        <v>880.633033479598</v>
+        <v>875.7014139444117</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09651168134674365</v>
+        <v>0.09716942040441867</v>
       </c>
       <c r="T31">
-        <v>0.9884650590508878</v>
+        <v>1.001285617534038</v>
       </c>
       <c r="U31">
         <v>0.05943661666253409</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.101024383533733</v>
+        <v>5.897656904082607</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08362070615700826</v>
+        <v>0.08363607707971052</v>
       </c>
       <c r="C32">
-        <v>6913.704857228578</v>
+        <v>6815.456386189597</v>
       </c>
       <c r="D32">
-        <v>8646.584857228579</v>
+        <v>8643.162386189597</v>
       </c>
       <c r="E32">
-        <v>-269.52</v>
+        <v>-174.694</v>
       </c>
       <c r="F32">
-        <v>2844.78</v>
+        <v>2939.606</v>
       </c>
       <c r="G32">
         <v>1111.9</v>
@@ -3917,28 +3917,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M32">
-        <v>169.0840983492438</v>
+        <v>174.7202349608852</v>
       </c>
       <c r="N32">
-        <v>828.1159016507562</v>
+        <v>822.4797650391147</v>
       </c>
       <c r="O32">
-        <v>103.5144877063445</v>
+        <v>102.8099706298893</v>
       </c>
       <c r="P32">
-        <v>724.6014139444117</v>
+        <v>719.6697944092253</v>
       </c>
       <c r="Q32">
-        <v>875.7014139444117</v>
+        <v>870.7697944092254</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09716942040441867</v>
+        <v>0.09784622436231616</v>
       </c>
       <c r="T32">
-        <v>1.001285617534038</v>
+        <v>1.014477786408004</v>
       </c>
       <c r="U32">
         <v>0.05943661666253409</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.897656904082607</v>
+        <v>5.707409907176716</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08363607707971052</v>
+        <v>0.08387544800241276</v>
       </c>
       <c r="C33">
-        <v>6815.456386189597</v>
+        <v>6667.679832874033</v>
       </c>
       <c r="D33">
-        <v>8643.162386189597</v>
+        <v>8590.211832874034</v>
       </c>
       <c r="E33">
-        <v>-174.694</v>
+        <v>-79.86799999999994</v>
       </c>
       <c r="F33">
-        <v>2939.606</v>
+        <v>3034.432</v>
       </c>
       <c r="G33">
         <v>1111.9</v>
@@ -3999,45 +3999,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M33">
-        <v>174.7202349608852</v>
+        <v>182.7839171725267</v>
       </c>
       <c r="N33">
-        <v>822.4797650391147</v>
+        <v>814.4160828274732</v>
       </c>
       <c r="O33">
-        <v>102.8099706298893</v>
+        <v>101.8020103534342</v>
       </c>
       <c r="P33">
-        <v>719.6697944092253</v>
+        <v>712.6140724740391</v>
       </c>
       <c r="Q33">
-        <v>870.7697944092254</v>
+        <v>863.7140724740391</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09784622436231616</v>
+        <v>0.09854293431897532</v>
       </c>
       <c r="T33">
-        <v>1.014477786408004</v>
+        <v>1.028057960248852</v>
       </c>
       <c r="U33">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V33">
         <v>0.125</v>
       </c>
       <c r="W33">
-        <v>0.05200703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>5.707409907176716</v>
+        <v>5.455622220081647</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08387544800241276</v>
+        <v>0.08389781892511501</v>
       </c>
       <c r="C34">
-        <v>6667.679832874033</v>
+        <v>6567.938356367871</v>
       </c>
       <c r="D34">
-        <v>8590.211832874034</v>
+        <v>8585.296356367871</v>
       </c>
       <c r="E34">
-        <v>-79.86799999999994</v>
+        <v>14.95800000000008</v>
       </c>
       <c r="F34">
-        <v>3034.432</v>
+        <v>3129.258</v>
       </c>
       <c r="G34">
         <v>1111.9</v>
@@ -4081,28 +4081,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M34">
-        <v>182.7839171725267</v>
+        <v>188.4959145841681</v>
       </c>
       <c r="N34">
-        <v>814.4160828274732</v>
+        <v>808.7040854158317</v>
       </c>
       <c r="O34">
-        <v>101.8020103534342</v>
+        <v>101.088010676979</v>
       </c>
       <c r="P34">
-        <v>712.6140724740391</v>
+        <v>707.6160747388528</v>
       </c>
       <c r="Q34">
-        <v>863.7140724740391</v>
+        <v>858.7160747388529</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09854293431897532</v>
+        <v>0.09926044158777357</v>
       </c>
       <c r="T34">
-        <v>1.028057960248852</v>
+        <v>1.042043512413307</v>
       </c>
       <c r="U34">
         <v>0.0602366166625341</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.455622220081647</v>
+        <v>5.290300334624628</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08389781892511501</v>
+        <v>0.08392018984781727</v>
       </c>
       <c r="C35">
-        <v>6567.938356367871</v>
+        <v>6468.202502095892</v>
       </c>
       <c r="D35">
-        <v>8585.296356367871</v>
+        <v>8580.386502095893</v>
       </c>
       <c r="E35">
-        <v>14.95800000000008</v>
+        <v>109.7840000000001</v>
       </c>
       <c r="F35">
-        <v>3129.258</v>
+        <v>3224.084</v>
       </c>
       <c r="G35">
         <v>1111.9</v>
@@ -4163,28 +4163,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M35">
-        <v>188.4959145841681</v>
+        <v>194.2079119958096</v>
       </c>
       <c r="N35">
-        <v>808.7040854158317</v>
+        <v>802.9920880041904</v>
       </c>
       <c r="O35">
-        <v>101.088010676979</v>
+        <v>100.3740110005238</v>
       </c>
       <c r="P35">
-        <v>707.6160747388528</v>
+        <v>702.6180770036666</v>
       </c>
       <c r="Q35">
-        <v>858.7160747388529</v>
+        <v>853.7180770036666</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09926044158777357</v>
+        <v>0.09999969150108087</v>
       </c>
       <c r="T35">
-        <v>1.042043512413307</v>
+        <v>1.056452869188806</v>
       </c>
       <c r="U35">
         <v>0.0602366166625341</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.290300334624628</v>
+        <v>5.134703265959197</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08392018984781727</v>
+        <v>0.08394256077051949</v>
       </c>
       <c r="C36">
-        <v>6468.202502095892</v>
+        <v>6368.4722604177</v>
       </c>
       <c r="D36">
-        <v>8580.386502095893</v>
+        <v>8575.482260417701</v>
       </c>
       <c r="E36">
-        <v>109.7840000000001</v>
+        <v>204.6100000000001</v>
       </c>
       <c r="F36">
-        <v>3224.084</v>
+        <v>3318.91</v>
       </c>
       <c r="G36">
         <v>1111.9</v>
@@ -4245,28 +4245,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M36">
-        <v>194.2079119958096</v>
+        <v>199.9199094074511</v>
       </c>
       <c r="N36">
-        <v>802.9920880041904</v>
+        <v>797.2800905925488</v>
       </c>
       <c r="O36">
-        <v>100.3740110005238</v>
+        <v>99.66001132406861</v>
       </c>
       <c r="P36">
-        <v>702.6180770036666</v>
+        <v>697.6200792684803</v>
       </c>
       <c r="Q36">
-        <v>853.7180770036666</v>
+        <v>848.7200792684803</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09999969150108087</v>
+        <v>0.1007616875655668</v>
       </c>
       <c r="T36">
-        <v>1.056452869188806</v>
+        <v>1.071305590788167</v>
       </c>
       <c r="U36">
         <v>0.0602366166625341</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.134703265959197</v>
+        <v>4.987997458360363</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08394256077051949</v>
+        <v>0.08396493169322175</v>
       </c>
       <c r="C37">
-        <v>6368.4722604177</v>
+        <v>6268.747621714905</v>
       </c>
       <c r="D37">
-        <v>8575.482260417701</v>
+        <v>8570.583621714906</v>
       </c>
       <c r="E37">
-        <v>204.6100000000001</v>
+        <v>299.4360000000001</v>
       </c>
       <c r="F37">
-        <v>3318.91</v>
+        <v>3413.736</v>
       </c>
       <c r="G37">
         <v>1111.9</v>
@@ -4327,28 +4327,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M37">
-        <v>199.9199094074511</v>
+        <v>205.6319068190925</v>
       </c>
       <c r="N37">
-        <v>797.2800905925488</v>
+        <v>791.5680931809075</v>
       </c>
       <c r="O37">
-        <v>99.66001132406861</v>
+        <v>98.94601164761343</v>
       </c>
       <c r="P37">
-        <v>697.6200792684803</v>
+        <v>692.622081533294</v>
       </c>
       <c r="Q37">
-        <v>848.7200792684803</v>
+        <v>843.722081533294</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1007616875655668</v>
+        <v>0.101547496007068</v>
       </c>
       <c r="T37">
-        <v>1.071305590788167</v>
+        <v>1.086622459937507</v>
       </c>
       <c r="U37">
         <v>0.0602366166625341</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.987997458360363</v>
+        <v>4.849441973405909</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08396493169322176</v>
+        <v>0.08398730261592399</v>
       </c>
       <c r="C38">
-        <v>6268.747621714904</v>
+        <v>6169.028576391109</v>
       </c>
       <c r="D38">
-        <v>8570.583621714904</v>
+        <v>8565.690576391109</v>
       </c>
       <c r="E38">
-        <v>299.4359999999997</v>
+        <v>394.2619999999997</v>
       </c>
       <c r="F38">
-        <v>3413.736</v>
+        <v>3508.562</v>
       </c>
       <c r="G38">
         <v>1111.9</v>
@@ -4409,28 +4409,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M38">
-        <v>205.6319068190925</v>
+        <v>211.343904230734</v>
       </c>
       <c r="N38">
-        <v>791.5680931809075</v>
+        <v>785.8560957692659</v>
       </c>
       <c r="O38">
-        <v>98.94601164761343</v>
+        <v>98.23201197115824</v>
       </c>
       <c r="P38">
-        <v>692.622081533294</v>
+        <v>687.6240837981077</v>
       </c>
       <c r="Q38">
-        <v>843.722081533294</v>
+        <v>838.7240837981077</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.101547496007068</v>
+        <v>0.1023582507482994</v>
       </c>
       <c r="T38">
-        <v>1.086622459937507</v>
+        <v>1.102425578901113</v>
       </c>
       <c r="U38">
         <v>0.0602366166625341</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.849441973405909</v>
+        <v>4.718375974124668</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08398730261592399</v>
+        <v>0.08400967353862625</v>
       </c>
       <c r="C39">
-        <v>6169.028576391109</v>
+        <v>6069.315114871792</v>
       </c>
       <c r="D39">
-        <v>8565.690576391109</v>
+        <v>8560.803114871793</v>
       </c>
       <c r="E39">
-        <v>394.2619999999997</v>
+        <v>489.0880000000002</v>
       </c>
       <c r="F39">
-        <v>3508.562</v>
+        <v>3603.388</v>
       </c>
       <c r="G39">
         <v>1111.9</v>
@@ -4491,28 +4491,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M39">
-        <v>211.343904230734</v>
+        <v>217.0559016423754</v>
       </c>
       <c r="N39">
-        <v>785.8560957692659</v>
+        <v>780.1440983576244</v>
       </c>
       <c r="O39">
-        <v>98.23201197115824</v>
+        <v>97.51801229470306</v>
       </c>
       <c r="P39">
-        <v>687.6240837981077</v>
+        <v>682.6260860629213</v>
       </c>
       <c r="Q39">
-        <v>838.7240837981077</v>
+        <v>833.7260860629214</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1023582507482994</v>
+        <v>0.1031951588682801</v>
       </c>
       <c r="T39">
-        <v>1.102425578901113</v>
+        <v>1.118738475895802</v>
       </c>
       <c r="U39">
         <v>0.0602366166625341</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.718375974124668</v>
+        <v>4.594208185331913</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08400967353862625</v>
+        <v>0.08403204446132849</v>
       </c>
       <c r="C40">
-        <v>6069.315114871792</v>
+        <v>5969.607227604298</v>
       </c>
       <c r="D40">
-        <v>8560.803114871793</v>
+        <v>8555.921227604298</v>
       </c>
       <c r="E40">
-        <v>489.0880000000002</v>
+        <v>583.9140000000002</v>
       </c>
       <c r="F40">
-        <v>3603.388</v>
+        <v>3698.214</v>
       </c>
       <c r="G40">
         <v>1111.9</v>
@@ -4573,28 +4573,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M40">
-        <v>217.0559016423754</v>
+        <v>222.7678990540169</v>
       </c>
       <c r="N40">
-        <v>780.1440983576244</v>
+        <v>774.4321009459831</v>
       </c>
       <c r="O40">
-        <v>97.51801229470306</v>
+        <v>96.80401261824788</v>
       </c>
       <c r="P40">
-        <v>682.6260860629213</v>
+        <v>677.6280883277352</v>
       </c>
       <c r="Q40">
-        <v>833.7260860629214</v>
+        <v>828.7280883277352</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1031951588682801</v>
+        <v>0.104059506598752</v>
       </c>
       <c r="T40">
-        <v>1.118738475895802</v>
+        <v>1.135586221972285</v>
       </c>
       <c r="U40">
         <v>0.0602366166625341</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.594208185331913</v>
+        <v>4.476407975451608</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08403204446132849</v>
+        <v>0.08405441538403075</v>
       </c>
       <c r="C41">
-        <v>5969.607227604298</v>
+        <v>5869.904905057729</v>
       </c>
       <c r="D41">
-        <v>8555.921227604298</v>
+        <v>8551.04490505773</v>
       </c>
       <c r="E41">
-        <v>583.9140000000002</v>
+        <v>678.7400000000002</v>
       </c>
       <c r="F41">
-        <v>3698.214</v>
+        <v>3793.04</v>
       </c>
       <c r="G41">
         <v>1111.9</v>
@@ -4655,28 +4655,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M41">
-        <v>222.7678990540169</v>
+        <v>228.4798964656584</v>
       </c>
       <c r="N41">
-        <v>774.4321009459831</v>
+        <v>768.7201035343415</v>
       </c>
       <c r="O41">
-        <v>96.80401261824788</v>
+        <v>96.09001294179269</v>
       </c>
       <c r="P41">
-        <v>677.6280883277352</v>
+        <v>672.6300905925489</v>
       </c>
       <c r="Q41">
-        <v>828.7280883277352</v>
+        <v>823.7300905925489</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.104059506598752</v>
+        <v>0.1049526659202397</v>
       </c>
       <c r="T41">
-        <v>1.135586221972285</v>
+        <v>1.15299555958465</v>
       </c>
       <c r="U41">
         <v>0.0602366166625341</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.476407975451608</v>
+        <v>4.364497776065317</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08405441538403075</v>
+        <v>0.08407678630673299</v>
       </c>
       <c r="C42">
-        <v>5869.904905057729</v>
+        <v>5770.208137722913</v>
       </c>
       <c r="D42">
-        <v>8551.04490505773</v>
+        <v>8546.174137722914</v>
       </c>
       <c r="E42">
-        <v>678.7400000000002</v>
+        <v>773.5660000000003</v>
       </c>
       <c r="F42">
-        <v>3793.04</v>
+        <v>3887.866</v>
       </c>
       <c r="G42">
         <v>1111.9</v>
@@ -4737,28 +4737,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M42">
-        <v>228.4798964656584</v>
+        <v>234.1918938772998</v>
       </c>
       <c r="N42">
-        <v>768.7201035343415</v>
+        <v>763.0081061227002</v>
       </c>
       <c r="O42">
-        <v>96.09001294179269</v>
+        <v>95.37601326533752</v>
       </c>
       <c r="P42">
-        <v>672.6300905925489</v>
+        <v>667.6320928573626</v>
       </c>
       <c r="Q42">
-        <v>823.7300905925489</v>
+        <v>818.7320928573627</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1049526659202397</v>
+        <v>0.1058761018288964</v>
       </c>
       <c r="T42">
-        <v>1.15299555958465</v>
+        <v>1.170995044234723</v>
       </c>
       <c r="U42">
         <v>0.0602366166625341</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.364497776065317</v>
+        <v>4.258046610795432</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08407678630673299</v>
+        <v>0.08446665722943525</v>
       </c>
       <c r="C43">
-        <v>5770.208137722913</v>
+        <v>5591.378725119148</v>
       </c>
       <c r="D43">
-        <v>8546.174137722914</v>
+        <v>8462.170725119149</v>
       </c>
       <c r="E43">
-        <v>773.5660000000003</v>
+        <v>868.3920000000003</v>
       </c>
       <c r="F43">
-        <v>3887.866</v>
+        <v>3982.692</v>
       </c>
       <c r="G43">
         <v>1111.9</v>
@@ -4819,45 +4819,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M43">
-        <v>234.1918938772998</v>
+        <v>243.8865832889413</v>
       </c>
       <c r="N43">
-        <v>763.0081061227002</v>
+        <v>753.3134167110586</v>
       </c>
       <c r="O43">
-        <v>95.37601326533752</v>
+        <v>94.16417708888233</v>
       </c>
       <c r="P43">
-        <v>667.6320928573626</v>
+        <v>659.1492396221763</v>
       </c>
       <c r="Q43">
-        <v>818.7320928573627</v>
+        <v>810.2492396221763</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1058761018288964</v>
+        <v>0.106831380355093</v>
       </c>
       <c r="T43">
-        <v>1.170995044234723</v>
+        <v>1.189615200769281</v>
       </c>
       <c r="U43">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V43">
         <v>0.125</v>
       </c>
       <c r="W43">
-        <v>0.05270703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.258046610795432</v>
+        <v>4.088785805894787</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08446665722943525</v>
+        <v>0.08449777815213749</v>
       </c>
       <c r="C44">
-        <v>5591.378725119149</v>
+        <v>5489.918381324087</v>
       </c>
       <c r="D44">
-        <v>8462.170725119149</v>
+        <v>8455.536381324087</v>
       </c>
       <c r="E44">
-        <v>868.3919999999998</v>
+        <v>963.2179999999998</v>
       </c>
       <c r="F44">
-        <v>3982.692</v>
+        <v>4077.518</v>
       </c>
       <c r="G44">
         <v>1111.9</v>
@@ -4901,28 +4901,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M44">
-        <v>243.8865832889412</v>
+        <v>249.6934067005827</v>
       </c>
       <c r="N44">
-        <v>753.3134167110587</v>
+        <v>747.5065932994172</v>
       </c>
       <c r="O44">
-        <v>94.16417708888234</v>
+        <v>93.43832416242715</v>
       </c>
       <c r="P44">
-        <v>659.1492396221764</v>
+        <v>654.06826913699</v>
       </c>
       <c r="Q44">
-        <v>810.2492396221764</v>
+        <v>805.16826913699</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.106831380355093</v>
+        <v>0.1078201774260685</v>
       </c>
       <c r="T44">
-        <v>1.18961520076928</v>
+        <v>1.208888696129612</v>
       </c>
       <c r="U44">
         <v>0.0612366166625341</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.088785805894788</v>
+        <v>3.993697763897234</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08449777815213749</v>
+        <v>0.08452889907483974</v>
       </c>
       <c r="C45">
-        <v>5489.918381324087</v>
+        <v>5388.468432033854</v>
       </c>
       <c r="D45">
-        <v>8455.536381324087</v>
+        <v>8448.912432033854</v>
       </c>
       <c r="E45">
-        <v>963.2179999999998</v>
+        <v>1058.044</v>
       </c>
       <c r="F45">
-        <v>4077.518</v>
+        <v>4172.344</v>
       </c>
       <c r="G45">
         <v>1111.9</v>
@@ -4983,28 +4983,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M45">
-        <v>249.6934067005827</v>
+        <v>255.5002301122242</v>
       </c>
       <c r="N45">
-        <v>747.5065932994172</v>
+        <v>741.6997698877758</v>
       </c>
       <c r="O45">
-        <v>93.43832416242715</v>
+        <v>92.71247123597198</v>
       </c>
       <c r="P45">
-        <v>654.06826913699</v>
+        <v>648.9872986518038</v>
       </c>
       <c r="Q45">
-        <v>805.16826913699</v>
+        <v>800.0872986518038</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1078201774260685</v>
+        <v>0.1088442886781502</v>
       </c>
       <c r="T45">
-        <v>1.208888696129612</v>
+        <v>1.228850530609956</v>
       </c>
       <c r="U45">
         <v>0.0612366166625341</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.993697763897234</v>
+        <v>3.902931905626843</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08452889907483974</v>
+        <v>0.08456001999754198</v>
       </c>
       <c r="C46">
-        <v>5388.468432033854</v>
+        <v>5287.028852838843</v>
       </c>
       <c r="D46">
-        <v>8448.912432033854</v>
+        <v>8442.298852838843</v>
       </c>
       <c r="E46">
-        <v>1058.044</v>
+        <v>1152.87</v>
       </c>
       <c r="F46">
-        <v>4172.344</v>
+        <v>4267.17</v>
       </c>
       <c r="G46">
         <v>1111.9</v>
@@ -5065,28 +5065,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M46">
-        <v>255.5002301122242</v>
+        <v>261.3070535238656</v>
       </c>
       <c r="N46">
-        <v>741.6997698877758</v>
+        <v>735.8929464761343</v>
       </c>
       <c r="O46">
-        <v>92.71247123597198</v>
+        <v>91.98661830951679</v>
       </c>
       <c r="P46">
-        <v>648.9872986518038</v>
+        <v>643.9063281666175</v>
       </c>
       <c r="Q46">
-        <v>800.0872986518038</v>
+        <v>795.0063281666175</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1088442886781502</v>
+        <v>0.1099056403393985</v>
       </c>
       <c r="T46">
-        <v>1.228850530609956</v>
+        <v>1.249538249980494</v>
       </c>
       <c r="U46">
         <v>0.0612366166625341</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.902931905626843</v>
+        <v>3.816200085501801</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08456001999754198</v>
+        <v>0.08459114092024422</v>
       </c>
       <c r="C47">
-        <v>5287.028852838843</v>
+        <v>5185.599619405811</v>
       </c>
       <c r="D47">
-        <v>8442.298852838843</v>
+        <v>8435.695619405811</v>
       </c>
       <c r="E47">
-        <v>1152.87</v>
+        <v>1247.696</v>
       </c>
       <c r="F47">
-        <v>4267.17</v>
+        <v>4361.996</v>
       </c>
       <c r="G47">
         <v>1111.9</v>
@@ -5147,28 +5147,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M47">
-        <v>261.3070535238656</v>
+        <v>267.1138769355071</v>
       </c>
       <c r="N47">
-        <v>735.8929464761343</v>
+        <v>730.0861230644928</v>
       </c>
       <c r="O47">
-        <v>91.98661830951679</v>
+        <v>91.2607653830616</v>
       </c>
       <c r="P47">
-        <v>643.9063281666175</v>
+        <v>638.8253576814311</v>
       </c>
       <c r="Q47">
-        <v>795.0063281666175</v>
+        <v>789.9253576814311</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1099056403393985</v>
+        <v>0.1110063013214338</v>
       </c>
       <c r="T47">
-        <v>1.249538249980494</v>
+        <v>1.27099218117957</v>
       </c>
       <c r="U47">
         <v>0.0612366166625341</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.816200085501801</v>
+        <v>3.733239214077849</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08459114092024422</v>
+        <v>0.08462226184294647</v>
       </c>
       <c r="C48">
-        <v>5185.599619405811</v>
+        <v>5084.180707477592</v>
       </c>
       <c r="D48">
-        <v>8435.695619405811</v>
+        <v>8429.102707477592</v>
       </c>
       <c r="E48">
-        <v>1247.696</v>
+        <v>1342.522</v>
       </c>
       <c r="F48">
-        <v>4361.996</v>
+        <v>4456.822</v>
       </c>
       <c r="G48">
         <v>1111.9</v>
@@ -5229,28 +5229,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M48">
-        <v>267.1138769355071</v>
+        <v>272.9207003471486</v>
       </c>
       <c r="N48">
-        <v>730.0861230644928</v>
+        <v>724.2792996528514</v>
       </c>
       <c r="O48">
-        <v>91.2607653830616</v>
+        <v>90.53491245660642</v>
       </c>
       <c r="P48">
-        <v>638.8253576814311</v>
+        <v>633.7443871962449</v>
       </c>
       <c r="Q48">
-        <v>789.9253576814311</v>
+        <v>784.844387196245</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1110063013214338</v>
+        <v>0.1121484966801497</v>
       </c>
       <c r="T48">
-        <v>1.27099218117957</v>
+        <v>1.293255694688046</v>
       </c>
       <c r="U48">
         <v>0.0612366166625341</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.733239214077849</v>
+        <v>3.653808592501725</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08462226184294647</v>
+        <v>0.08465338276564872</v>
       </c>
       <c r="C49">
-        <v>5084.180707477592</v>
+        <v>4982.772092872788</v>
       </c>
       <c r="D49">
-        <v>8429.102707477592</v>
+        <v>8422.520092872788</v>
       </c>
       <c r="E49">
-        <v>1342.522</v>
+        <v>1437.348</v>
       </c>
       <c r="F49">
-        <v>4456.822</v>
+        <v>4551.648</v>
       </c>
       <c r="G49">
         <v>1111.9</v>
@@ -5311,28 +5311,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M49">
-        <v>272.9207003471486</v>
+        <v>278.72752375879</v>
       </c>
       <c r="N49">
-        <v>724.2792996528514</v>
+        <v>718.47247624121</v>
       </c>
       <c r="O49">
-        <v>90.53491245660642</v>
+        <v>89.80905953015125</v>
       </c>
       <c r="P49">
-        <v>633.7443871962449</v>
+        <v>628.6634167110587</v>
       </c>
       <c r="Q49">
-        <v>784.844387196245</v>
+        <v>779.7634167110588</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1121484966801497</v>
+        <v>0.1133346226295854</v>
       </c>
       <c r="T49">
-        <v>1.293255694688046</v>
+        <v>1.316375497177616</v>
       </c>
       <c r="U49">
         <v>0.0612366166625341</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.653808592501725</v>
+        <v>3.577687580157939</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08465338276564871</v>
+        <v>0.08468450368835098</v>
       </c>
       <c r="C50">
-        <v>4982.772092872791</v>
+        <v>4881.373751485484</v>
       </c>
       <c r="D50">
-        <v>8422.520092872792</v>
+        <v>8415.947751485484</v>
       </c>
       <c r="E50">
-        <v>1437.348</v>
+        <v>1532.174</v>
       </c>
       <c r="F50">
-        <v>4551.648</v>
+        <v>4646.474</v>
       </c>
       <c r="G50">
         <v>1111.9</v>
@@ -5393,28 +5393,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M50">
-        <v>278.72752375879</v>
+        <v>284.5343471704315</v>
       </c>
       <c r="N50">
-        <v>718.47247624121</v>
+        <v>712.6656528295684</v>
       </c>
       <c r="O50">
-        <v>89.80905953015125</v>
+        <v>89.08320660369606</v>
       </c>
       <c r="P50">
-        <v>628.6634167110587</v>
+        <v>623.5824462258724</v>
       </c>
       <c r="Q50">
-        <v>779.7634167110588</v>
+        <v>774.6824462258725</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1133346226295854</v>
+        <v>0.1145672633221362</v>
       </c>
       <c r="T50">
-        <v>1.316375497177616</v>
+        <v>1.340401958588347</v>
       </c>
       <c r="U50">
         <v>0.0612366166625341</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.577687580157939</v>
+        <v>3.504673547909818</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08468450368835098</v>
+        <v>0.08471562461105321</v>
       </c>
       <c r="C51">
-        <v>4881.373751485484</v>
+        <v>4779.985659284949</v>
       </c>
       <c r="D51">
-        <v>8415.947751485484</v>
+        <v>8409.38565928495</v>
       </c>
       <c r="E51">
-        <v>1532.174</v>
+        <v>1627</v>
       </c>
       <c r="F51">
-        <v>4646.474</v>
+        <v>4741.3</v>
       </c>
       <c r="G51">
         <v>1111.9</v>
@@ -5475,28 +5475,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M51">
-        <v>284.5343471704315</v>
+        <v>290.3411705820729</v>
       </c>
       <c r="N51">
-        <v>712.6656528295684</v>
+        <v>706.8588294179269</v>
       </c>
       <c r="O51">
-        <v>89.08320660369606</v>
+        <v>88.35735367724087</v>
       </c>
       <c r="P51">
-        <v>623.5824462258724</v>
+        <v>618.501475740686</v>
       </c>
       <c r="Q51">
-        <v>774.6824462258725</v>
+        <v>769.6014757406861</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1145672633221362</v>
+        <v>0.1158492096423891</v>
       </c>
       <c r="T51">
-        <v>1.340401958588347</v>
+        <v>1.365389478455507</v>
       </c>
       <c r="U51">
         <v>0.0612366166625341</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.504673547909818</v>
+        <v>3.434580076951621</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08471562461105321</v>
+        <v>0.08474674553375547</v>
       </c>
       <c r="C52">
-        <v>4779.985659284949</v>
+        <v>4678.607792315332</v>
       </c>
       <c r="D52">
-        <v>8409.38565928495</v>
+        <v>8402.833792315332</v>
       </c>
       <c r="E52">
-        <v>1627</v>
+        <v>1721.826</v>
       </c>
       <c r="F52">
-        <v>4741.3</v>
+        <v>4836.126</v>
       </c>
       <c r="G52">
         <v>1111.9</v>
@@ -5557,28 +5557,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M52">
-        <v>290.3411705820729</v>
+        <v>296.1479939937144</v>
       </c>
       <c r="N52">
-        <v>706.8588294179269</v>
+        <v>701.0520060062855</v>
       </c>
       <c r="O52">
-        <v>88.35735367724087</v>
+        <v>87.63150075078569</v>
       </c>
       <c r="P52">
-        <v>618.501475740686</v>
+        <v>613.4205052554998</v>
       </c>
       <c r="Q52">
-        <v>769.6014757406861</v>
+        <v>764.5205052554999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1158492096423891</v>
+        <v>0.1171834803022442</v>
       </c>
       <c r="T52">
-        <v>1.365389478455507</v>
+        <v>1.391396897092754</v>
       </c>
       <c r="U52">
         <v>0.0612366166625341</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.434580076951621</v>
+        <v>3.367235369560413</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08474674553375547</v>
+        <v>0.08477786645645771</v>
       </c>
       <c r="C53">
-        <v>4678.607792315332</v>
+        <v>4577.240126695396</v>
       </c>
       <c r="D53">
-        <v>8402.833792315332</v>
+        <v>8396.292126695396</v>
       </c>
       <c r="E53">
-        <v>1721.826</v>
+        <v>1816.652</v>
       </c>
       <c r="F53">
-        <v>4836.126</v>
+        <v>4930.952</v>
       </c>
       <c r="G53">
         <v>1111.9</v>
@@ -5639,28 +5639,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M53">
-        <v>296.1479939937144</v>
+        <v>301.9548174053559</v>
       </c>
       <c r="N53">
-        <v>701.0520060062855</v>
+        <v>695.2451825946441</v>
       </c>
       <c r="O53">
-        <v>87.63150075078569</v>
+        <v>86.90564782433052</v>
       </c>
       <c r="P53">
-        <v>613.4205052554998</v>
+        <v>608.3395347703135</v>
       </c>
       <c r="Q53">
-        <v>764.5205052554999</v>
+        <v>759.4395347703136</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1171834803022442</v>
+        <v>0.1185733455729265</v>
       </c>
       <c r="T53">
-        <v>1.391396897092754</v>
+        <v>1.418487958173221</v>
       </c>
       <c r="U53">
         <v>0.0612366166625341</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.367235369560413</v>
+        <v>3.302480843222713</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08477786645645771</v>
+        <v>0.08480898737915996</v>
       </c>
       <c r="C54">
-        <v>4577.240126695396</v>
+        <v>4475.882638618201</v>
       </c>
       <c r="D54">
-        <v>8396.292126695396</v>
+        <v>8389.760638618201</v>
       </c>
       <c r="E54">
-        <v>1816.652</v>
+        <v>1911.478</v>
       </c>
       <c r="F54">
-        <v>4930.952</v>
+        <v>5025.778</v>
       </c>
       <c r="G54">
         <v>1111.9</v>
@@ -5721,28 +5721,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M54">
-        <v>301.9548174053559</v>
+        <v>307.7616408169973</v>
       </c>
       <c r="N54">
-        <v>695.2451825946441</v>
+        <v>689.4383591830026</v>
       </c>
       <c r="O54">
-        <v>86.90564782433052</v>
+        <v>86.17979489787533</v>
       </c>
       <c r="P54">
-        <v>608.3395347703135</v>
+        <v>603.2585642851272</v>
       </c>
       <c r="Q54">
-        <v>759.4395347703136</v>
+        <v>754.3585642851273</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1185733455729265</v>
+        <v>0.1200223540466165</v>
       </c>
       <c r="T54">
-        <v>1.418487958173221</v>
+        <v>1.446731830363494</v>
       </c>
       <c r="U54">
         <v>0.0612366166625341</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.302480843222713</v>
+        <v>3.240169883916624</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08480898737915996</v>
+        <v>0.08484010830186221</v>
       </c>
       <c r="C55">
-        <v>4475.882638618201</v>
+        <v>4374.535304350832</v>
       </c>
       <c r="D55">
-        <v>8389.760638618201</v>
+        <v>8383.239304350833</v>
       </c>
       <c r="E55">
-        <v>1911.478</v>
+        <v>2006.304</v>
       </c>
       <c r="F55">
-        <v>5025.778</v>
+        <v>5120.604</v>
       </c>
       <c r="G55">
         <v>1111.9</v>
@@ -5803,28 +5803,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M55">
-        <v>307.7616408169973</v>
+        <v>313.5684642286388</v>
       </c>
       <c r="N55">
-        <v>689.4383591830026</v>
+        <v>683.6315357713611</v>
       </c>
       <c r="O55">
-        <v>86.17979489787533</v>
+        <v>85.45394197142014</v>
       </c>
       <c r="P55">
-        <v>603.2585642851272</v>
+        <v>598.177593799941</v>
       </c>
       <c r="Q55">
-        <v>754.3585642851273</v>
+        <v>749.277593799941</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1200223540466165</v>
+        <v>0.1215343628887279</v>
       </c>
       <c r="T55">
-        <v>1.446731830363494</v>
+        <v>1.476203696996823</v>
       </c>
       <c r="U55">
         <v>0.0612366166625341</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.240169883916624</v>
+        <v>3.180166737918168</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08484010830186221</v>
+        <v>0.08487122922456444</v>
       </c>
       <c r="C56">
-        <v>4374.535304350832</v>
+        <v>4273.198100234118</v>
       </c>
       <c r="D56">
-        <v>8383.239304350833</v>
+        <v>8376.728100234119</v>
       </c>
       <c r="E56">
-        <v>2006.304</v>
+        <v>2101.13</v>
       </c>
       <c r="F56">
-        <v>5120.604</v>
+        <v>5215.43</v>
       </c>
       <c r="G56">
         <v>1111.9</v>
@@ -5885,28 +5885,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M56">
-        <v>313.5684642286388</v>
+        <v>319.3752876402802</v>
       </c>
       <c r="N56">
-        <v>683.6315357713611</v>
+        <v>677.8247123597197</v>
       </c>
       <c r="O56">
-        <v>85.45394197142014</v>
+        <v>84.72808904496496</v>
       </c>
       <c r="P56">
-        <v>598.177593799941</v>
+        <v>593.0966233147548</v>
       </c>
       <c r="Q56">
-        <v>749.277593799941</v>
+        <v>744.1966233147548</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1215343628887279</v>
+        <v>0.123113572123822</v>
       </c>
       <c r="T56">
-        <v>1.476203696996823</v>
+        <v>1.506985424369411</v>
       </c>
       <c r="U56">
         <v>0.0612366166625341</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.180166737918168</v>
+        <v>3.122345524501474</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08487122922456444</v>
+        <v>0.0849023501472667</v>
       </c>
       <c r="C57">
-        <v>4273.198100234118</v>
+        <v>4171.871002682306</v>
       </c>
       <c r="D57">
-        <v>8376.728100234119</v>
+        <v>8370.227002682306</v>
       </c>
       <c r="E57">
-        <v>2101.13</v>
+        <v>2195.956</v>
       </c>
       <c r="F57">
-        <v>5215.43</v>
+        <v>5310.256</v>
       </c>
       <c r="G57">
         <v>1111.9</v>
@@ -5967,28 +5967,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M57">
-        <v>319.3752876402802</v>
+        <v>325.1821110519217</v>
       </c>
       <c r="N57">
-        <v>677.8247123597197</v>
+        <v>672.0178889480783</v>
       </c>
       <c r="O57">
-        <v>84.72808904496496</v>
+        <v>84.00223611850979</v>
       </c>
       <c r="P57">
-        <v>593.0966233147548</v>
+        <v>588.0156528295685</v>
       </c>
       <c r="Q57">
-        <v>744.1966233147548</v>
+        <v>739.1156528295685</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.123113572123822</v>
+        <v>0.124764563596875</v>
       </c>
       <c r="T57">
-        <v>1.506985424369411</v>
+        <v>1.539166321168026</v>
       </c>
       <c r="U57">
         <v>0.0612366166625341</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.122345524501474</v>
+        <v>3.066589354421091</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0849023501472667</v>
+        <v>0.08493347106996894</v>
       </c>
       <c r="C58">
-        <v>4171.871002682306</v>
+        <v>4070.553988182834</v>
       </c>
       <c r="D58">
-        <v>8370.227002682306</v>
+        <v>8363.735988182836</v>
       </c>
       <c r="E58">
-        <v>2195.956</v>
+        <v>2290.782000000001</v>
       </c>
       <c r="F58">
-        <v>5310.256</v>
+        <v>5405.082000000001</v>
       </c>
       <c r="G58">
         <v>1111.9</v>
@@ -6049,28 +6049,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M58">
-        <v>325.1821110519217</v>
+        <v>330.9889344635632</v>
       </c>
       <c r="N58">
-        <v>672.0178889480783</v>
+        <v>666.2110655364368</v>
       </c>
       <c r="O58">
-        <v>84.00223611850979</v>
+        <v>83.2763831920546</v>
       </c>
       <c r="P58">
-        <v>588.0156528295685</v>
+        <v>582.9346823443822</v>
       </c>
       <c r="Q58">
-        <v>739.1156528295685</v>
+        <v>734.0346823443822</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.124764563596875</v>
+        <v>0.1264923453710002</v>
       </c>
       <c r="T58">
-        <v>1.539166321168026</v>
+        <v>1.57284400386425</v>
       </c>
       <c r="U58">
         <v>0.0612366166625341</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.066589354421091</v>
+        <v>3.012789541185632</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08493347106996894</v>
+        <v>0.0862333419926712</v>
       </c>
       <c r="C59">
-        <v>4070.553988182834</v>
+        <v>3713.318670713868</v>
       </c>
       <c r="D59">
-        <v>8363.735988182836</v>
+        <v>8101.326670713869</v>
       </c>
       <c r="E59">
-        <v>2290.782000000001</v>
+        <v>2385.608000000001</v>
       </c>
       <c r="F59">
-        <v>5405.082000000001</v>
+        <v>5499.908000000001</v>
       </c>
       <c r="G59">
         <v>1111.9</v>
@@ -6131,45 +6131,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M59">
-        <v>330.9889344635632</v>
+        <v>350.5455278752046</v>
       </c>
       <c r="N59">
-        <v>666.2110655364368</v>
+        <v>646.6544721247953</v>
       </c>
       <c r="O59">
-        <v>83.2763831920546</v>
+        <v>80.83180901559942</v>
       </c>
       <c r="P59">
-        <v>582.9346823443822</v>
+        <v>565.8226631091959</v>
       </c>
       <c r="Q59">
-        <v>734.0346823443822</v>
+        <v>716.9226631091959</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1264923453710002</v>
+        <v>0.1283024024677027</v>
       </c>
       <c r="T59">
-        <v>1.57284400386425</v>
+        <v>1.608125385736486</v>
       </c>
       <c r="U59">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V59">
         <v>0.125</v>
       </c>
       <c r="W59">
-        <v>0.05358203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.012789541185632</v>
+        <v>2.844708948490727</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08623334199267119</v>
+        <v>0.08628633791537343</v>
       </c>
       <c r="C60">
-        <v>3713.318670713872</v>
+        <v>3608.143104733864</v>
       </c>
       <c r="D60">
-        <v>8101.326670713871</v>
+        <v>8090.977104733864</v>
       </c>
       <c r="E60">
-        <v>2385.607999999999</v>
+        <v>2480.433999999999</v>
       </c>
       <c r="F60">
-        <v>5499.907999999999</v>
+        <v>5594.733999999999</v>
       </c>
       <c r="G60">
         <v>1111.9</v>
@@ -6213,28 +6213,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M60">
-        <v>350.5455278752045</v>
+        <v>356.589416286846</v>
       </c>
       <c r="N60">
-        <v>646.6544721247953</v>
+        <v>640.610583713154</v>
       </c>
       <c r="O60">
-        <v>80.83180901559942</v>
+        <v>80.07632296414425</v>
       </c>
       <c r="P60">
-        <v>565.8226631091959</v>
+        <v>560.5342607490097</v>
       </c>
       <c r="Q60">
-        <v>716.9226631091959</v>
+        <v>711.6342607490097</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1283024024677027</v>
+        <v>0.1302007550325371</v>
       </c>
       <c r="T60">
-        <v>1.608125385736485</v>
+        <v>1.645127810626878</v>
       </c>
       <c r="U60">
         <v>0.06373661666253409</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.844708948490727</v>
+        <v>2.796493542584105</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08628633791537343</v>
+        <v>0.08633933383807568</v>
       </c>
       <c r="C61">
-        <v>3608.143104733864</v>
+        <v>3502.993948465696</v>
       </c>
       <c r="D61">
-        <v>8090.977104733864</v>
+        <v>8080.653948465697</v>
       </c>
       <c r="E61">
-        <v>2480.433999999999</v>
+        <v>2575.26</v>
       </c>
       <c r="F61">
-        <v>5594.733999999999</v>
+        <v>5689.56</v>
       </c>
       <c r="G61">
         <v>1111.9</v>
@@ -6295,28 +6295,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M61">
-        <v>356.589416286846</v>
+        <v>362.6333046984875</v>
       </c>
       <c r="N61">
-        <v>640.610583713154</v>
+        <v>634.5666953015125</v>
       </c>
       <c r="O61">
-        <v>80.07632296414425</v>
+        <v>79.32083691268906</v>
       </c>
       <c r="P61">
-        <v>560.5342607490097</v>
+        <v>555.2458583888234</v>
       </c>
       <c r="Q61">
-        <v>711.6342607490097</v>
+        <v>706.3458583888234</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1302007550325371</v>
+        <v>0.1321940252256132</v>
       </c>
       <c r="T61">
-        <v>1.645127810626878</v>
+        <v>1.683980356761791</v>
       </c>
       <c r="U61">
         <v>0.06373661666253409</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.796493542584105</v>
+        <v>2.749885316874369</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08633933383807568</v>
+        <v>0.08639232976077793</v>
       </c>
       <c r="C62">
-        <v>3502.993948465696</v>
+        <v>3397.871100950915</v>
       </c>
       <c r="D62">
-        <v>8080.653948465697</v>
+        <v>8070.357100950915</v>
       </c>
       <c r="E62">
-        <v>2575.26</v>
+        <v>2670.086</v>
       </c>
       <c r="F62">
-        <v>5689.56</v>
+        <v>5784.386</v>
       </c>
       <c r="G62">
         <v>1111.9</v>
@@ -6377,28 +6377,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M62">
-        <v>362.6333046984875</v>
+        <v>368.6771931101289</v>
       </c>
       <c r="N62">
-        <v>634.5666953015125</v>
+        <v>628.5228068898709</v>
       </c>
       <c r="O62">
-        <v>79.32083691268906</v>
+        <v>78.56535086123387</v>
       </c>
       <c r="P62">
-        <v>555.2458583888234</v>
+        <v>549.9574560286371</v>
       </c>
       <c r="Q62">
-        <v>706.3458583888234</v>
+        <v>701.0574560286371</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1321940252256132</v>
+        <v>0.1342895144029496</v>
       </c>
       <c r="T62">
-        <v>1.683980356761791</v>
+        <v>1.724825341160033</v>
       </c>
       <c r="U62">
         <v>0.06373661666253409</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.749885316874369</v>
+        <v>2.704805229712494</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08639232976077793</v>
+        <v>0.08644532568348018</v>
       </c>
       <c r="C63">
-        <v>3397.871100950915</v>
+        <v>3292.774461745</v>
       </c>
       <c r="D63">
-        <v>8070.357100950915</v>
+        <v>8060.086461745001</v>
       </c>
       <c r="E63">
-        <v>2670.086</v>
+        <v>2764.912</v>
       </c>
       <c r="F63">
-        <v>5784.386</v>
+        <v>5879.212</v>
       </c>
       <c r="G63">
         <v>1111.9</v>
@@ -6459,28 +6459,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M63">
-        <v>368.6771931101289</v>
+        <v>374.7210815217704</v>
       </c>
       <c r="N63">
-        <v>628.5228068898709</v>
+        <v>622.4789184782295</v>
       </c>
       <c r="O63">
-        <v>78.56535086123387</v>
+        <v>77.80986480977869</v>
       </c>
       <c r="P63">
-        <v>549.9574560286371</v>
+        <v>544.6690536684508</v>
       </c>
       <c r="Q63">
-        <v>701.0574560286371</v>
+        <v>695.7690536684509</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1342895144029496</v>
+        <v>0.1364952924843564</v>
       </c>
       <c r="T63">
-        <v>1.724825341160033</v>
+        <v>1.767820061579235</v>
       </c>
       <c r="U63">
         <v>0.06373661666253409</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.704805229712494</v>
+        <v>2.66117933891068</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08644532568348018</v>
+        <v>0.08649832160618243</v>
       </c>
       <c r="C64">
-        <v>3292.774461745</v>
+        <v>3187.7039309141</v>
       </c>
       <c r="D64">
-        <v>8060.086461745001</v>
+        <v>8049.8419309141</v>
       </c>
       <c r="E64">
-        <v>2764.912</v>
+        <v>2859.738</v>
       </c>
       <c r="F64">
-        <v>5879.212</v>
+        <v>5974.038</v>
       </c>
       <c r="G64">
         <v>1111.9</v>
@@ -6541,28 +6541,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M64">
-        <v>374.7210815217704</v>
+        <v>380.7649699334119</v>
       </c>
       <c r="N64">
-        <v>622.4789184782295</v>
+        <v>616.4350300665881</v>
       </c>
       <c r="O64">
-        <v>77.80986480977869</v>
+        <v>77.05437875832351</v>
       </c>
       <c r="P64">
-        <v>544.6690536684508</v>
+        <v>539.3806513082645</v>
       </c>
       <c r="Q64">
-        <v>695.7690536684509</v>
+        <v>690.4806513082646</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1364952924843564</v>
+        <v>0.1388203018134068</v>
       </c>
       <c r="T64">
-        <v>1.767820061579235</v>
+        <v>1.813138820940015</v>
       </c>
       <c r="U64">
         <v>0.06373661666253409</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.66117933891068</v>
+        <v>2.618938397023209</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08649832160618243</v>
+        <v>0.08655131752888467</v>
       </c>
       <c r="C65">
-        <v>3187.7039309141</v>
+        <v>3082.659409031791</v>
       </c>
       <c r="D65">
-        <v>8049.8419309141</v>
+        <v>8039.623409031791</v>
       </c>
       <c r="E65">
-        <v>2859.738</v>
+        <v>2954.564</v>
       </c>
       <c r="F65">
-        <v>5974.038</v>
+        <v>6068.864</v>
       </c>
       <c r="G65">
         <v>1111.9</v>
@@ -6623,28 +6623,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M65">
-        <v>380.7649699334119</v>
+        <v>386.8088583450534</v>
       </c>
       <c r="N65">
-        <v>616.4350300665881</v>
+        <v>610.3911416549465</v>
       </c>
       <c r="O65">
-        <v>77.05437875832351</v>
+        <v>76.29889270686832</v>
       </c>
       <c r="P65">
-        <v>539.3806513082645</v>
+        <v>534.0922489480782</v>
       </c>
       <c r="Q65">
-        <v>690.4806513082646</v>
+        <v>685.1922489480783</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1388203018134068</v>
+        <v>0.1412744783274044</v>
       </c>
       <c r="T65">
-        <v>1.813138820940015</v>
+        <v>1.860975289154172</v>
       </c>
       <c r="U65">
         <v>0.06373661666253409</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.618938397023209</v>
+        <v>2.578017484569721</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08655131752888467</v>
+        <v>0.08660431345158692</v>
       </c>
       <c r="C66">
-        <v>3082.659409031791</v>
+        <v>2977.640797175856</v>
       </c>
       <c r="D66">
-        <v>8039.623409031791</v>
+        <v>8029.430797175856</v>
       </c>
       <c r="E66">
-        <v>2954.564</v>
+        <v>3049.39</v>
       </c>
       <c r="F66">
-        <v>6068.864</v>
+        <v>6163.690000000001</v>
       </c>
       <c r="G66">
         <v>1111.9</v>
@@ -6705,28 +6705,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M66">
-        <v>386.8088583450534</v>
+        <v>392.8527467566948</v>
       </c>
       <c r="N66">
-        <v>610.3911416549465</v>
+        <v>604.3472532433052</v>
       </c>
       <c r="O66">
-        <v>76.29889270686832</v>
+        <v>75.54340665541315</v>
       </c>
       <c r="P66">
-        <v>534.0922489480782</v>
+        <v>528.8038465878921</v>
       </c>
       <c r="Q66">
-        <v>685.1922489480783</v>
+        <v>679.9038465878921</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1412744783274044</v>
+        <v>0.1438688934993448</v>
       </c>
       <c r="T66">
-        <v>1.860975289154172</v>
+        <v>1.911545269837709</v>
       </c>
       <c r="U66">
         <v>0.06373661666253409</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.578017484569721</v>
+        <v>2.538355677114803</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08660431345158692</v>
+        <v>0.08867855937428917</v>
       </c>
       <c r="C67">
-        <v>2977.640797175856</v>
+        <v>2503.220465761279</v>
       </c>
       <c r="D67">
-        <v>8029.430797175856</v>
+        <v>7649.836465761279</v>
       </c>
       <c r="E67">
-        <v>3049.39</v>
+        <v>3144.216</v>
       </c>
       <c r="F67">
-        <v>6163.690000000001</v>
+        <v>6258.516000000001</v>
       </c>
       <c r="G67">
         <v>1111.9</v>
@@ -6787,45 +6787,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M67">
-        <v>392.8527467566948</v>
+        <v>420.8014411683363</v>
       </c>
       <c r="N67">
-        <v>604.3472532433052</v>
+        <v>576.3985588316636</v>
       </c>
       <c r="O67">
-        <v>75.54340665541315</v>
+        <v>72.04981985395796</v>
       </c>
       <c r="P67">
-        <v>528.8038465878921</v>
+        <v>504.3487389777057</v>
       </c>
       <c r="Q67">
-        <v>679.9038465878921</v>
+        <v>655.4487389777057</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1438688934993448</v>
+        <v>0.146615921328458</v>
       </c>
       <c r="T67">
-        <v>1.911545269837709</v>
+        <v>1.965089955267337</v>
       </c>
       <c r="U67">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V67">
         <v>0.125</v>
       </c>
       <c r="W67">
-        <v>0.05576953957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.538355677114803</v>
+        <v>2.369763747080616</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08867855937428917</v>
+        <v>0.08876218029699143</v>
       </c>
       <c r="C68">
-        <v>2503.220465761279</v>
+        <v>2393.842726441202</v>
       </c>
       <c r="D68">
-        <v>7649.836465761279</v>
+        <v>7635.284726441203</v>
       </c>
       <c r="E68">
-        <v>3144.216</v>
+        <v>3239.042</v>
       </c>
       <c r="F68">
-        <v>6258.516000000001</v>
+        <v>6353.342000000001</v>
       </c>
       <c r="G68">
         <v>1111.9</v>
@@ -6869,28 +6869,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M68">
-        <v>420.8014411683363</v>
+        <v>427.1772205799778</v>
       </c>
       <c r="N68">
-        <v>576.3985588316636</v>
+        <v>570.0227794200222</v>
       </c>
       <c r="O68">
-        <v>72.04981985395796</v>
+        <v>71.25284742750277</v>
       </c>
       <c r="P68">
-        <v>504.3487389777057</v>
+        <v>498.7699319925194</v>
       </c>
       <c r="Q68">
-        <v>655.4487389777057</v>
+        <v>649.8699319925194</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.146615921328458</v>
+        <v>0.1495294356926691</v>
       </c>
       <c r="T68">
-        <v>1.965089955267337</v>
+        <v>2.021879773147245</v>
       </c>
       <c r="U68">
         <v>0.0672366166625341</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.369763747080616</v>
+        <v>2.334394138915234</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08876218029699143</v>
+        <v>0.08884580121969368</v>
       </c>
       <c r="C69">
-        <v>2393.842726441202</v>
+        <v>2284.520243486429</v>
       </c>
       <c r="D69">
-        <v>7635.284726441203</v>
+        <v>7620.788243486429</v>
       </c>
       <c r="E69">
-        <v>3239.042</v>
+        <v>3333.868</v>
       </c>
       <c r="F69">
-        <v>6353.342000000001</v>
+        <v>6448.168000000001</v>
       </c>
       <c r="G69">
         <v>1111.9</v>
@@ -6951,28 +6951,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M69">
-        <v>427.1772205799778</v>
+        <v>433.5529999916192</v>
       </c>
       <c r="N69">
-        <v>570.0227794200222</v>
+        <v>563.6470000083807</v>
       </c>
       <c r="O69">
-        <v>71.25284742750277</v>
+        <v>70.45587500104759</v>
       </c>
       <c r="P69">
-        <v>498.7699319925194</v>
+        <v>493.1911250073331</v>
       </c>
       <c r="Q69">
-        <v>649.8699319925194</v>
+        <v>644.2911250073331</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1495294356926691</v>
+        <v>0.1526250447046434</v>
       </c>
       <c r="T69">
-        <v>2.021879773147245</v>
+        <v>2.082218954644648</v>
       </c>
       <c r="U69">
         <v>0.0672366166625341</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.334394138915234</v>
+        <v>2.300064813342951</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08884580121969368</v>
+        <v>0.08892942214239591</v>
       </c>
       <c r="C70">
-        <v>2284.520243486429</v>
+        <v>2175.252702761327</v>
       </c>
       <c r="D70">
-        <v>7620.788243486429</v>
+        <v>7606.346702761327</v>
       </c>
       <c r="E70">
-        <v>3333.868</v>
+        <v>3428.694</v>
       </c>
       <c r="F70">
-        <v>6448.168000000001</v>
+        <v>6542.994000000001</v>
       </c>
       <c r="G70">
         <v>1111.9</v>
@@ -7033,28 +7033,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M70">
-        <v>433.5529999916192</v>
+        <v>439.9287794032606</v>
       </c>
       <c r="N70">
-        <v>563.6470000083807</v>
+        <v>557.2712205967393</v>
       </c>
       <c r="O70">
-        <v>70.45587500104759</v>
+        <v>69.65890257459242</v>
       </c>
       <c r="P70">
-        <v>493.1911250073331</v>
+        <v>487.612318022147</v>
       </c>
       <c r="Q70">
-        <v>644.2911250073331</v>
+        <v>638.712318022147</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1526250447046434</v>
+        <v>0.1559203704270676</v>
       </c>
       <c r="T70">
-        <v>2.082218954644648</v>
+        <v>2.146450986561237</v>
       </c>
       <c r="U70">
         <v>0.0672366166625341</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.300064813342951</v>
+        <v>2.266730540685807</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08892942214239591</v>
+        <v>0.09072804306509816</v>
       </c>
       <c r="C71">
-        <v>2175.252702761327</v>
+        <v>1782.531380984255</v>
       </c>
       <c r="D71">
-        <v>7606.346702761327</v>
+        <v>7308.451380984255</v>
       </c>
       <c r="E71">
-        <v>3428.694</v>
+        <v>3523.52</v>
       </c>
       <c r="F71">
-        <v>6542.994000000001</v>
+        <v>6637.820000000001</v>
       </c>
       <c r="G71">
         <v>1111.9</v>
@@ -7115,45 +7115,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M71">
-        <v>439.9287794032606</v>
+        <v>464.8904548149021</v>
       </c>
       <c r="N71">
-        <v>557.2712205967393</v>
+        <v>532.3095451850978</v>
       </c>
       <c r="O71">
-        <v>69.65890257459242</v>
+        <v>66.53869314813723</v>
       </c>
       <c r="P71">
-        <v>487.612318022147</v>
+        <v>465.7708520369606</v>
       </c>
       <c r="Q71">
-        <v>638.712318022147</v>
+        <v>616.8708520369606</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1559203704270676</v>
+        <v>0.1594353845309868</v>
       </c>
       <c r="T71">
-        <v>2.146450986561237</v>
+        <v>2.214965153938933</v>
       </c>
       <c r="U71">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V71">
         <v>0.125</v>
       </c>
       <c r="W71">
-        <v>0.05883203957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.266730540685807</v>
+        <v>2.145021455424459</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09072804306509816</v>
+        <v>0.09083616398780042</v>
       </c>
       <c r="C72">
-        <v>1782.531380984255</v>
+        <v>1670.539670544953</v>
       </c>
       <c r="D72">
-        <v>7308.451380984255</v>
+        <v>7291.285670544954</v>
       </c>
       <c r="E72">
-        <v>3523.52</v>
+        <v>3618.346</v>
       </c>
       <c r="F72">
-        <v>6637.820000000001</v>
+        <v>6732.646000000001</v>
       </c>
       <c r="G72">
         <v>1111.9</v>
@@ -7197,28 +7197,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M72">
-        <v>464.8904548149021</v>
+        <v>471.5317470265435</v>
       </c>
       <c r="N72">
-        <v>532.3095451850978</v>
+        <v>525.6682529734564</v>
       </c>
       <c r="O72">
-        <v>66.53869314813723</v>
+        <v>65.70853162168206</v>
       </c>
       <c r="P72">
-        <v>465.7708520369606</v>
+        <v>459.9597213517744</v>
       </c>
       <c r="Q72">
-        <v>616.8708520369606</v>
+        <v>611.0597213517744</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1594353845309868</v>
+        <v>0.1631928134006935</v>
       </c>
       <c r="T72">
-        <v>2.214965153938933</v>
+        <v>2.288204436308194</v>
       </c>
       <c r="U72">
         <v>0.07003661666253409</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.145021455424459</v>
+        <v>2.114809885629748</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09083616398780041</v>
+        <v>0.09094428491050266</v>
       </c>
       <c r="C73">
-        <v>1670.539670544956</v>
+        <v>1558.628407011687</v>
       </c>
       <c r="D73">
-        <v>7291.285670544956</v>
+        <v>7274.200407011687</v>
       </c>
       <c r="E73">
-        <v>3618.346</v>
+        <v>3713.172</v>
       </c>
       <c r="F73">
-        <v>6732.646</v>
+        <v>6827.472</v>
       </c>
       <c r="G73">
         <v>1111.9</v>
@@ -7279,28 +7279,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M73">
-        <v>471.5317470265435</v>
+        <v>478.173039238185</v>
       </c>
       <c r="N73">
-        <v>525.6682529734564</v>
+        <v>519.026960761815</v>
       </c>
       <c r="O73">
-        <v>65.70853162168206</v>
+        <v>64.87837009522687</v>
       </c>
       <c r="P73">
-        <v>459.9597213517744</v>
+        <v>454.1485906665881</v>
       </c>
       <c r="Q73">
-        <v>611.0597213517744</v>
+        <v>605.2485906665881</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1631928134006934</v>
+        <v>0.1672186300468078</v>
       </c>
       <c r="T73">
-        <v>2.288204436308193</v>
+        <v>2.366675095989545</v>
       </c>
       <c r="U73">
         <v>0.07003661666253409</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.114809885629748</v>
+        <v>2.085437526107113</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09094428491050266</v>
+        <v>0.09105240583320491</v>
       </c>
       <c r="C74">
-        <v>1558.628407011687</v>
+        <v>1446.797026186244</v>
       </c>
       <c r="D74">
-        <v>7274.200407011687</v>
+        <v>7257.195026186244</v>
       </c>
       <c r="E74">
-        <v>3713.172</v>
+        <v>3807.998</v>
       </c>
       <c r="F74">
-        <v>6827.472</v>
+        <v>6922.298</v>
       </c>
       <c r="G74">
         <v>1111.9</v>
@@ -7361,28 +7361,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M74">
-        <v>478.173039238185</v>
+        <v>484.8143314498264</v>
       </c>
       <c r="N74">
-        <v>519.026960761815</v>
+        <v>512.3856685501735</v>
       </c>
       <c r="O74">
-        <v>64.87837009522687</v>
+        <v>64.04820856877168</v>
       </c>
       <c r="P74">
-        <v>454.1485906665881</v>
+        <v>448.3374599814018</v>
       </c>
       <c r="Q74">
-        <v>605.2485906665881</v>
+        <v>599.4374599814018</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1672186300468078</v>
+        <v>0.171542655333375</v>
       </c>
       <c r="T74">
-        <v>2.366675095989545</v>
+        <v>2.450958397128773</v>
       </c>
       <c r="U74">
         <v>0.07003661666253409</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.085437526107113</v>
+        <v>2.05686988876318</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09105240583320491</v>
+        <v>0.09116052675590716</v>
       </c>
       <c r="C75">
-        <v>1446.797026186244</v>
+        <v>1335.044969133971</v>
       </c>
       <c r="D75">
-        <v>7257.195026186244</v>
+        <v>7240.26896913397</v>
       </c>
       <c r="E75">
-        <v>3807.998</v>
+        <v>3902.824</v>
       </c>
       <c r="F75">
-        <v>6922.298</v>
+        <v>7017.124</v>
       </c>
       <c r="G75">
         <v>1111.9</v>
@@ -7443,28 +7443,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M75">
-        <v>484.8143314498264</v>
+        <v>491.4556236614679</v>
       </c>
       <c r="N75">
-        <v>512.3856685501735</v>
+        <v>505.744376338532</v>
       </c>
       <c r="O75">
-        <v>64.04820856877168</v>
+        <v>63.21804704231651</v>
       </c>
       <c r="P75">
-        <v>448.3374599814018</v>
+        <v>442.5263292962155</v>
       </c>
       <c r="Q75">
-        <v>599.4374599814018</v>
+        <v>593.6263292962155</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.171542655333375</v>
+        <v>0.1761992979496782</v>
       </c>
       <c r="T75">
-        <v>2.450958397128773</v>
+        <v>2.541725029124866</v>
       </c>
       <c r="U75">
         <v>0.07003661666253409</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.05686988876318</v>
+        <v>2.02907434972584</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09116052675590716</v>
+        <v>0.0912686476786094</v>
       </c>
       <c r="C76">
-        <v>1335.044969133971</v>
+        <v>1223.371682122519</v>
       </c>
       <c r="D76">
-        <v>7240.26896913397</v>
+        <v>7223.421682122519</v>
       </c>
       <c r="E76">
-        <v>3902.824</v>
+        <v>3997.650000000001</v>
       </c>
       <c r="F76">
-        <v>7017.124</v>
+        <v>7111.950000000001</v>
       </c>
       <c r="G76">
         <v>1111.9</v>
@@ -7525,28 +7525,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M76">
-        <v>491.4556236614679</v>
+        <v>498.0969158731094</v>
       </c>
       <c r="N76">
-        <v>505.744376338532</v>
+        <v>499.1030841268906</v>
       </c>
       <c r="O76">
-        <v>63.21804704231651</v>
+        <v>62.38788551586132</v>
       </c>
       <c r="P76">
-        <v>442.5263292962155</v>
+        <v>436.7151986110292</v>
       </c>
       <c r="Q76">
-        <v>593.6263292962155</v>
+        <v>587.8151986110292</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1761992979496782</v>
+        <v>0.1812284719752856</v>
       </c>
       <c r="T76">
-        <v>2.541725029124866</v>
+        <v>2.639752991680646</v>
       </c>
       <c r="U76">
         <v>0.07003661666253409</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.02907434972584</v>
+        <v>2.002020025062828</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0912686476786094</v>
+        <v>0.09656376860131165</v>
       </c>
       <c r="C77">
-        <v>1223.371682122519</v>
+        <v>389.5942187046176</v>
       </c>
       <c r="D77">
-        <v>7223.421682122519</v>
+        <v>6484.470218704619</v>
       </c>
       <c r="E77">
-        <v>3997.650000000001</v>
+        <v>4092.476000000001</v>
       </c>
       <c r="F77">
-        <v>7111.950000000001</v>
+        <v>7206.776000000001</v>
       </c>
       <c r="G77">
         <v>1111.9</v>
@@ -7607,45 +7607,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M77">
-        <v>498.0969158731094</v>
+        <v>560.951060884751</v>
       </c>
       <c r="N77">
-        <v>499.1030841268906</v>
+        <v>436.248939115249</v>
       </c>
       <c r="O77">
-        <v>62.38788551586132</v>
+        <v>54.53111738940612</v>
       </c>
       <c r="P77">
-        <v>436.7151986110292</v>
+        <v>381.7178217258428</v>
       </c>
       <c r="Q77">
-        <v>587.8151986110292</v>
+        <v>532.8178217258428</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1812284719752856</v>
+        <v>0.1866767438363603</v>
       </c>
       <c r="T77">
-        <v>2.639752991680646</v>
+        <v>2.745949951116074</v>
       </c>
       <c r="U77">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V77">
         <v>0.125</v>
       </c>
       <c r="W77">
-        <v>0.06128203957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.002020025062828</v>
+        <v>1.777695185079394</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09656376860131165</v>
+        <v>0.09674013952401389</v>
       </c>
       <c r="C78">
-        <v>389.5942187046176</v>
+        <v>272.7480193223728</v>
       </c>
       <c r="D78">
-        <v>6484.470218704619</v>
+        <v>6462.450019322374</v>
       </c>
       <c r="E78">
-        <v>4092.476000000001</v>
+        <v>4187.302000000001</v>
       </c>
       <c r="F78">
-        <v>7206.776000000001</v>
+        <v>7301.602000000001</v>
       </c>
       <c r="G78">
         <v>1111.9</v>
@@ -7689,28 +7689,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M78">
-        <v>560.951060884751</v>
+        <v>568.3319958963924</v>
       </c>
       <c r="N78">
-        <v>436.248939115249</v>
+        <v>428.8680041036075</v>
       </c>
       <c r="O78">
-        <v>54.53111738940612</v>
+        <v>53.60850051295094</v>
       </c>
       <c r="P78">
-        <v>381.7178217258428</v>
+        <v>375.2595035906565</v>
       </c>
       <c r="Q78">
-        <v>532.8178217258428</v>
+        <v>526.3595035906566</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1866767438363603</v>
+        <v>0.1925987784679632</v>
       </c>
       <c r="T78">
-        <v>2.745949951116074</v>
+        <v>2.861381428763279</v>
       </c>
       <c r="U78">
         <v>0.07783661666253411</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.777695185079394</v>
+        <v>1.754608234623818</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09674013952401389</v>
+        <v>0.09957826044671614</v>
       </c>
       <c r="C79">
-        <v>272.7480193223728</v>
+        <v>-156.921226329524</v>
       </c>
       <c r="D79">
-        <v>6462.450019322374</v>
+        <v>6127.606773670477</v>
       </c>
       <c r="E79">
-        <v>4187.302000000001</v>
+        <v>4282.128000000001</v>
       </c>
       <c r="F79">
-        <v>7301.602000000001</v>
+        <v>7396.428000000001</v>
       </c>
       <c r="G79">
         <v>1111.9</v>
@@ -7771,45 +7771,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M79">
-        <v>568.3319958963924</v>
+        <v>604.5590001080338</v>
       </c>
       <c r="N79">
-        <v>428.8680041036075</v>
+        <v>392.6409998919661</v>
       </c>
       <c r="O79">
-        <v>53.60850051295094</v>
+        <v>49.08012498649576</v>
       </c>
       <c r="P79">
-        <v>375.2595035906565</v>
+        <v>343.5608749054703</v>
       </c>
       <c r="Q79">
-        <v>526.3595035906566</v>
+        <v>494.6608749054703</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1925987784679632</v>
+        <v>0.1990591798842574</v>
       </c>
       <c r="T79">
-        <v>2.861381428763279</v>
+        <v>2.987306677105684</v>
       </c>
       <c r="U79">
-        <v>0.07783661666253411</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V79">
         <v>0.125</v>
       </c>
       <c r="W79">
-        <v>0.06810703957971734</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.754608234623818</v>
+        <v>1.649466801125782</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09957826044671614</v>
+        <v>0.09978875636941839</v>
       </c>
       <c r="C80">
-        <v>-156.921226329524</v>
+        <v>-275.2047563970045</v>
       </c>
       <c r="D80">
-        <v>6127.606773670477</v>
+        <v>6104.149243602997</v>
       </c>
       <c r="E80">
-        <v>4282.128000000001</v>
+        <v>4376.954000000001</v>
       </c>
       <c r="F80">
-        <v>7396.428000000001</v>
+        <v>7491.254000000001</v>
       </c>
       <c r="G80">
         <v>1111.9</v>
@@ -7853,28 +7853,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M80">
-        <v>604.5590001080338</v>
+        <v>612.3097565196753</v>
       </c>
       <c r="N80">
-        <v>392.6409998919661</v>
+        <v>384.8902434803247</v>
       </c>
       <c r="O80">
-        <v>49.08012498649576</v>
+        <v>48.11128043504058</v>
       </c>
       <c r="P80">
-        <v>343.5608749054703</v>
+        <v>336.7789630452841</v>
       </c>
       <c r="Q80">
-        <v>494.6608749054703</v>
+        <v>487.8789630452841</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1990591798842574</v>
+        <v>0.2061348576259129</v>
       </c>
       <c r="T80">
-        <v>2.987306677105684</v>
+        <v>3.125224806242604</v>
       </c>
       <c r="U80">
         <v>0.0817366166625341</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.649466801125782</v>
+        <v>1.628587474529253</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09978875636941839</v>
+        <v>0.09999925229212064</v>
       </c>
       <c r="C81">
-        <v>-275.2047563970045</v>
+        <v>-393.3093724783184</v>
       </c>
       <c r="D81">
-        <v>6104.149243602997</v>
+        <v>6080.870627521682</v>
       </c>
       <c r="E81">
-        <v>4376.954000000001</v>
+        <v>4471.780000000001</v>
       </c>
       <c r="F81">
-        <v>7491.254000000001</v>
+        <v>7586.080000000001</v>
       </c>
       <c r="G81">
         <v>1111.9</v>
@@ -7935,28 +7935,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M81">
-        <v>612.3097565196753</v>
+        <v>620.0605129313167</v>
       </c>
       <c r="N81">
-        <v>384.8902434803247</v>
+        <v>377.1394870686833</v>
       </c>
       <c r="O81">
-        <v>48.11128043504058</v>
+        <v>47.14243588358541</v>
       </c>
       <c r="P81">
-        <v>336.7789630452841</v>
+        <v>329.9970511850979</v>
       </c>
       <c r="Q81">
-        <v>487.8789630452841</v>
+        <v>481.0970511850978</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2061348576259129</v>
+        <v>0.2139181031417339</v>
       </c>
       <c r="T81">
-        <v>3.125224806242604</v>
+        <v>3.276934748293216</v>
       </c>
       <c r="U81">
         <v>0.0817366166625341</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.628587474529253</v>
+        <v>1.608230131097638</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09999925229212064</v>
+        <v>0.1002097482148229</v>
       </c>
       <c r="C82">
-        <v>-393.3093724783184</v>
+        <v>-511.2371137015125</v>
       </c>
       <c r="D82">
-        <v>6080.870627521682</v>
+        <v>6057.768886298488</v>
       </c>
       <c r="E82">
-        <v>4471.780000000001</v>
+        <v>4566.606000000001</v>
       </c>
       <c r="F82">
-        <v>7586.080000000001</v>
+        <v>7680.906000000001</v>
       </c>
       <c r="G82">
         <v>1111.9</v>
@@ -8017,28 +8017,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M82">
-        <v>620.0605129313167</v>
+        <v>627.8112693429582</v>
       </c>
       <c r="N82">
-        <v>377.1394870686833</v>
+        <v>369.3887306570417</v>
       </c>
       <c r="O82">
-        <v>47.14243588358541</v>
+        <v>46.17359133213021</v>
       </c>
       <c r="P82">
-        <v>329.9970511850979</v>
+        <v>323.2151393249115</v>
       </c>
       <c r="Q82">
-        <v>481.0970511850978</v>
+        <v>474.3151393249115</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2139181031417339</v>
+        <v>0.2225206376592203</v>
       </c>
       <c r="T82">
-        <v>3.276934748293216</v>
+        <v>3.444614157928103</v>
       </c>
       <c r="U82">
         <v>0.0817366166625341</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.608230131097638</v>
+        <v>1.588375438121123</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1002097482148229</v>
+        <v>0.1004202441375251</v>
       </c>
       <c r="C83">
-        <v>-511.2371137015125</v>
+        <v>-628.989988324628</v>
       </c>
       <c r="D83">
-        <v>6057.768886298488</v>
+        <v>6034.842011675372</v>
       </c>
       <c r="E83">
-        <v>4566.606000000001</v>
+        <v>4661.432000000001</v>
       </c>
       <c r="F83">
-        <v>7680.906000000001</v>
+        <v>7775.732000000001</v>
       </c>
       <c r="G83">
         <v>1111.9</v>
@@ -8099,28 +8099,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M83">
-        <v>627.8112693429582</v>
+        <v>635.5620257545996</v>
       </c>
       <c r="N83">
-        <v>369.3887306570417</v>
+        <v>361.6379742454003</v>
       </c>
       <c r="O83">
-        <v>46.17359133213021</v>
+        <v>45.20474678067504</v>
       </c>
       <c r="P83">
-        <v>323.2151393249115</v>
+        <v>316.4332274647253</v>
       </c>
       <c r="Q83">
-        <v>474.3151393249115</v>
+        <v>467.5332274647253</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2225206376592203</v>
+        <v>0.2320790093453163</v>
       </c>
       <c r="T83">
-        <v>3.444614157928103</v>
+        <v>3.630924613077978</v>
       </c>
       <c r="U83">
         <v>0.0817366166625341</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.588375438121123</v>
+        <v>1.569005005948915</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1004202441375251</v>
+        <v>0.1006307400602274</v>
       </c>
       <c r="C84">
-        <v>-628.989988324628</v>
+        <v>-746.5699743176774</v>
       </c>
       <c r="D84">
-        <v>6034.842011675372</v>
+        <v>6012.088025682323</v>
       </c>
       <c r="E84">
-        <v>4661.432000000001</v>
+        <v>4756.258000000001</v>
       </c>
       <c r="F84">
-        <v>7775.732000000001</v>
+        <v>7870.558000000001</v>
       </c>
       <c r="G84">
         <v>1111.9</v>
@@ -8181,28 +8181,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M84">
-        <v>635.5620257545996</v>
+        <v>643.312782166241</v>
       </c>
       <c r="N84">
-        <v>361.6379742454003</v>
+        <v>353.8872178337589</v>
       </c>
       <c r="O84">
-        <v>45.20474678067504</v>
+        <v>44.23590222921986</v>
       </c>
       <c r="P84">
-        <v>316.4332274647253</v>
+        <v>309.651315604539</v>
       </c>
       <c r="Q84">
-        <v>467.5332274647253</v>
+        <v>460.7513156045391</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2320790093453163</v>
+        <v>0.2427618953474236</v>
       </c>
       <c r="T84">
-        <v>3.630924613077978</v>
+        <v>3.839153945304308</v>
       </c>
       <c r="U84">
         <v>0.0817366166625341</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.569005005948915</v>
+        <v>1.550101331178446</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1006307400602274</v>
+        <v>0.1008412359829296</v>
       </c>
       <c r="C85">
-        <v>-746.5699743176774</v>
+        <v>-863.9790199314875</v>
       </c>
       <c r="D85">
-        <v>6012.088025682323</v>
+        <v>5989.504980068514</v>
       </c>
       <c r="E85">
-        <v>4756.258000000001</v>
+        <v>4851.084000000001</v>
       </c>
       <c r="F85">
-        <v>7870.558000000001</v>
+        <v>7965.384000000001</v>
       </c>
       <c r="G85">
         <v>1111.9</v>
@@ -8263,28 +8263,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M85">
-        <v>643.312782166241</v>
+        <v>651.0635385778826</v>
       </c>
       <c r="N85">
-        <v>353.8872178337589</v>
+        <v>346.1364614221173</v>
       </c>
       <c r="O85">
-        <v>44.23590222921986</v>
+        <v>43.26705767776467</v>
       </c>
       <c r="P85">
-        <v>309.651315604539</v>
+        <v>302.8694037443527</v>
       </c>
       <c r="Q85">
-        <v>460.7513156045391</v>
+        <v>453.9694037443527</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2427618953474236</v>
+        <v>0.2547801420997943</v>
       </c>
       <c r="T85">
-        <v>3.839153945304308</v>
+        <v>4.073411944058931</v>
       </c>
       <c r="U85">
         <v>0.0817366166625341</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.550101331178446</v>
+        <v>1.531647743902512</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1008412359829296</v>
+        <v>0.1010517319056319</v>
       </c>
       <c r="C86">
-        <v>-863.9790199314848</v>
+        <v>-981.2190442537676</v>
       </c>
       <c r="D86">
-        <v>5989.504980068516</v>
+        <v>5967.090955746233</v>
       </c>
       <c r="E86">
-        <v>4851.084</v>
+        <v>4945.91</v>
       </c>
       <c r="F86">
-        <v>7965.384</v>
+        <v>8060.21</v>
       </c>
       <c r="G86">
         <v>1111.9</v>
@@ -8345,28 +8345,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M86">
-        <v>651.0635385778825</v>
+        <v>658.8142949895239</v>
       </c>
       <c r="N86">
-        <v>346.1364614221175</v>
+        <v>338.385705010476</v>
       </c>
       <c r="O86">
-        <v>43.26705767776468</v>
+        <v>42.29821312630951</v>
       </c>
       <c r="P86">
-        <v>302.8694037443528</v>
+        <v>296.0874918841665</v>
       </c>
       <c r="Q86">
-        <v>453.9694037443528</v>
+        <v>447.1874918841665</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2547801420997941</v>
+        <v>0.2684008217524809</v>
       </c>
       <c r="T86">
-        <v>4.073411944058927</v>
+        <v>4.338904342647498</v>
       </c>
       <c r="U86">
         <v>0.0817366166625341</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.531647743902512</v>
+        <v>1.51362835868013</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1010517319056319</v>
+        <v>0.1119477278283341</v>
       </c>
       <c r="C87">
-        <v>-981.2190442537676</v>
+        <v>-2044.358485164299</v>
       </c>
       <c r="D87">
-        <v>5967.090955746233</v>
+        <v>4998.7775148357</v>
       </c>
       <c r="E87">
-        <v>4945.91</v>
+        <v>5040.736</v>
       </c>
       <c r="F87">
-        <v>8060.21</v>
+        <v>8155.036</v>
       </c>
       <c r="G87">
         <v>1111.9</v>
@@ -8427,45 +8427,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M87">
-        <v>658.8142949895239</v>
+        <v>782.3665626011655</v>
       </c>
       <c r="N87">
-        <v>338.385705010476</v>
+        <v>214.8334373988345</v>
       </c>
       <c r="O87">
-        <v>42.29821312630951</v>
+        <v>26.85417967485431</v>
       </c>
       <c r="P87">
-        <v>296.0874918841665</v>
+        <v>187.9792577239801</v>
       </c>
       <c r="Q87">
-        <v>447.1874918841665</v>
+        <v>339.0792577239802</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2684008217524809</v>
+        <v>0.283967312784123</v>
       </c>
       <c r="T87">
-        <v>4.338904342647498</v>
+        <v>4.642324226748722</v>
       </c>
       <c r="U87">
-        <v>0.0817366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V87">
         <v>0.125</v>
       </c>
       <c r="W87">
-        <v>0.07151953957971734</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y87">
-        <v>1.51362835868013</v>
+        <v>1.274594349590516</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1119477278283341</v>
+        <v>0.1122824737510364</v>
       </c>
       <c r="C88">
-        <v>-2044.358485164299</v>
+        <v>-2163.981860358492</v>
       </c>
       <c r="D88">
-        <v>4998.7775148357</v>
+        <v>4973.98013964151</v>
       </c>
       <c r="E88">
-        <v>5040.736</v>
+        <v>5135.562000000001</v>
       </c>
       <c r="F88">
-        <v>8155.036</v>
+        <v>8249.862000000001</v>
       </c>
       <c r="G88">
         <v>1111.9</v>
@@ -8509,28 +8509,28 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M88">
-        <v>782.3665626011655</v>
+        <v>791.463848212807</v>
       </c>
       <c r="N88">
-        <v>214.8334373988345</v>
+        <v>205.736151787193</v>
       </c>
       <c r="O88">
-        <v>26.85417967485431</v>
+        <v>25.71701897339912</v>
       </c>
       <c r="P88">
-        <v>187.9792577239801</v>
+        <v>180.0191328137938</v>
       </c>
       <c r="Q88">
-        <v>339.0792577239802</v>
+        <v>331.1191328137938</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.283967312784123</v>
+        <v>0.3019286485898637</v>
       </c>
       <c r="T88">
-        <v>4.642324226748722</v>
+        <v>4.992424093019364</v>
       </c>
       <c r="U88">
         <v>0.0959366166625341</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.274594349590516</v>
+        <v>1.259943839825107</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1122824737510364</v>
+        <v>0.135359281935733</v>
       </c>
       <c r="C89">
-        <v>-2163.981860358492</v>
+        <v>-3526.342786343037</v>
       </c>
       <c r="D89">
-        <v>4973.98013964151</v>
+        <v>3706.445213656963</v>
       </c>
       <c r="E89">
-        <v>5135.562000000001</v>
+        <v>5230.388</v>
       </c>
       <c r="F89">
-        <v>8249.862000000001</v>
+        <v>8344.688</v>
       </c>
       <c r="G89">
         <v>1111.9</v>
@@ -8591,45 +8591,45 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M89">
-        <v>791.463848212807</v>
+        <v>1039.219210624448</v>
       </c>
       <c r="N89">
-        <v>205.736151787193</v>
+        <v>-42.01921062444842</v>
       </c>
       <c r="O89">
-        <v>25.71701897339912</v>
+        <v>-5.252401328056052</v>
       </c>
       <c r="P89">
-        <v>180.0191328137938</v>
+        <v>-36.76680929639237</v>
       </c>
       <c r="Q89">
-        <v>331.1191328137938</v>
+        <v>114.3331907036076</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3019286485898637</v>
+        <v>0.324268235381412</v>
       </c>
       <c r="T89">
-        <v>4.992424093019364</v>
+        <v>5.427864220237669</v>
       </c>
       <c r="U89">
-        <v>0.0959366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V89">
-        <v>0.125</v>
+        <v>0.1199458196361671</v>
       </c>
       <c r="W89">
-        <v>0.08394453957971734</v>
+        <v>0.1095989701022313</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y89">
-        <v>1.259943839825107</v>
+        <v>0.9595665570893365</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.135359281935733</v>
+        <v>0.1361466481023583</v>
       </c>
       <c r="C90">
-        <v>-3526.342786343037</v>
+        <v>-3653.117599035299</v>
       </c>
       <c r="D90">
-        <v>3706.445213656963</v>
+        <v>3674.496400964703</v>
       </c>
       <c r="E90">
-        <v>5230.388</v>
+        <v>5325.214000000001</v>
       </c>
       <c r="F90">
-        <v>8344.688</v>
+        <v>8439.514000000001</v>
       </c>
       <c r="G90">
         <v>1111.9</v>
@@ -8673,37 +8673,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M90">
-        <v>1039.219210624448</v>
+        <v>1051.02851983609</v>
       </c>
       <c r="N90">
-        <v>-42.01921062444842</v>
+        <v>-53.82851983609009</v>
       </c>
       <c r="O90">
-        <v>-5.252401328056052</v>
+        <v>-6.728564979511262</v>
       </c>
       <c r="P90">
-        <v>-36.76680929639237</v>
+        <v>-47.09995485657883</v>
       </c>
       <c r="Q90">
-        <v>114.3331907036076</v>
+        <v>104.0000451434212</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.324268235381412</v>
+        <v>0.3495835295069949</v>
       </c>
       <c r="T90">
-        <v>5.427864220237669</v>
+        <v>5.921306422077457</v>
       </c>
       <c r="U90">
         <v>0.1245366166625341</v>
       </c>
       <c r="V90">
-        <v>0.1199458196361671</v>
+        <v>0.1185981137975584</v>
       </c>
       <c r="W90">
-        <v>0.1095989701022313</v>
+        <v>0.109766808827628</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.9595665570893365</v>
+        <v>0.9487849103804673</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1361466481023583</v>
+        <v>0.1369340142689837</v>
       </c>
       <c r="C91">
-        <v>-3653.117599035299</v>
+        <v>-3779.346334120303</v>
       </c>
       <c r="D91">
-        <v>3674.496400964703</v>
+        <v>3643.093665879697</v>
       </c>
       <c r="E91">
-        <v>5325.214000000001</v>
+        <v>5420.04</v>
       </c>
       <c r="F91">
-        <v>8439.514000000001</v>
+        <v>8534.34</v>
       </c>
       <c r="G91">
         <v>1111.9</v>
@@ -8755,37 +8755,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M91">
-        <v>1051.02851983609</v>
+        <v>1062.837829047731</v>
       </c>
       <c r="N91">
-        <v>-53.82851983609009</v>
+        <v>-65.63782904773132</v>
       </c>
       <c r="O91">
-        <v>-6.728564979511262</v>
+        <v>-8.204728630966414</v>
       </c>
       <c r="P91">
-        <v>-47.09995485657883</v>
+        <v>-57.4331004167649</v>
       </c>
       <c r="Q91">
-        <v>104.0000451434212</v>
+        <v>93.66689958323509</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3495835295069949</v>
+        <v>0.3799618824576945</v>
       </c>
       <c r="T91">
-        <v>5.921306422077457</v>
+        <v>6.513437064285204</v>
       </c>
       <c r="U91">
         <v>0.1245366166625341</v>
       </c>
       <c r="V91">
-        <v>0.1185981137975584</v>
+        <v>0.1172803569775856</v>
       </c>
       <c r="W91">
-        <v>0.109766808827628</v>
+        <v>0.1099309178035714</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.9487849103804673</v>
+        <v>0.9382428558206846</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1369340142689837</v>
+        <v>0.137721380435609</v>
       </c>
       <c r="C92">
-        <v>-3779.346334120303</v>
+        <v>-3905.042873516965</v>
       </c>
       <c r="D92">
-        <v>3643.093665879697</v>
+        <v>3612.223126483036</v>
       </c>
       <c r="E92">
-        <v>5420.04</v>
+        <v>5514.866000000001</v>
       </c>
       <c r="F92">
-        <v>8534.34</v>
+        <v>8629.166000000001</v>
       </c>
       <c r="G92">
         <v>1111.9</v>
@@ -8837,37 +8837,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M92">
-        <v>1062.837829047731</v>
+        <v>1074.647138259373</v>
       </c>
       <c r="N92">
-        <v>-65.63782904773132</v>
+        <v>-77.44713825937299</v>
       </c>
       <c r="O92">
-        <v>-8.204728630966414</v>
+        <v>-9.680892282421624</v>
       </c>
       <c r="P92">
-        <v>-57.4331004167649</v>
+        <v>-67.76624597695137</v>
       </c>
       <c r="Q92">
-        <v>93.66689958323509</v>
+        <v>83.33375402304863</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3799618824576945</v>
+        <v>0.4170909805085494</v>
       </c>
       <c r="T92">
-        <v>6.513437064285204</v>
+        <v>7.237152293650228</v>
       </c>
       <c r="U92">
         <v>0.1245366166625341</v>
       </c>
       <c r="V92">
-        <v>0.1172803569775856</v>
+        <v>0.1159915618459637</v>
       </c>
       <c r="W92">
-        <v>0.1099309178035714</v>
+        <v>0.1100914199888347</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.9382428558206846</v>
+        <v>0.9279324947677099</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.137721380435609</v>
+        <v>0.1385087466022343</v>
       </c>
       <c r="C93">
-        <v>-3905.042873516965</v>
+        <v>-4030.220632572069</v>
       </c>
       <c r="D93">
-        <v>3612.223126483036</v>
+        <v>3581.871367427931</v>
       </c>
       <c r="E93">
-        <v>5514.866000000001</v>
+        <v>5609.692</v>
       </c>
       <c r="F93">
-        <v>8629.166000000001</v>
+        <v>8723.992</v>
       </c>
       <c r="G93">
         <v>1111.9</v>
@@ -8919,37 +8919,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M93">
-        <v>1074.647138259373</v>
+        <v>1086.456447471014</v>
       </c>
       <c r="N93">
-        <v>-77.44713825937299</v>
+        <v>-89.25644747101421</v>
       </c>
       <c r="O93">
-        <v>-9.680892282421624</v>
+        <v>-11.15705593387678</v>
       </c>
       <c r="P93">
-        <v>-67.76624597695137</v>
+        <v>-78.09939153713744</v>
       </c>
       <c r="Q93">
-        <v>83.33375402304863</v>
+        <v>73.00060846286256</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4170909805085494</v>
+        <v>0.4635023530721182</v>
       </c>
       <c r="T93">
-        <v>7.237152293650228</v>
+        <v>8.141796330356508</v>
       </c>
       <c r="U93">
         <v>0.1245366166625341</v>
       </c>
       <c r="V93">
-        <v>0.1159915618459637</v>
+        <v>0.114730783999812</v>
       </c>
       <c r="W93">
-        <v>0.1100914199888347</v>
+        <v>0.1102484329961575</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.9279324947677099</v>
+        <v>0.9178462719984958</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1385087466022343</v>
+        <v>0.1392961127688597</v>
       </c>
       <c r="C94">
-        <v>-4030.220632572069</v>
+        <v>-4154.89257949884</v>
       </c>
       <c r="D94">
-        <v>3581.871367427931</v>
+        <v>3552.025420501161</v>
       </c>
       <c r="E94">
-        <v>5609.692</v>
+        <v>5704.518000000001</v>
       </c>
       <c r="F94">
-        <v>8723.992</v>
+        <v>8818.818000000001</v>
       </c>
       <c r="G94">
         <v>1111.9</v>
@@ -9001,37 +9001,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M94">
-        <v>1086.456447471014</v>
+        <v>1098.265756682656</v>
       </c>
       <c r="N94">
-        <v>-89.25644747101421</v>
+        <v>-101.0657566826559</v>
       </c>
       <c r="O94">
-        <v>-11.15705593387678</v>
+        <v>-12.63321958533199</v>
       </c>
       <c r="P94">
-        <v>-78.09939153713744</v>
+        <v>-88.4325370973239</v>
       </c>
       <c r="Q94">
-        <v>73.00060846286256</v>
+        <v>62.66746290267609</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4635023530721182</v>
+        <v>0.5231741177967065</v>
       </c>
       <c r="T94">
-        <v>8.141796330356508</v>
+        <v>9.30491009183601</v>
       </c>
       <c r="U94">
         <v>0.1245366166625341</v>
       </c>
       <c r="V94">
-        <v>0.114730783999812</v>
+        <v>0.113497119655728</v>
       </c>
       <c r="W94">
-        <v>0.1102484329961575</v>
+        <v>0.1104020693796669</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.9178462719984958</v>
+        <v>0.9079769572458236</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1392961127688597</v>
+        <v>0.140083478935485</v>
       </c>
       <c r="C95">
-        <v>-4154.89257949884</v>
+        <v>-4279.071253851691</v>
       </c>
       <c r="D95">
-        <v>3552.025420501161</v>
+        <v>3522.672746148309</v>
       </c>
       <c r="E95">
-        <v>5704.518000000001</v>
+        <v>5799.344</v>
       </c>
       <c r="F95">
-        <v>8818.818000000001</v>
+        <v>8913.644</v>
       </c>
       <c r="G95">
         <v>1111.9</v>
@@ -9083,37 +9083,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M95">
-        <v>1098.265756682656</v>
+        <v>1110.075065894297</v>
       </c>
       <c r="N95">
-        <v>-101.0657566826559</v>
+        <v>-112.8750658942971</v>
       </c>
       <c r="O95">
-        <v>-12.63321958533199</v>
+        <v>-14.10938323678714</v>
       </c>
       <c r="P95">
-        <v>-88.4325370973239</v>
+        <v>-98.76568265750997</v>
       </c>
       <c r="Q95">
-        <v>62.66746290267609</v>
+        <v>52.33431734249002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5231741177967065</v>
+        <v>0.6027364707628244</v>
       </c>
       <c r="T95">
-        <v>9.30491009183601</v>
+        <v>10.85572844047535</v>
       </c>
       <c r="U95">
         <v>0.1245366166625341</v>
       </c>
       <c r="V95">
-        <v>0.113497119655728</v>
+        <v>0.1122897034891777</v>
       </c>
       <c r="W95">
-        <v>0.1104020693796669</v>
+        <v>0.1105524369039528</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.9079769572458236</v>
+        <v>0.8983176279134215</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.140083478935485</v>
+        <v>0.1408708451021104</v>
       </c>
       <c r="C96">
-        <v>-4279.071253851691</v>
+        <v>-4402.768784092505</v>
       </c>
       <c r="D96">
-        <v>3522.672746148309</v>
+        <v>3493.801215907497</v>
       </c>
       <c r="E96">
-        <v>5799.344</v>
+        <v>5894.170000000001</v>
       </c>
       <c r="F96">
-        <v>8913.644</v>
+        <v>9008.470000000001</v>
       </c>
       <c r="G96">
         <v>1111.9</v>
@@ -9165,37 +9165,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M96">
-        <v>1110.075065894297</v>
+        <v>1121.884375105939</v>
       </c>
       <c r="N96">
-        <v>-112.8750658942971</v>
+        <v>-124.6843751059388</v>
       </c>
       <c r="O96">
-        <v>-14.10938323678714</v>
+        <v>-15.58554688824235</v>
       </c>
       <c r="P96">
-        <v>-98.76568265750997</v>
+        <v>-109.0988282176964</v>
       </c>
       <c r="Q96">
-        <v>52.33431734249002</v>
+        <v>42.00117178230356</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6027364707628244</v>
+        <v>0.7141237649153896</v>
       </c>
       <c r="T96">
-        <v>10.85572844047535</v>
+        <v>13.02687412857042</v>
       </c>
       <c r="U96">
         <v>0.1245366166625341</v>
       </c>
       <c r="V96">
-        <v>0.1122897034891777</v>
+        <v>0.1111077066103442</v>
       </c>
       <c r="W96">
-        <v>0.1105524369039528</v>
+        <v>0.1106996387961484</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8983176279134215</v>
+        <v>0.8888616528827537</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1408708451021104</v>
+        <v>0.1416582112687357</v>
       </c>
       <c r="C97">
-        <v>-4402.768784092505</v>
+        <v>-4525.996904300058</v>
       </c>
       <c r="D97">
-        <v>3493.801215907497</v>
+        <v>3465.399095699942</v>
       </c>
       <c r="E97">
-        <v>5894.170000000001</v>
+        <v>5988.996</v>
       </c>
       <c r="F97">
-        <v>9008.470000000001</v>
+        <v>9103.296</v>
       </c>
       <c r="G97">
         <v>1111.9</v>
@@ -9247,37 +9247,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M97">
-        <v>1121.884375105939</v>
+        <v>1133.69368431758</v>
       </c>
       <c r="N97">
-        <v>-124.6843751059388</v>
+        <v>-136.4936843175802</v>
       </c>
       <c r="O97">
-        <v>-15.58554688824235</v>
+        <v>-17.06171053969753</v>
       </c>
       <c r="P97">
-        <v>-109.0988282176964</v>
+        <v>-119.4319737778827</v>
       </c>
       <c r="Q97">
-        <v>42.00117178230356</v>
+        <v>31.66802622211729</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7141237649153896</v>
+        <v>0.8812047061442374</v>
       </c>
       <c r="T97">
-        <v>13.02687412857042</v>
+        <v>16.28359266071304</v>
       </c>
       <c r="U97">
         <v>0.1245366166625341</v>
       </c>
       <c r="V97">
-        <v>0.1111077066103442</v>
+        <v>0.1099503346664865</v>
       </c>
       <c r="W97">
-        <v>0.1106996387961484</v>
+        <v>0.1108437739822565</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8888616528827537</v>
+        <v>0.8796026773318917</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1416582112687357</v>
+        <v>0.1424455774353611</v>
       </c>
       <c r="C98">
-        <v>-4525.996904300058</v>
+        <v>-4648.766970071054</v>
       </c>
       <c r="D98">
-        <v>3465.399095699942</v>
+        <v>3437.455029928945</v>
       </c>
       <c r="E98">
-        <v>5988.996</v>
+        <v>6083.821999999999</v>
       </c>
       <c r="F98">
-        <v>9103.296</v>
+        <v>9198.121999999999</v>
       </c>
       <c r="G98">
         <v>1111.9</v>
@@ -9329,37 +9329,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M98">
-        <v>1133.69368431758</v>
+        <v>1145.502993529221</v>
       </c>
       <c r="N98">
-        <v>-136.4936843175802</v>
+        <v>-148.3029935292215</v>
       </c>
       <c r="O98">
-        <v>-17.06171053969753</v>
+        <v>-18.53787419115268</v>
       </c>
       <c r="P98">
-        <v>-119.4319737778827</v>
+        <v>-129.7651193380688</v>
       </c>
       <c r="Q98">
-        <v>31.66802622211729</v>
+        <v>21.33488066193124</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8812047061442351</v>
+        <v>1.159672941525647</v>
       </c>
       <c r="T98">
-        <v>16.28359266071299</v>
+        <v>21.71145688095066</v>
       </c>
       <c r="U98">
         <v>0.1245366166625341</v>
       </c>
       <c r="V98">
-        <v>0.1099503346664865</v>
+        <v>0.1088168260616773</v>
       </c>
       <c r="W98">
-        <v>0.1108437739822565</v>
+        <v>0.1109849373088573</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8796026773318917</v>
+        <v>0.8705346084934187</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1424455774353611</v>
+        <v>0.1432329436019864</v>
       </c>
       <c r="C99">
-        <v>-4648.766970071054</v>
+        <v>-4771.089973657937</v>
       </c>
       <c r="D99">
-        <v>3437.455029928945</v>
+        <v>3409.958026342063</v>
       </c>
       <c r="E99">
-        <v>6083.821999999999</v>
+        <v>6178.648</v>
       </c>
       <c r="F99">
-        <v>9198.121999999999</v>
+        <v>9292.948</v>
       </c>
       <c r="G99">
         <v>1111.9</v>
@@ -9411,37 +9411,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M99">
-        <v>1145.502993529221</v>
+        <v>1157.312302740863</v>
       </c>
       <c r="N99">
-        <v>-148.3029935292215</v>
+        <v>-160.1123027408631</v>
       </c>
       <c r="O99">
-        <v>-18.53787419115268</v>
+        <v>-20.01403784260789</v>
       </c>
       <c r="P99">
-        <v>-129.7651193380688</v>
+        <v>-140.0982648982553</v>
       </c>
       <c r="Q99">
-        <v>21.33488066193124</v>
+        <v>11.00173510174474</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.159672941525647</v>
+        <v>1.71660941228847</v>
       </c>
       <c r="T99">
-        <v>21.71145688095066</v>
+        <v>32.56718532142598</v>
       </c>
       <c r="U99">
         <v>0.1245366166625341</v>
       </c>
       <c r="V99">
-        <v>0.1088168260616773</v>
+        <v>0.1077064502855378</v>
       </c>
       <c r="W99">
-        <v>0.1109849373088573</v>
+        <v>0.1111232197512418</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8705346084934187</v>
+        <v>0.861651602284302</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1432329436019864</v>
+        <v>0.1440203097686117</v>
       </c>
       <c r="C100">
-        <v>-4771.089973657937</v>
+        <v>-4892.976558385946</v>
       </c>
       <c r="D100">
-        <v>3409.958026342063</v>
+        <v>3382.897441614053</v>
       </c>
       <c r="E100">
-        <v>6178.648</v>
+        <v>6273.473999999999</v>
       </c>
       <c r="F100">
-        <v>9292.948</v>
+        <v>9387.773999999999</v>
       </c>
       <c r="G100">
         <v>1111.9</v>
@@ -9493,37 +9493,37 @@
         <v>997.1999999999999</v>
       </c>
       <c r="M100">
-        <v>1157.312302740863</v>
+        <v>1169.121611952504</v>
       </c>
       <c r="N100">
-        <v>-160.1123027408631</v>
+        <v>-171.9216119525043</v>
       </c>
       <c r="O100">
-        <v>-20.01403784260789</v>
+        <v>-21.49020149406304</v>
       </c>
       <c r="P100">
-        <v>-140.0982648982553</v>
+        <v>-150.4314104584413</v>
       </c>
       <c r="Q100">
-        <v>11.00173510174474</v>
+        <v>0.6685895415587026</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.71660941228847</v>
+        <v>3.38741882457694</v>
       </c>
       <c r="T100">
-        <v>32.56718532142598</v>
+        <v>65.13437064285196</v>
       </c>
       <c r="U100">
         <v>0.1245366166625341</v>
       </c>
       <c r="V100">
-        <v>0.1077064502855378</v>
+        <v>0.1066185063432596</v>
       </c>
       <c r="W100">
-        <v>0.1111232197512418</v>
+        <v>0.1112587086089316</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.861651602284302</v>
+        <v>0.8529480507460769</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1440203097686117</v>
-      </c>
-      <c r="C101">
-        <v>-4892.976558385946</v>
-      </c>
-      <c r="D101">
-        <v>3382.897441614053</v>
-      </c>
-      <c r="E101">
-        <v>6273.473999999999</v>
-      </c>
-      <c r="F101">
-        <v>9387.773999999999</v>
-      </c>
-      <c r="G101">
-        <v>1111.9</v>
-      </c>
-      <c r="H101">
-        <v>6368.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1148.3</v>
-      </c>
-      <c r="K101">
-        <v>151.1</v>
-      </c>
-      <c r="L101">
-        <v>997.1999999999999</v>
-      </c>
-      <c r="M101">
-        <v>1169.121611952504</v>
-      </c>
-      <c r="N101">
-        <v>-171.9216119525043</v>
-      </c>
-      <c r="O101">
-        <v>-21.49020149406304</v>
-      </c>
-      <c r="P101">
-        <v>-150.4314104584413</v>
-      </c>
-      <c r="Q101">
-        <v>0.6685895415587026</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.38741882457694</v>
-      </c>
-      <c r="T101">
-        <v>65.13437064285196</v>
-      </c>
-      <c r="U101">
-        <v>0.1245366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.1066185063432596</v>
-      </c>
-      <c r="W101">
-        <v>0.1112587086089316</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Caa/CCC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8529480507460769</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
